--- a/recipes/onion-garlic-free-indian/focus-states/01-goa/excel/goa-recipes.xlsx
+++ b/recipes/onion-garlic-free-indian/focus-states/01-goa/excel/goa-recipes.xlsx
@@ -104,7 +104,7 @@
       <name val="Calibri"/>
       <b val="1"/>
       <color rgb="009A3412"/>
-      <sz val="16"/>
+      <sz val="12"/>
     </font>
   </fonts>
   <fills count="19">
@@ -259,7 +259,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="50">
+  <cellXfs count="53">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
@@ -358,6 +358,9 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="18" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -1465,7 +1468,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:D23"/>
+  <dimension ref="A1:D39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -1477,7 +1480,7 @@
     <row r="1" ht="32" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>RECIPE CARD  ·  Alsande Tondak (no garlic)</t>
+          <t>Parslia Kitchen OS · RECIPE CARD · Alsande Tondak (no garlic)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1487,7 +1490,7 @@
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>Goa kitchen  ·  Side  ·  Goan Hindu vegetarian / sattvic</t>
+          <t>Pure Prasad · No onion · No garlic · No eggs · No meat · No fish  ·  Goa  ·  Side</t>
         </is>
       </c>
       <c r="B2" s="4" t="n"/>
@@ -1507,44 +1510,44 @@
     <row r="5" ht="18" customHeight="1">
       <c r="A5" s="39" t="inlineStr">
         <is>
-          <t>Serves</t>
+          <t>YIELD</t>
         </is>
       </c>
       <c r="B5" s="39" t="inlineStr">
         <is>
-          <t>Prep</t>
+          <t>PORTION</t>
         </is>
       </c>
       <c r="C5" s="39" t="inlineStr">
         <is>
-          <t>Cook</t>
+          <t>SERVICE</t>
         </is>
       </c>
       <c r="D5" s="39" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>TIME</t>
         </is>
       </c>
     </row>
     <row r="6" ht="28" customHeight="1">
       <c r="A6" s="40" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>4 portions</t>
         </is>
       </c>
       <c r="B6" s="40" t="inlineStr">
         <is>
-          <t>10 min</t>
+          <t>1 portion</t>
         </is>
       </c>
       <c r="C6" s="40" t="inlineStr">
         <is>
-          <t>25 min</t>
+          <t>Hot</t>
         </is>
       </c>
       <c r="D6" s="40" t="inlineStr">
         <is>
-          <t>35 min</t>
+          <t>Prep 10 min · Cook 25 min</t>
         </is>
       </c>
     </row>
@@ -1746,37 +1749,216 @@
       <c r="C22" s="46" t="n"/>
       <c r="D22" s="46" t="n"/>
     </row>
-    <row r="23" ht="36" customHeight="1">
+    <row r="23" ht="66" customHeight="1">
       <c r="A23" s="47" t="n">
         <v>1</v>
       </c>
       <c r="B23" s="48" t="inlineStr">
         <is>
-          <t>Cook beans with kokum. Add coconut and spices until thick.</t>
+          <t>Mise en place. Weigh every ingredient on this card for 4 portions. Set Stainless steel kadhai or saucepan — never aluminium. Wash produce. Confirm spice blends have no onion or garlic powder. No onion, no garlic, no aluminium.</t>
         </is>
       </c>
       <c r="C23" s="49" t="n"/>
       <c r="D23" s="49" t="n"/>
     </row>
+    <row r="24" ht="36" customHeight="1">
+      <c r="A24" s="32" t="n">
+        <v>2</v>
+      </c>
+      <c r="B24" s="30" t="inlineStr">
+        <is>
+          <t>Cut vegetables to even size so they cook together.</t>
+        </is>
+      </c>
+      <c r="C24" s="31" t="n"/>
+      <c r="D24" s="31" t="n"/>
+    </row>
+    <row r="25" ht="54" customHeight="1">
+      <c r="A25" s="47" t="n">
+        <v>3</v>
+      </c>
+      <c r="B25" s="48" t="inlineStr">
+        <is>
+          <t>Heat fat in Stainless steel kadhai or saucepan — never aluminium on medium. Bloom hing 20–30 seconds until fragrant — this is the onion-garlic stand-in. Do not burn it.</t>
+        </is>
+      </c>
+      <c r="C25" s="49" t="n"/>
+      <c r="D25" s="49" t="n"/>
+    </row>
+    <row r="26" ht="54" customHeight="1">
+      <c r="A26" s="32" t="n">
+        <v>4</v>
+      </c>
+      <c r="B26" s="30" t="inlineStr">
+        <is>
+          <t>Cook beans with kokum. Work in Stainless steel kadhai or saucepan — never aluminium. Cook to the doneness below, tasting salt at the end. Do not add onion, garlic or aluminium cookware.</t>
+        </is>
+      </c>
+      <c r="C26" s="31" t="n"/>
+      <c r="D26" s="31" t="n"/>
+    </row>
+    <row r="27" ht="54" customHeight="1">
+      <c r="A27" s="47" t="n">
+        <v>5</v>
+      </c>
+      <c r="B27" s="48" t="inlineStr">
+        <is>
+          <t>Add coconut and spices until thick. Work in Stainless steel kadhai or saucepan — never aluminium. Cook to the doneness below, tasting salt at the end. Do not add onion, garlic or aluminium cookware.</t>
+        </is>
+      </c>
+      <c r="C27" s="49" t="n"/>
+      <c r="D27" s="49" t="n"/>
+    </row>
+    <row r="28" ht="42" customHeight="1">
+      <c r="A28" s="32" t="n">
+        <v>6</v>
+      </c>
+      <c r="B28" s="30" t="inlineStr">
+        <is>
+          <t>Doneness: vegetables yield to a knife, gravy coats a spoon, salt is balanced. Rest 2 minutes off the heat so seasoning settles.</t>
+        </is>
+      </c>
+      <c r="C28" s="31" t="n"/>
+      <c r="D28" s="31" t="n"/>
+    </row>
+    <row r="29" ht="42" customHeight="1">
+      <c r="A29" s="47" t="n">
+        <v>7</v>
+      </c>
+      <c r="B29" s="48" t="inlineStr">
+        <is>
+          <t>Taste and adjust salt, lemon or chilli only — do not add onion or garlic at the finish. Garnish as listed. Yield is 4 portions.</t>
+        </is>
+      </c>
+      <c r="C29" s="49" t="n"/>
+      <c r="D29" s="49" t="n"/>
+    </row>
+    <row r="30" ht="42" customHeight="1">
+      <c r="A30" s="32" t="n">
+        <v>8</v>
+      </c>
+      <c r="B30" s="30" t="inlineStr">
+        <is>
+          <t>Hold hot above 63 C if the pass is delayed, or cool quickly and reheat once only to piping hot. Do not hold in aluminium. Service: Hot.</t>
+        </is>
+      </c>
+      <c r="C30" s="31" t="n"/>
+      <c r="D30" s="31" t="n"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="21" t="inlineStr">
+        <is>
+          <t>Nutrition per portion</t>
+        </is>
+      </c>
+      <c r="B32" s="22" t="n"/>
+      <c r="C32" s="22" t="n"/>
+      <c r="D32" s="22" t="n"/>
+    </row>
+    <row r="33" ht="36" customHeight="1">
+      <c r="A33" s="12" t="inlineStr">
+        <is>
+          <t>kcal 589  ·  Protein 29 g  ·  Carbs 93 g  ·  Fat 13 g  ·  Fibre 23 g. Nutrition is a kitchen estimate from typical produce values, not a laboratory analysis.</t>
+        </is>
+      </c>
+      <c r="B33" s="50" t="n"/>
+      <c r="C33" s="50" t="n"/>
+      <c r="D33" s="50" t="n"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="24" t="inlineStr">
+        <is>
+          <t>Allergens</t>
+        </is>
+      </c>
+      <c r="B34" s="6" t="n"/>
+      <c r="C34" s="6" t="n"/>
+      <c r="D34" s="6" t="n"/>
+    </row>
+    <row r="35" ht="48" customHeight="1">
+      <c r="A35" s="25" t="inlineStr">
+        <is>
+          <t>Gluten (wheat) · Always verify labels; this card is a kitchen estimate, not a lab certificate.</t>
+        </is>
+      </c>
+      <c r="B35" s="26" t="n"/>
+      <c r="C35" s="26" t="n"/>
+      <c r="D35" s="26" t="n"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="24" t="inlineStr">
+        <is>
+          <t>Chef notes</t>
+        </is>
+      </c>
+      <c r="B36" s="6" t="n"/>
+      <c r="C36" s="6" t="n"/>
+      <c r="D36" s="6" t="n"/>
+    </row>
+    <row r="37" ht="72" customHeight="1">
+      <c r="A37" s="25" t="inlineStr">
+        <is>
+          <t>For Alsande Tondak (no garlic): keep the mix slightly drier than you think; wet mixes split or go greasy. Bloom hing in hot fat 20–30 seconds; raw hing tastes medicinal. Commercial hing is often cut with wheat flour — use a gluten-free hing if you must mark Gluten Free. Never cook tomato, tamarind, lemon, yogurt or milk in aluminium; use stainless steel, iron, clay or glass. Spice blends: read the packet. Many garam masalas hide onion or garlic powder.</t>
+        </is>
+      </c>
+      <c r="B37" s="26" t="n"/>
+      <c r="C37" s="26" t="n"/>
+      <c r="D37" s="26" t="n"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="51" t="inlineStr">
+        <is>
+          <t>Service notes</t>
+        </is>
+      </c>
+      <c r="B38" s="52" t="n"/>
+      <c r="C38" s="52" t="n"/>
+      <c r="D38" s="52" t="n"/>
+    </row>
+    <row r="39" ht="64" customHeight="1">
+      <c r="A39" s="12" t="inlineStr">
+        <is>
+          <t>Serve family-style in a steel bowl. Keep a lid on at the pass so it does not skin. Service temperature: Hot. Allergen label for this dish: Gluten (wheat); Always verify labels; this card is a kitchen estimate, not a lab certificate. State clearly: vegetarian, no onion, no garlic, no eggs, no meat, no fish. Nutrition on this card is an estimate for 1 portion of 4.</t>
+        </is>
+      </c>
+      <c r="B39" s="50" t="n"/>
+      <c r="C39" s="50" t="n"/>
+      <c r="D39" s="50" t="n"/>
+    </row>
   </sheetData>
-  <mergeCells count="17">
+  <mergeCells count="32">
+    <mergeCell ref="A8:D8"/>
+    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="B23:D23"/>
+    <mergeCell ref="A35:D35"/>
+    <mergeCell ref="A38:D38"/>
+    <mergeCell ref="C14:D14"/>
+    <mergeCell ref="B29:D29"/>
+    <mergeCell ref="B28:D28"/>
+    <mergeCell ref="A9:D9"/>
+    <mergeCell ref="C16:D16"/>
+    <mergeCell ref="A34:D34"/>
+    <mergeCell ref="A39:D39"/>
+    <mergeCell ref="B30:D30"/>
+    <mergeCell ref="A11:D11"/>
+    <mergeCell ref="B24:D24"/>
+    <mergeCell ref="A36:D36"/>
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="C12:D12"/>
-    <mergeCell ref="A9:D9"/>
-    <mergeCell ref="A8:D8"/>
-    <mergeCell ref="C16:D16"/>
-    <mergeCell ref="C15:D15"/>
-    <mergeCell ref="B23:D23"/>
+    <mergeCell ref="B26:D26"/>
+    <mergeCell ref="B25:D25"/>
+    <mergeCell ref="C17:D17"/>
+    <mergeCell ref="A37:D37"/>
     <mergeCell ref="B22:D22"/>
     <mergeCell ref="A3:D3"/>
     <mergeCell ref="C19:D19"/>
     <mergeCell ref="A21:D21"/>
-    <mergeCell ref="C14:D14"/>
+    <mergeCell ref="B27:D27"/>
     <mergeCell ref="C13:D13"/>
     <mergeCell ref="A2:D2"/>
-    <mergeCell ref="A11:D11"/>
-    <mergeCell ref="C17:D17"/>
     <mergeCell ref="C18:D18"/>
+    <mergeCell ref="A33:D33"/>
+    <mergeCell ref="A32:D32"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" paperSize="9" fitToHeight="1" fitToWidth="1"/>
@@ -1790,7 +1972,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:D23"/>
+  <dimension ref="A1:D38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -1802,7 +1984,7 @@
     <row r="1" ht="32" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>RECIPE CARD  ·  Cabbage Foogath</t>
+          <t>Parslia Kitchen OS · RECIPE CARD · Cabbage Foogath</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1812,7 +1994,7 @@
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>Goa kitchen  ·  Side  ·  Goan Hindu vegetarian / sattvic</t>
+          <t>Pure Prasad · No onion · No garlic · No eggs · No meat · No fish  ·  Goa  ·  Side</t>
         </is>
       </c>
       <c r="B2" s="4" t="n"/>
@@ -1832,44 +2014,44 @@
     <row r="5" ht="18" customHeight="1">
       <c r="A5" s="39" t="inlineStr">
         <is>
-          <t>Serves</t>
+          <t>YIELD</t>
         </is>
       </c>
       <c r="B5" s="39" t="inlineStr">
         <is>
-          <t>Prep</t>
+          <t>PORTION</t>
         </is>
       </c>
       <c r="C5" s="39" t="inlineStr">
         <is>
-          <t>Cook</t>
+          <t>SERVICE</t>
         </is>
       </c>
       <c r="D5" s="39" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>TIME</t>
         </is>
       </c>
     </row>
     <row r="6" ht="28" customHeight="1">
       <c r="A6" s="40" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>4 portions</t>
         </is>
       </c>
       <c r="B6" s="40" t="inlineStr">
         <is>
-          <t>10 min</t>
+          <t>1 portion</t>
         </is>
       </c>
       <c r="C6" s="40" t="inlineStr">
         <is>
-          <t>12 min</t>
+          <t>Hot</t>
         </is>
       </c>
       <c r="D6" s="40" t="inlineStr">
         <is>
-          <t>22 min</t>
+          <t>Prep 10 min · Cook 12 min</t>
         </is>
       </c>
     </row>
@@ -2071,37 +2253,203 @@
       <c r="C22" s="46" t="n"/>
       <c r="D22" s="46" t="n"/>
     </row>
-    <row r="23" ht="36" customHeight="1">
+    <row r="23" ht="66" customHeight="1">
       <c r="A23" s="47" t="n">
         <v>1</v>
       </c>
       <c r="B23" s="48" t="inlineStr">
         <is>
-          <t>Temper, stir-fry cabbage, finish coconut.</t>
+          <t>Mise en place. Weigh every ingredient on this card for 4 portions. Set Stainless steel kadhai or saucepan — never aluminium. Wash produce. Confirm spice blends have no onion or garlic powder. No onion, no garlic, no aluminium.</t>
         </is>
       </c>
       <c r="C23" s="49" t="n"/>
       <c r="D23" s="49" t="n"/>
     </row>
+    <row r="24" ht="36" customHeight="1">
+      <c r="A24" s="32" t="n">
+        <v>2</v>
+      </c>
+      <c r="B24" s="30" t="inlineStr">
+        <is>
+          <t>Cut vegetables to even size so they cook together.</t>
+        </is>
+      </c>
+      <c r="C24" s="31" t="n"/>
+      <c r="D24" s="31" t="n"/>
+    </row>
+    <row r="25" ht="54" customHeight="1">
+      <c r="A25" s="47" t="n">
+        <v>3</v>
+      </c>
+      <c r="B25" s="48" t="inlineStr">
+        <is>
+          <t>Heat fat in Stainless steel kadhai or saucepan — never aluminium on medium. Bloom hing 20–30 seconds until fragrant — this is the onion-garlic stand-in. Do not burn it.</t>
+        </is>
+      </c>
+      <c r="C25" s="49" t="n"/>
+      <c r="D25" s="49" t="n"/>
+    </row>
+    <row r="26" ht="54" customHeight="1">
+      <c r="A26" s="32" t="n">
+        <v>4</v>
+      </c>
+      <c r="B26" s="30" t="inlineStr">
+        <is>
+          <t>Temper, stir-fry cabbage, finish coconut. Work in Stainless steel kadhai or saucepan — never aluminium. Cook to the doneness below, tasting salt at the end. Do not add onion, garlic or aluminium cookware.</t>
+        </is>
+      </c>
+      <c r="C26" s="31" t="n"/>
+      <c r="D26" s="31" t="n"/>
+    </row>
+    <row r="27" ht="42" customHeight="1">
+      <c r="A27" s="47" t="n">
+        <v>5</v>
+      </c>
+      <c r="B27" s="48" t="inlineStr">
+        <is>
+          <t>Doneness: vegetables yield to a knife, gravy coats a spoon, salt is balanced. Rest 2 minutes off the heat so seasoning settles.</t>
+        </is>
+      </c>
+      <c r="C27" s="49" t="n"/>
+      <c r="D27" s="49" t="n"/>
+    </row>
+    <row r="28" ht="42" customHeight="1">
+      <c r="A28" s="32" t="n">
+        <v>6</v>
+      </c>
+      <c r="B28" s="30" t="inlineStr">
+        <is>
+          <t>Taste and adjust salt, lemon or chilli only — do not add onion or garlic at the finish. Garnish as listed. Yield is 4 portions.</t>
+        </is>
+      </c>
+      <c r="C28" s="31" t="n"/>
+      <c r="D28" s="31" t="n"/>
+    </row>
+    <row r="29" ht="42" customHeight="1">
+      <c r="A29" s="47" t="n">
+        <v>7</v>
+      </c>
+      <c r="B29" s="48" t="inlineStr">
+        <is>
+          <t>Hold hot above 63 C if the pass is delayed, or cool quickly and reheat once only to piping hot. Do not hold in aluminium. Service: Hot.</t>
+        </is>
+      </c>
+      <c r="C29" s="49" t="n"/>
+      <c r="D29" s="49" t="n"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="21" t="inlineStr">
+        <is>
+          <t>Nutrition per portion</t>
+        </is>
+      </c>
+      <c r="B31" s="22" t="n"/>
+      <c r="C31" s="22" t="n"/>
+      <c r="D31" s="22" t="n"/>
+    </row>
+    <row r="32" ht="36" customHeight="1">
+      <c r="A32" s="12" t="inlineStr">
+        <is>
+          <t>kcal 131  ·  Protein 3 g  ·  Carbs 14 g  ·  Fat 8 g  ·  Fibre 6 g. Nutrition is a kitchen estimate from typical produce values, not a laboratory analysis.</t>
+        </is>
+      </c>
+      <c r="B32" s="50" t="n"/>
+      <c r="C32" s="50" t="n"/>
+      <c r="D32" s="50" t="n"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="24" t="inlineStr">
+        <is>
+          <t>Allergens</t>
+        </is>
+      </c>
+      <c r="B33" s="6" t="n"/>
+      <c r="C33" s="6" t="n"/>
+      <c r="D33" s="6" t="n"/>
+    </row>
+    <row r="34" ht="48" customHeight="1">
+      <c r="A34" s="25" t="inlineStr">
+        <is>
+          <t>Gluten (wheat) · Mustard · Always verify labels; this card is a kitchen estimate, not a lab certificate.</t>
+        </is>
+      </c>
+      <c r="B34" s="26" t="n"/>
+      <c r="C34" s="26" t="n"/>
+      <c r="D34" s="26" t="n"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="24" t="inlineStr">
+        <is>
+          <t>Chef notes</t>
+        </is>
+      </c>
+      <c r="B35" s="6" t="n"/>
+      <c r="C35" s="6" t="n"/>
+      <c r="D35" s="6" t="n"/>
+    </row>
+    <row r="36" ht="72" customHeight="1">
+      <c r="A36" s="25" t="inlineStr">
+        <is>
+          <t>For Cabbage Foogath: keep the mix slightly drier than you think; wet mixes split or go greasy. Bloom hing in hot fat 20–30 seconds; raw hing tastes medicinal. Commercial hing is often cut with wheat flour — use a gluten-free hing if you must mark Gluten Free. Never cook tomato, tamarind, lemon, yogurt or milk in aluminium; use stainless steel, iron, clay or glass. Spice blends: read the packet. Many garam masalas hide onion or garlic powder.</t>
+        </is>
+      </c>
+      <c r="B36" s="26" t="n"/>
+      <c r="C36" s="26" t="n"/>
+      <c r="D36" s="26" t="n"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="51" t="inlineStr">
+        <is>
+          <t>Service notes</t>
+        </is>
+      </c>
+      <c r="B37" s="52" t="n"/>
+      <c r="C37" s="52" t="n"/>
+      <c r="D37" s="52" t="n"/>
+    </row>
+    <row r="38" ht="64" customHeight="1">
+      <c r="A38" s="12" t="inlineStr">
+        <is>
+          <t>Serve family-style in a steel bowl. Keep a lid on at the pass so it does not skin. Service temperature: Hot. Allergen label for this dish: Gluten (wheat); Mustard; Always verify labels; this card is a kitchen estimate, not a lab certificate. State clearly: vegetarian, no onion, no garlic, no eggs, no meat, no fish. Nutrition on this card is an estimate for 1 portion of 4.</t>
+        </is>
+      </c>
+      <c r="B38" s="50" t="n"/>
+      <c r="C38" s="50" t="n"/>
+      <c r="D38" s="50" t="n"/>
+    </row>
   </sheetData>
-  <mergeCells count="17">
+  <mergeCells count="31">
+    <mergeCell ref="A8:D8"/>
+    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="B23:D23"/>
+    <mergeCell ref="A35:D35"/>
+    <mergeCell ref="A38:D38"/>
+    <mergeCell ref="C14:D14"/>
+    <mergeCell ref="B29:D29"/>
+    <mergeCell ref="B28:D28"/>
+    <mergeCell ref="A9:D9"/>
+    <mergeCell ref="A31:D31"/>
+    <mergeCell ref="C16:D16"/>
+    <mergeCell ref="A34:D34"/>
+    <mergeCell ref="A11:D11"/>
+    <mergeCell ref="B24:D24"/>
+    <mergeCell ref="A36:D36"/>
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="C12:D12"/>
-    <mergeCell ref="A9:D9"/>
-    <mergeCell ref="A8:D8"/>
-    <mergeCell ref="C16:D16"/>
-    <mergeCell ref="C15:D15"/>
-    <mergeCell ref="B23:D23"/>
+    <mergeCell ref="B26:D26"/>
+    <mergeCell ref="B25:D25"/>
+    <mergeCell ref="C17:D17"/>
+    <mergeCell ref="A37:D37"/>
     <mergeCell ref="B22:D22"/>
     <mergeCell ref="A3:D3"/>
     <mergeCell ref="C19:D19"/>
     <mergeCell ref="A21:D21"/>
-    <mergeCell ref="C14:D14"/>
+    <mergeCell ref="B27:D27"/>
     <mergeCell ref="C13:D13"/>
     <mergeCell ref="A2:D2"/>
-    <mergeCell ref="A11:D11"/>
-    <mergeCell ref="C17:D17"/>
     <mergeCell ref="C18:D18"/>
+    <mergeCell ref="A33:D33"/>
+    <mergeCell ref="A32:D32"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" paperSize="9" fitToHeight="1" fitToWidth="1"/>
@@ -2115,7 +2463,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:D23"/>
+  <dimension ref="A1:D38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -2127,7 +2475,7 @@
     <row r="1" ht="32" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>RECIPE CARD  ·  Pumpkin Bhaji</t>
+          <t>Parslia Kitchen OS · RECIPE CARD · Pumpkin Bhaji</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2137,7 +2485,7 @@
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>Goa kitchen  ·  Side  ·  Goan Hindu vegetarian / sattvic</t>
+          <t>Pure Prasad · No onion · No garlic · No eggs · No meat · No fish  ·  Goa  ·  Side</t>
         </is>
       </c>
       <c r="B2" s="4" t="n"/>
@@ -2157,44 +2505,44 @@
     <row r="5" ht="18" customHeight="1">
       <c r="A5" s="39" t="inlineStr">
         <is>
-          <t>Serves</t>
+          <t>YIELD</t>
         </is>
       </c>
       <c r="B5" s="39" t="inlineStr">
         <is>
-          <t>Prep</t>
+          <t>PORTION</t>
         </is>
       </c>
       <c r="C5" s="39" t="inlineStr">
         <is>
-          <t>Cook</t>
+          <t>SERVICE</t>
         </is>
       </c>
       <c r="D5" s="39" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>TIME</t>
         </is>
       </c>
     </row>
     <row r="6" ht="28" customHeight="1">
       <c r="A6" s="40" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>4 portions</t>
         </is>
       </c>
       <c r="B6" s="40" t="inlineStr">
         <is>
-          <t>10 min</t>
+          <t>1 portion</t>
         </is>
       </c>
       <c r="C6" s="40" t="inlineStr">
         <is>
-          <t>15 min</t>
+          <t>Hot</t>
         </is>
       </c>
       <c r="D6" s="40" t="inlineStr">
         <is>
-          <t>25 min</t>
+          <t>Prep 10 min · Cook 15 min</t>
         </is>
       </c>
     </row>
@@ -2396,37 +2744,203 @@
       <c r="C22" s="46" t="n"/>
       <c r="D22" s="46" t="n"/>
     </row>
-    <row r="23" ht="36" customHeight="1">
+    <row r="23" ht="66" customHeight="1">
       <c r="A23" s="47" t="n">
         <v>1</v>
       </c>
       <c r="B23" s="48" t="inlineStr">
         <is>
-          <t>Temper, cover until soft, coconut and jaggery.</t>
+          <t>Mise en place. Weigh every ingredient on this card for 4 portions. Set Stainless steel kadhai or saucepan — never aluminium. Wash produce. Confirm spice blends have no onion or garlic powder. No onion, no garlic, no aluminium.</t>
         </is>
       </c>
       <c r="C23" s="49" t="n"/>
       <c r="D23" s="49" t="n"/>
     </row>
+    <row r="24" ht="36" customHeight="1">
+      <c r="A24" s="32" t="n">
+        <v>2</v>
+      </c>
+      <c r="B24" s="30" t="inlineStr">
+        <is>
+          <t>Cut vegetables to even size so they cook together.</t>
+        </is>
+      </c>
+      <c r="C24" s="31" t="n"/>
+      <c r="D24" s="31" t="n"/>
+    </row>
+    <row r="25" ht="54" customHeight="1">
+      <c r="A25" s="47" t="n">
+        <v>3</v>
+      </c>
+      <c r="B25" s="48" t="inlineStr">
+        <is>
+          <t>Heat fat in Stainless steel kadhai or saucepan — never aluminium on medium. Bloom hing 20–30 seconds until fragrant — this is the onion-garlic stand-in. Do not burn it.</t>
+        </is>
+      </c>
+      <c r="C25" s="49" t="n"/>
+      <c r="D25" s="49" t="n"/>
+    </row>
+    <row r="26" ht="54" customHeight="1">
+      <c r="A26" s="32" t="n">
+        <v>4</v>
+      </c>
+      <c r="B26" s="30" t="inlineStr">
+        <is>
+          <t>Temper, cover until soft, coconut and jaggery. Work in Stainless steel kadhai or saucepan — never aluminium. Cook to the doneness below, tasting salt at the end. Do not add onion, garlic or aluminium cookware.</t>
+        </is>
+      </c>
+      <c r="C26" s="31" t="n"/>
+      <c r="D26" s="31" t="n"/>
+    </row>
+    <row r="27" ht="42" customHeight="1">
+      <c r="A27" s="47" t="n">
+        <v>5</v>
+      </c>
+      <c r="B27" s="48" t="inlineStr">
+        <is>
+          <t>Doneness: vegetables yield to a knife, gravy coats a spoon, salt is balanced. Rest 2 minutes off the heat so seasoning settles.</t>
+        </is>
+      </c>
+      <c r="C27" s="49" t="n"/>
+      <c r="D27" s="49" t="n"/>
+    </row>
+    <row r="28" ht="42" customHeight="1">
+      <c r="A28" s="32" t="n">
+        <v>6</v>
+      </c>
+      <c r="B28" s="30" t="inlineStr">
+        <is>
+          <t>Taste and adjust salt, lemon or chilli only — do not add onion or garlic at the finish. Garnish as listed. Yield is 4 portions.</t>
+        </is>
+      </c>
+      <c r="C28" s="31" t="n"/>
+      <c r="D28" s="31" t="n"/>
+    </row>
+    <row r="29" ht="42" customHeight="1">
+      <c r="A29" s="47" t="n">
+        <v>7</v>
+      </c>
+      <c r="B29" s="48" t="inlineStr">
+        <is>
+          <t>Hold hot above 63 C if the pass is delayed, or cool quickly and reheat once only to piping hot. Do not hold in aluminium. Service: Hot.</t>
+        </is>
+      </c>
+      <c r="C29" s="49" t="n"/>
+      <c r="D29" s="49" t="n"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="21" t="inlineStr">
+        <is>
+          <t>Nutrition per portion</t>
+        </is>
+      </c>
+      <c r="B31" s="22" t="n"/>
+      <c r="C31" s="22" t="n"/>
+      <c r="D31" s="22" t="n"/>
+    </row>
+    <row r="32" ht="36" customHeight="1">
+      <c r="A32" s="12" t="inlineStr">
+        <is>
+          <t>kcal 131  ·  Protein 2 g  ·  Carbs 15 g  ·  Fat 8 g  ·  Fibre 3 g. Nutrition is a kitchen estimate from typical produce values, not a laboratory analysis.</t>
+        </is>
+      </c>
+      <c r="B32" s="50" t="n"/>
+      <c r="C32" s="50" t="n"/>
+      <c r="D32" s="50" t="n"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="24" t="inlineStr">
+        <is>
+          <t>Allergens</t>
+        </is>
+      </c>
+      <c r="B33" s="6" t="n"/>
+      <c r="C33" s="6" t="n"/>
+      <c r="D33" s="6" t="n"/>
+    </row>
+    <row r="34" ht="48" customHeight="1">
+      <c r="A34" s="25" t="inlineStr">
+        <is>
+          <t>Gluten (wheat) · Mustard · Always verify labels; this card is a kitchen estimate, not a lab certificate.</t>
+        </is>
+      </c>
+      <c r="B34" s="26" t="n"/>
+      <c r="C34" s="26" t="n"/>
+      <c r="D34" s="26" t="n"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="24" t="inlineStr">
+        <is>
+          <t>Chef notes</t>
+        </is>
+      </c>
+      <c r="B35" s="6" t="n"/>
+      <c r="C35" s="6" t="n"/>
+      <c r="D35" s="6" t="n"/>
+    </row>
+    <row r="36" ht="72" customHeight="1">
+      <c r="A36" s="25" t="inlineStr">
+        <is>
+          <t>For Pumpkin Bhaji: keep the mix slightly drier than you think; wet mixes split or go greasy. Bloom hing in hot fat 20–30 seconds; raw hing tastes medicinal. Commercial hing is often cut with wheat flour — use a gluten-free hing if you must mark Gluten Free. Never cook tomato, tamarind, lemon, yogurt or milk in aluminium; use stainless steel, iron, clay or glass. Spice blends: read the packet. Many garam masalas hide onion or garlic powder.</t>
+        </is>
+      </c>
+      <c r="B36" s="26" t="n"/>
+      <c r="C36" s="26" t="n"/>
+      <c r="D36" s="26" t="n"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="51" t="inlineStr">
+        <is>
+          <t>Service notes</t>
+        </is>
+      </c>
+      <c r="B37" s="52" t="n"/>
+      <c r="C37" s="52" t="n"/>
+      <c r="D37" s="52" t="n"/>
+    </row>
+    <row r="38" ht="64" customHeight="1">
+      <c r="A38" s="12" t="inlineStr">
+        <is>
+          <t>Serve family-style in a steel bowl. Keep a lid on at the pass so it does not skin. Service temperature: Hot. Allergen label for this dish: Gluten (wheat); Mustard; Always verify labels; this card is a kitchen estimate, not a lab certificate. State clearly: vegetarian, no onion, no garlic, no eggs, no meat, no fish. Nutrition on this card is an estimate for 1 portion of 4.</t>
+        </is>
+      </c>
+      <c r="B38" s="50" t="n"/>
+      <c r="C38" s="50" t="n"/>
+      <c r="D38" s="50" t="n"/>
+    </row>
   </sheetData>
-  <mergeCells count="17">
+  <mergeCells count="31">
+    <mergeCell ref="A8:D8"/>
+    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="B23:D23"/>
+    <mergeCell ref="A35:D35"/>
+    <mergeCell ref="A38:D38"/>
+    <mergeCell ref="C14:D14"/>
+    <mergeCell ref="B29:D29"/>
+    <mergeCell ref="B28:D28"/>
+    <mergeCell ref="A9:D9"/>
+    <mergeCell ref="A31:D31"/>
+    <mergeCell ref="C16:D16"/>
+    <mergeCell ref="A34:D34"/>
+    <mergeCell ref="A11:D11"/>
+    <mergeCell ref="B24:D24"/>
+    <mergeCell ref="A36:D36"/>
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="C12:D12"/>
-    <mergeCell ref="A9:D9"/>
-    <mergeCell ref="A8:D8"/>
-    <mergeCell ref="C16:D16"/>
-    <mergeCell ref="C15:D15"/>
-    <mergeCell ref="B23:D23"/>
+    <mergeCell ref="B26:D26"/>
+    <mergeCell ref="B25:D25"/>
+    <mergeCell ref="C17:D17"/>
+    <mergeCell ref="A37:D37"/>
     <mergeCell ref="B22:D22"/>
     <mergeCell ref="A3:D3"/>
     <mergeCell ref="C19:D19"/>
     <mergeCell ref="A21:D21"/>
-    <mergeCell ref="C14:D14"/>
+    <mergeCell ref="B27:D27"/>
     <mergeCell ref="C13:D13"/>
     <mergeCell ref="A2:D2"/>
-    <mergeCell ref="A11:D11"/>
-    <mergeCell ref="C17:D17"/>
     <mergeCell ref="C18:D18"/>
+    <mergeCell ref="A33:D33"/>
+    <mergeCell ref="A32:D32"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" paperSize="9" fitToHeight="1" fitToWidth="1"/>
@@ -2440,7 +2954,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:D21"/>
+  <dimension ref="A1:D35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -2452,7 +2966,7 @@
     <row r="1" ht="32" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>RECIPE CARD  ·  Sannas</t>
+          <t>Parslia Kitchen OS · RECIPE CARD · Sannas</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2462,7 +2976,7 @@
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>Goa kitchen  ·  Bread  ·  Goan Hindu vegetarian / sattvic</t>
+          <t>Pure Prasad · No onion · No garlic · No eggs · No meat · No fish  ·  Goa  ·  Bread</t>
         </is>
       </c>
       <c r="B2" s="4" t="n"/>
@@ -2482,44 +2996,44 @@
     <row r="5" ht="18" customHeight="1">
       <c r="A5" s="39" t="inlineStr">
         <is>
-          <t>Serves</t>
+          <t>YIELD</t>
         </is>
       </c>
       <c r="B5" s="39" t="inlineStr">
         <is>
-          <t>Prep</t>
+          <t>PORTION</t>
         </is>
       </c>
       <c r="C5" s="39" t="inlineStr">
         <is>
-          <t>Cook</t>
+          <t>SERVICE</t>
         </is>
       </c>
       <c r="D5" s="39" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>TIME</t>
         </is>
       </c>
     </row>
     <row r="6" ht="28" customHeight="1">
       <c r="A6" s="40" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>4 portions</t>
         </is>
       </c>
       <c r="B6" s="40" t="inlineStr">
         <is>
-          <t>70 min</t>
+          <t>1 portion</t>
         </is>
       </c>
       <c r="C6" s="40" t="inlineStr">
         <is>
-          <t>15 min</t>
+          <t>Hot</t>
         </is>
       </c>
       <c r="D6" s="40" t="inlineStr">
         <is>
-          <t>85 min</t>
+          <t>Prep 70 min · Cook 15 min</t>
         </is>
       </c>
     </row>
@@ -2685,35 +3199,188 @@
       <c r="C20" s="46" t="n"/>
       <c r="D20" s="46" t="n"/>
     </row>
-    <row r="21" ht="36" customHeight="1">
+    <row r="21" ht="66" customHeight="1">
       <c r="A21" s="47" t="n">
         <v>1</v>
       </c>
       <c r="B21" s="48" t="inlineStr">
         <is>
-          <t>Grind, ferment, steam 12 minutes in a steel idli stand.</t>
+          <t>Mise en place. Weigh every ingredient on this card for 4 portions. Set Stainless steel steamer and steel thali — never aluminium. Wash produce. Confirm spice blends have no onion or garlic powder. No onion, no garlic, no aluminium.</t>
         </is>
       </c>
       <c r="C21" s="49" t="n"/>
       <c r="D21" s="49" t="n"/>
     </row>
+    <row r="22" ht="42" customHeight="1">
+      <c r="A22" s="32" t="n">
+        <v>2</v>
+      </c>
+      <c r="B22" s="30" t="inlineStr">
+        <is>
+          <t>Cut vegetables to even size so they cook together. For dough, add water gradually; rest covered 10–15 minutes before rolling.</t>
+        </is>
+      </c>
+      <c r="C22" s="31" t="n"/>
+      <c r="D22" s="31" t="n"/>
+    </row>
+    <row r="23" ht="66" customHeight="1">
+      <c r="A23" s="47" t="n">
+        <v>3</v>
+      </c>
+      <c r="B23" s="48" t="inlineStr">
+        <is>
+          <t>Grind, ferment, steam 12 minutes in a steel idli stand. Work in Stainless steel steamer and steel thali — never aluminium. Cook to the doneness below, tasting salt at the end. Do not add onion, garlic or aluminium cookware.</t>
+        </is>
+      </c>
+      <c r="C23" s="49" t="n"/>
+      <c r="D23" s="49" t="n"/>
+    </row>
+    <row r="24" ht="42" customHeight="1">
+      <c r="A24" s="32" t="n">
+        <v>4</v>
+      </c>
+      <c r="B24" s="30" t="inlineStr">
+        <is>
+          <t>Doneness: bread is cooked through, no wet dough in the centre, light brown spots on the face.</t>
+        </is>
+      </c>
+      <c r="C24" s="31" t="n"/>
+      <c r="D24" s="31" t="n"/>
+    </row>
+    <row r="25" ht="42" customHeight="1">
+      <c r="A25" s="47" t="n">
+        <v>5</v>
+      </c>
+      <c r="B25" s="48" t="inlineStr">
+        <is>
+          <t>Taste and adjust salt, lemon or chilli only — do not add onion or garlic at the finish. Garnish as listed. Yield is 4 portions.</t>
+        </is>
+      </c>
+      <c r="C25" s="49" t="n"/>
+      <c r="D25" s="49" t="n"/>
+    </row>
+    <row r="26" ht="42" customHeight="1">
+      <c r="A26" s="32" t="n">
+        <v>6</v>
+      </c>
+      <c r="B26" s="30" t="inlineStr">
+        <is>
+          <t>Hold wrapped in a clean cloth in a covered steel box up to 30 minutes. Refresh on a hot tawa 20 seconds if needed. Service: Hot.</t>
+        </is>
+      </c>
+      <c r="C26" s="31" t="n"/>
+      <c r="D26" s="31" t="n"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="21" t="inlineStr">
+        <is>
+          <t>Nutrition per portion</t>
+        </is>
+      </c>
+      <c r="B28" s="22" t="n"/>
+      <c r="C28" s="22" t="n"/>
+      <c r="D28" s="22" t="n"/>
+    </row>
+    <row r="29" ht="36" customHeight="1">
+      <c r="A29" s="12" t="inlineStr">
+        <is>
+          <t>kcal 506  ·  Protein 7 g  ·  Carbs 103 g  ·  Fat 7 g  ·  Fibre 3 g. Nutrition is a kitchen estimate from typical produce values, not a laboratory analysis.</t>
+        </is>
+      </c>
+      <c r="B29" s="50" t="n"/>
+      <c r="C29" s="50" t="n"/>
+      <c r="D29" s="50" t="n"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="24" t="inlineStr">
+        <is>
+          <t>Allergens</t>
+        </is>
+      </c>
+      <c r="B30" s="6" t="n"/>
+      <c r="C30" s="6" t="n"/>
+      <c r="D30" s="6" t="n"/>
+    </row>
+    <row r="31" ht="48" customHeight="1">
+      <c r="A31" s="25" t="inlineStr">
+        <is>
+          <t>Gluten (wheat) · Always verify labels; this card is a kitchen estimate, not a lab certificate.</t>
+        </is>
+      </c>
+      <c r="B31" s="26" t="n"/>
+      <c r="C31" s="26" t="n"/>
+      <c r="D31" s="26" t="n"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="24" t="inlineStr">
+        <is>
+          <t>Chef notes</t>
+        </is>
+      </c>
+      <c r="B32" s="6" t="n"/>
+      <c r="C32" s="6" t="n"/>
+      <c r="D32" s="6" t="n"/>
+    </row>
+    <row r="33" ht="72" customHeight="1">
+      <c r="A33" s="25" t="inlineStr">
+        <is>
+          <t>For Sannas: keep the mix slightly drier than you think; wet mixes split or go greasy. Bloom hing in hot fat 20–30 seconds; raw hing tastes medicinal. Commercial hing is often cut with wheat flour — use a gluten-free hing if you must mark Gluten Free. Never cook tomato, tamarind, lemon, yogurt or milk in aluminium; use stainless steel, iron, clay or glass. Spice blends: read the packet. Many garam masalas hide onion or garlic powder.</t>
+        </is>
+      </c>
+      <c r="B33" s="26" t="n"/>
+      <c r="C33" s="26" t="n"/>
+      <c r="D33" s="26" t="n"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="51" t="inlineStr">
+        <is>
+          <t>Service notes</t>
+        </is>
+      </c>
+      <c r="B34" s="52" t="n"/>
+      <c r="C34" s="52" t="n"/>
+      <c r="D34" s="52" t="n"/>
+    </row>
+    <row r="35" ht="64" customHeight="1">
+      <c r="A35" s="12" t="inlineStr">
+        <is>
+          <t>Send to table wrapped. Do not stack in plastic or they sweat. Service temperature: Hot. Allergen label for this dish: Gluten (wheat); Always verify labels; this card is a kitchen estimate, not a lab certificate. State clearly: vegetarian, no onion, no garlic, no eggs, no meat, no fish. Nutrition on this card is an estimate for 1 portion of 4.</t>
+        </is>
+      </c>
+      <c r="B35" s="50" t="n"/>
+      <c r="C35" s="50" t="n"/>
+      <c r="D35" s="50" t="n"/>
+    </row>
   </sheetData>
-  <mergeCells count="15">
+  <mergeCells count="28">
+    <mergeCell ref="A8:D8"/>
+    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="B23:D23"/>
+    <mergeCell ref="A35:D35"/>
+    <mergeCell ref="A29:D29"/>
+    <mergeCell ref="C14:D14"/>
+    <mergeCell ref="A19:D19"/>
+    <mergeCell ref="A28:D28"/>
+    <mergeCell ref="A9:D9"/>
+    <mergeCell ref="A31:D31"/>
+    <mergeCell ref="C16:D16"/>
+    <mergeCell ref="A34:D34"/>
+    <mergeCell ref="A30:D30"/>
+    <mergeCell ref="A11:D11"/>
+    <mergeCell ref="B24:D24"/>
+    <mergeCell ref="B20:D20"/>
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="C12:D12"/>
-    <mergeCell ref="A9:D9"/>
-    <mergeCell ref="A8:D8"/>
-    <mergeCell ref="C16:D16"/>
-    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="B26:D26"/>
+    <mergeCell ref="B25:D25"/>
+    <mergeCell ref="C17:D17"/>
+    <mergeCell ref="B22:D22"/>
     <mergeCell ref="A3:D3"/>
-    <mergeCell ref="C14:D14"/>
     <mergeCell ref="C13:D13"/>
     <mergeCell ref="A2:D2"/>
-    <mergeCell ref="A11:D11"/>
-    <mergeCell ref="A19:D19"/>
     <mergeCell ref="B21:D21"/>
-    <mergeCell ref="C17:D17"/>
-    <mergeCell ref="B20:D20"/>
+    <mergeCell ref="A33:D33"/>
+    <mergeCell ref="A32:D32"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" paperSize="9" fitToHeight="1" fitToWidth="1"/>
@@ -2727,7 +3394,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:D19"/>
+  <dimension ref="A1:D35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -2739,7 +3406,7 @@
     <row r="1" ht="32" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>RECIPE CARD  ·  Pole</t>
+          <t>Parslia Kitchen OS · RECIPE CARD · Pole</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2749,7 +3416,7 @@
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>Goa kitchen  ·  Bread  ·  Goan Hindu vegetarian / sattvic</t>
+          <t>Pure Prasad · No onion · No garlic · No eggs · No meat · No fish  ·  Goa  ·  Bread</t>
         </is>
       </c>
       <c r="B2" s="4" t="n"/>
@@ -2769,44 +3436,44 @@
     <row r="5" ht="18" customHeight="1">
       <c r="A5" s="39" t="inlineStr">
         <is>
-          <t>Serves</t>
+          <t>YIELD</t>
         </is>
       </c>
       <c r="B5" s="39" t="inlineStr">
         <is>
-          <t>Prep</t>
+          <t>PORTION</t>
         </is>
       </c>
       <c r="C5" s="39" t="inlineStr">
         <is>
-          <t>Cook</t>
+          <t>SERVICE</t>
         </is>
       </c>
       <c r="D5" s="39" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>TIME</t>
         </is>
       </c>
     </row>
     <row r="6" ht="28" customHeight="1">
       <c r="A6" s="40" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>4 portions</t>
         </is>
       </c>
       <c r="B6" s="40" t="inlineStr">
         <is>
-          <t>20 min</t>
+          <t>1 portion</t>
         </is>
       </c>
       <c r="C6" s="40" t="inlineStr">
         <is>
-          <t>15 min</t>
+          <t>Hot</t>
         </is>
       </c>
       <c r="D6" s="40" t="inlineStr">
         <is>
-          <t>35 min</t>
+          <t>Prep 20 min · Cook 15 min</t>
         </is>
       </c>
     </row>
@@ -2936,33 +3603,212 @@
       <c r="C18" s="46" t="n"/>
       <c r="D18" s="46" t="n"/>
     </row>
-    <row r="19" ht="42" customHeight="1">
+    <row r="19" ht="54" customHeight="1">
       <c r="A19" s="47" t="n">
         <v>1</v>
       </c>
       <c r="B19" s="48" t="inlineStr">
         <is>
-          <t>Grind thin. Pour on iron tawa. Do not flip hard — it should stay soft.</t>
+          <t>Mise en place. Weigh every ingredient on this card for 4 portions. Set Cast-iron tawa (not aluminium). Wash produce. Confirm spice blends have no onion or garlic powder. No onion, no garlic, no aluminium.</t>
         </is>
       </c>
       <c r="C19" s="49" t="n"/>
       <c r="D19" s="49" t="n"/>
     </row>
+    <row r="20" ht="42" customHeight="1">
+      <c r="A20" s="32" t="n">
+        <v>2</v>
+      </c>
+      <c r="B20" s="30" t="inlineStr">
+        <is>
+          <t>Cut vegetables to even size so they cook together. For dough, add water gradually; rest covered 10–15 minutes before rolling.</t>
+        </is>
+      </c>
+      <c r="C20" s="31" t="n"/>
+      <c r="D20" s="31" t="n"/>
+    </row>
+    <row r="21" ht="54" customHeight="1">
+      <c r="A21" s="47" t="n">
+        <v>3</v>
+      </c>
+      <c r="B21" s="48" t="inlineStr">
+        <is>
+          <t>Grind thin. Work in Cast-iron tawa (not aluminium). Cook to the doneness below, tasting salt at the end. Do not add onion, garlic or aluminium cookware.</t>
+        </is>
+      </c>
+      <c r="C21" s="49" t="n"/>
+      <c r="D21" s="49" t="n"/>
+    </row>
+    <row r="22" ht="54" customHeight="1">
+      <c r="A22" s="32" t="n">
+        <v>4</v>
+      </c>
+      <c r="B22" s="30" t="inlineStr">
+        <is>
+          <t>Pour on iron tawa. Work in Cast-iron tawa (not aluminium). Cook to the doneness below, tasting salt at the end. Do not add onion, garlic or aluminium cookware.</t>
+        </is>
+      </c>
+      <c r="C22" s="31" t="n"/>
+      <c r="D22" s="31" t="n"/>
+    </row>
+    <row r="23" ht="54" customHeight="1">
+      <c r="A23" s="47" t="n">
+        <v>5</v>
+      </c>
+      <c r="B23" s="48" t="inlineStr">
+        <is>
+          <t>Do not flip hard — it should stay soft. Work in Cast-iron tawa (not aluminium). Cook to the doneness below, tasting salt at the end. Do not add onion, garlic or aluminium cookware.</t>
+        </is>
+      </c>
+      <c r="C23" s="49" t="n"/>
+      <c r="D23" s="49" t="n"/>
+    </row>
+    <row r="24" ht="42" customHeight="1">
+      <c r="A24" s="32" t="n">
+        <v>6</v>
+      </c>
+      <c r="B24" s="30" t="inlineStr">
+        <is>
+          <t>Doneness: bread is cooked through, no wet dough in the centre, light brown spots on the face.</t>
+        </is>
+      </c>
+      <c r="C24" s="31" t="n"/>
+      <c r="D24" s="31" t="n"/>
+    </row>
+    <row r="25" ht="42" customHeight="1">
+      <c r="A25" s="47" t="n">
+        <v>7</v>
+      </c>
+      <c r="B25" s="48" t="inlineStr">
+        <is>
+          <t>Taste and adjust salt, lemon or chilli only — do not add onion or garlic at the finish. Garnish as listed. Yield is 4 portions.</t>
+        </is>
+      </c>
+      <c r="C25" s="49" t="n"/>
+      <c r="D25" s="49" t="n"/>
+    </row>
+    <row r="26" ht="42" customHeight="1">
+      <c r="A26" s="32" t="n">
+        <v>8</v>
+      </c>
+      <c r="B26" s="30" t="inlineStr">
+        <is>
+          <t>Hold wrapped in a clean cloth in a covered steel box up to 30 minutes. Refresh on a hot tawa 20 seconds if needed. Service: Hot.</t>
+        </is>
+      </c>
+      <c r="C26" s="31" t="n"/>
+      <c r="D26" s="31" t="n"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="21" t="inlineStr">
+        <is>
+          <t>Nutrition per portion</t>
+        </is>
+      </c>
+      <c r="B28" s="22" t="n"/>
+      <c r="C28" s="22" t="n"/>
+      <c r="D28" s="22" t="n"/>
+    </row>
+    <row r="29" ht="36" customHeight="1">
+      <c r="A29" s="12" t="inlineStr">
+        <is>
+          <t>kcal 185  ·  Protein 3 g  ·  Carbs 38 g  ·  Fat 2 g  ·  Fibre 1 g. Nutrition is a kitchen estimate from typical produce values, not a laboratory analysis.</t>
+        </is>
+      </c>
+      <c r="B29" s="50" t="n"/>
+      <c r="C29" s="50" t="n"/>
+      <c r="D29" s="50" t="n"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="24" t="inlineStr">
+        <is>
+          <t>Allergens</t>
+        </is>
+      </c>
+      <c r="B30" s="6" t="n"/>
+      <c r="C30" s="6" t="n"/>
+      <c r="D30" s="6" t="n"/>
+    </row>
+    <row r="31" ht="48" customHeight="1">
+      <c r="A31" s="25" t="inlineStr">
+        <is>
+          <t>Gluten (wheat) · Always verify labels; this card is a kitchen estimate, not a lab certificate.</t>
+        </is>
+      </c>
+      <c r="B31" s="26" t="n"/>
+      <c r="C31" s="26" t="n"/>
+      <c r="D31" s="26" t="n"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="24" t="inlineStr">
+        <is>
+          <t>Chef notes</t>
+        </is>
+      </c>
+      <c r="B32" s="6" t="n"/>
+      <c r="C32" s="6" t="n"/>
+      <c r="D32" s="6" t="n"/>
+    </row>
+    <row r="33" ht="72" customHeight="1">
+      <c r="A33" s="25" t="inlineStr">
+        <is>
+          <t>For Pole: keep the mix slightly drier than you think; wet mixes split or go greasy. Bloom hing in hot fat 20–30 seconds; raw hing tastes medicinal. Commercial hing is often cut with wheat flour — use a gluten-free hing if you must mark Gluten Free. Never cook tomato, tamarind, lemon, yogurt or milk in aluminium; use stainless steel, iron, clay or glass. Spice blends: read the packet. Many garam masalas hide onion or garlic powder.</t>
+        </is>
+      </c>
+      <c r="B33" s="26" t="n"/>
+      <c r="C33" s="26" t="n"/>
+      <c r="D33" s="26" t="n"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="51" t="inlineStr">
+        <is>
+          <t>Service notes</t>
+        </is>
+      </c>
+      <c r="B34" s="52" t="n"/>
+      <c r="C34" s="52" t="n"/>
+      <c r="D34" s="52" t="n"/>
+    </row>
+    <row r="35" ht="64" customHeight="1">
+      <c r="A35" s="12" t="inlineStr">
+        <is>
+          <t>Send to table wrapped. Do not stack in plastic or they sweat. Service temperature: Hot. Allergen label for this dish: Gluten (wheat); Always verify labels; this card is a kitchen estimate, not a lab certificate. State clearly: vegetarian, no onion, no garlic, no eggs, no meat, no fish. Nutrition on this card is an estimate for 1 portion of 4.</t>
+        </is>
+      </c>
+      <c r="B35" s="50" t="n"/>
+      <c r="C35" s="50" t="n"/>
+      <c r="D35" s="50" t="n"/>
+    </row>
   </sheetData>
-  <mergeCells count="13">
+  <mergeCells count="28">
+    <mergeCell ref="A17:D17"/>
+    <mergeCell ref="A8:D8"/>
+    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="B23:D23"/>
+    <mergeCell ref="A35:D35"/>
+    <mergeCell ref="A29:D29"/>
+    <mergeCell ref="C14:D14"/>
+    <mergeCell ref="A28:D28"/>
+    <mergeCell ref="A9:D9"/>
+    <mergeCell ref="B19:D19"/>
+    <mergeCell ref="A31:D31"/>
+    <mergeCell ref="A34:D34"/>
+    <mergeCell ref="A30:D30"/>
+    <mergeCell ref="A11:D11"/>
+    <mergeCell ref="B24:D24"/>
+    <mergeCell ref="B20:D20"/>
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="C12:D12"/>
-    <mergeCell ref="A9:D9"/>
-    <mergeCell ref="A17:D17"/>
-    <mergeCell ref="A8:D8"/>
-    <mergeCell ref="B19:D19"/>
-    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="B26:D26"/>
+    <mergeCell ref="B25:D25"/>
+    <mergeCell ref="B22:D22"/>
     <mergeCell ref="A3:D3"/>
     <mergeCell ref="B18:D18"/>
-    <mergeCell ref="C14:D14"/>
     <mergeCell ref="C13:D13"/>
     <mergeCell ref="A2:D2"/>
-    <mergeCell ref="A11:D11"/>
+    <mergeCell ref="B21:D21"/>
+    <mergeCell ref="A33:D33"/>
+    <mergeCell ref="A32:D32"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" paperSize="9" fitToHeight="1" fitToWidth="1"/>
@@ -2976,7 +3822,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:D23"/>
+  <dimension ref="A1:D34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -2988,7 +3834,7 @@
     <row r="1" ht="32" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>RECIPE CARD  ·  Soft Wheat Roti</t>
+          <t>Parslia Kitchen OS · RECIPE CARD · Soft Wheat Roti</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2998,7 +3844,7 @@
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>Goa kitchen  ·  Bread  ·  Goan Hindu vegetarian / sattvic</t>
+          <t>Pure Prasad · No onion · No garlic · No eggs · No meat · No fish  ·  Goa  ·  Bread</t>
         </is>
       </c>
       <c r="B2" s="4" t="n"/>
@@ -3018,44 +3864,44 @@
     <row r="5" ht="18" customHeight="1">
       <c r="A5" s="39" t="inlineStr">
         <is>
-          <t>Serves</t>
+          <t>YIELD</t>
         </is>
       </c>
       <c r="B5" s="39" t="inlineStr">
         <is>
-          <t>Prep</t>
+          <t>PORTION</t>
         </is>
       </c>
       <c r="C5" s="39" t="inlineStr">
         <is>
-          <t>Cook</t>
+          <t>SERVICE</t>
         </is>
       </c>
       <c r="D5" s="39" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>TIME</t>
         </is>
       </c>
     </row>
     <row r="6" ht="28" customHeight="1">
       <c r="A6" s="40" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>4 portions</t>
         </is>
       </c>
       <c r="B6" s="40" t="inlineStr">
         <is>
-          <t>15 min</t>
+          <t>1 portion</t>
         </is>
       </c>
       <c r="C6" s="40" t="inlineStr">
         <is>
-          <t>15 min</t>
+          <t>Hot</t>
         </is>
       </c>
       <c r="D6" s="40" t="inlineStr">
         <is>
-          <t>30 min</t>
+          <t>Prep 15 min · Cook 15 min</t>
         </is>
       </c>
     </row>
@@ -3203,56 +4049,187 @@
       <c r="C19" s="46" t="n"/>
       <c r="D19" s="46" t="n"/>
     </row>
-    <row r="20" ht="36" customHeight="1">
+    <row r="20" ht="54" customHeight="1">
       <c r="A20" s="47" t="n">
         <v>1</v>
       </c>
       <c r="B20" s="48" t="inlineStr">
         <is>
-          <t>Roll and cook on iron tawa.</t>
+          <t>Mise en place. Weigh every ingredient on this card for 4 portions. Set Cast-iron tawa (not aluminium). Wash produce. Confirm spice blends have no onion or garlic powder. No onion, no garlic, no aluminium.</t>
         </is>
       </c>
       <c r="C20" s="49" t="n"/>
       <c r="D20" s="49" t="n"/>
     </row>
-    <row r="22">
-      <c r="A22" s="24" t="inlineStr">
+    <row r="21" ht="42" customHeight="1">
+      <c r="A21" s="32" t="n">
+        <v>2</v>
+      </c>
+      <c r="B21" s="30" t="inlineStr">
+        <is>
+          <t>Cut vegetables to even size so they cook together. For dough, add water gradually; rest covered 10–15 minutes before rolling.</t>
+        </is>
+      </c>
+      <c r="C21" s="31" t="n"/>
+      <c r="D21" s="31" t="n"/>
+    </row>
+    <row r="22" ht="54" customHeight="1">
+      <c r="A22" s="47" t="n">
+        <v>3</v>
+      </c>
+      <c r="B22" s="48" t="inlineStr">
+        <is>
+          <t>Roll and cook on iron tawa. Work in Cast-iron tawa (not aluminium). Cook to the doneness below, tasting salt at the end. Do not add onion, garlic or aluminium cookware.</t>
+        </is>
+      </c>
+      <c r="C22" s="49" t="n"/>
+      <c r="D22" s="49" t="n"/>
+    </row>
+    <row r="23" ht="42" customHeight="1">
+      <c r="A23" s="32" t="n">
+        <v>4</v>
+      </c>
+      <c r="B23" s="30" t="inlineStr">
+        <is>
+          <t>Doneness: bread is cooked through, no wet dough in the centre, light brown spots on the face.</t>
+        </is>
+      </c>
+      <c r="C23" s="31" t="n"/>
+      <c r="D23" s="31" t="n"/>
+    </row>
+    <row r="24" ht="42" customHeight="1">
+      <c r="A24" s="47" t="n">
+        <v>5</v>
+      </c>
+      <c r="B24" s="48" t="inlineStr">
+        <is>
+          <t>Taste and adjust salt, lemon or chilli only — do not add onion or garlic at the finish. Garnish as listed. Yield is 4 portions.</t>
+        </is>
+      </c>
+      <c r="C24" s="49" t="n"/>
+      <c r="D24" s="49" t="n"/>
+    </row>
+    <row r="25" ht="42" customHeight="1">
+      <c r="A25" s="32" t="n">
+        <v>6</v>
+      </c>
+      <c r="B25" s="30" t="inlineStr">
+        <is>
+          <t>Hold wrapped in a clean cloth in a covered steel box up to 30 minutes. Refresh on a hot tawa 20 seconds if needed. Service: Hot.</t>
+        </is>
+      </c>
+      <c r="C25" s="31" t="n"/>
+      <c r="D25" s="31" t="n"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="21" t="inlineStr">
+        <is>
+          <t>Nutrition per portion</t>
+        </is>
+      </c>
+      <c r="B27" s="22" t="n"/>
+      <c r="C27" s="22" t="n"/>
+      <c r="D27" s="22" t="n"/>
+    </row>
+    <row r="28" ht="36" customHeight="1">
+      <c r="A28" s="12" t="inlineStr">
+        <is>
+          <t>kcal 267  ·  Protein 7 g  ·  Carbs 43 g  ·  Fat 8 g  ·  Fibre 7 g. Nutrition is a kitchen estimate from typical produce values, not a laboratory analysis.</t>
+        </is>
+      </c>
+      <c r="B28" s="50" t="n"/>
+      <c r="C28" s="50" t="n"/>
+      <c r="D28" s="50" t="n"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="24" t="inlineStr">
+        <is>
+          <t>Allergens</t>
+        </is>
+      </c>
+      <c r="B29" s="6" t="n"/>
+      <c r="C29" s="6" t="n"/>
+      <c r="D29" s="6" t="n"/>
+    </row>
+    <row r="30" ht="48" customHeight="1">
+      <c r="A30" s="25" t="inlineStr">
+        <is>
+          <t>Gluten (wheat) · Milk · Always verify labels; this card is a kitchen estimate, not a lab certificate.</t>
+        </is>
+      </c>
+      <c r="B30" s="26" t="n"/>
+      <c r="C30" s="26" t="n"/>
+      <c r="D30" s="26" t="n"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="24" t="inlineStr">
         <is>
           <t>Chef notes</t>
         </is>
       </c>
-      <c r="B22" s="6" t="n"/>
-      <c r="C22" s="6" t="n"/>
-      <c r="D22" s="6" t="n"/>
-    </row>
-    <row r="23" ht="48" customHeight="1">
-      <c r="A23" s="25" t="inlineStr">
-        <is>
-          <t>Everyday bread with caldin.</t>
-        </is>
-      </c>
-      <c r="B23" s="26" t="n"/>
-      <c r="C23" s="26" t="n"/>
-      <c r="D23" s="26" t="n"/>
+      <c r="B31" s="6" t="n"/>
+      <c r="C31" s="6" t="n"/>
+      <c r="D31" s="6" t="n"/>
+    </row>
+    <row r="32" ht="72" customHeight="1">
+      <c r="A32" s="25" t="inlineStr">
+        <is>
+          <t>For Soft Wheat Roti: keep the mix slightly drier than you think; wet mixes split or go greasy. Bloom hing in hot fat 20–30 seconds; raw hing tastes medicinal. Commercial hing is often cut with wheat flour — use a gluten-free hing if you must mark Gluten Free. Never cook tomato, tamarind, lemon, yogurt or milk in aluminium; use stainless steel, iron, clay or glass. Spice blends: read the packet. Many garam masalas hide onion or garlic powder.</t>
+        </is>
+      </c>
+      <c r="B32" s="26" t="n"/>
+      <c r="C32" s="26" t="n"/>
+      <c r="D32" s="26" t="n"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="51" t="inlineStr">
+        <is>
+          <t>Service notes</t>
+        </is>
+      </c>
+      <c r="B33" s="52" t="n"/>
+      <c r="C33" s="52" t="n"/>
+      <c r="D33" s="52" t="n"/>
+    </row>
+    <row r="34" ht="64" customHeight="1">
+      <c r="A34" s="12" t="inlineStr">
+        <is>
+          <t>Send to table wrapped. Do not stack in plastic or they sweat. Service temperature: Hot. Allergen label for this dish: Gluten (wheat); Milk; Always verify labels; this card is a kitchen estimate, not a lab certificate. State clearly: vegetarian, no onion, no garlic, no eggs, no meat, no fish. Nutrition on this card is an estimate for 1 portion of 4.</t>
+        </is>
+      </c>
+      <c r="B34" s="50" t="n"/>
+      <c r="C34" s="50" t="n"/>
+      <c r="D34" s="50" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="16">
+  <mergeCells count="27">
+    <mergeCell ref="A8:D8"/>
+    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="B23:D23"/>
+    <mergeCell ref="A29:D29"/>
+    <mergeCell ref="C14:D14"/>
+    <mergeCell ref="A28:D28"/>
+    <mergeCell ref="A9:D9"/>
+    <mergeCell ref="B19:D19"/>
+    <mergeCell ref="A31:D31"/>
+    <mergeCell ref="C16:D16"/>
+    <mergeCell ref="A34:D34"/>
+    <mergeCell ref="A30:D30"/>
+    <mergeCell ref="A11:D11"/>
+    <mergeCell ref="B24:D24"/>
+    <mergeCell ref="B20:D20"/>
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="C12:D12"/>
-    <mergeCell ref="A9:D9"/>
+    <mergeCell ref="B25:D25"/>
     <mergeCell ref="A18:D18"/>
-    <mergeCell ref="A8:D8"/>
-    <mergeCell ref="B19:D19"/>
-    <mergeCell ref="C16:D16"/>
-    <mergeCell ref="A22:D22"/>
-    <mergeCell ref="C15:D15"/>
-    <mergeCell ref="A23:D23"/>
+    <mergeCell ref="A27:D27"/>
+    <mergeCell ref="B22:D22"/>
     <mergeCell ref="A3:D3"/>
-    <mergeCell ref="C14:D14"/>
     <mergeCell ref="C13:D13"/>
     <mergeCell ref="A2:D2"/>
-    <mergeCell ref="A11:D11"/>
-    <mergeCell ref="B20:D20"/>
+    <mergeCell ref="B21:D21"/>
+    <mergeCell ref="A33:D33"/>
+    <mergeCell ref="A32:D32"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" paperSize="9" fitToHeight="1" fitToWidth="1"/>
@@ -3266,7 +4243,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:D21"/>
+  <dimension ref="A1:D35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -3278,7 +4255,7 @@
     <row r="1" ht="32" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>RECIPE CARD  ·  Bebinca Slab</t>
+          <t>Parslia Kitchen OS · RECIPE CARD · Bebinca Slab</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3288,7 +4265,7 @@
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>Goa kitchen  ·  Sweet  ·  Goan Hindu vegetarian / sattvic</t>
+          <t>Pure Prasad · No onion · No garlic · No eggs · No meat · No fish  ·  Goa  ·  Sweet</t>
         </is>
       </c>
       <c r="B2" s="4" t="n"/>
@@ -3308,44 +4285,44 @@
     <row r="5" ht="18" customHeight="1">
       <c r="A5" s="39" t="inlineStr">
         <is>
-          <t>Serves</t>
+          <t>YIELD</t>
         </is>
       </c>
       <c r="B5" s="39" t="inlineStr">
         <is>
-          <t>Prep</t>
+          <t>PORTION</t>
         </is>
       </c>
       <c r="C5" s="39" t="inlineStr">
         <is>
-          <t>Cook</t>
+          <t>SERVICE</t>
         </is>
       </c>
       <c r="D5" s="39" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>TIME</t>
         </is>
       </c>
     </row>
     <row r="6" ht="28" customHeight="1">
       <c r="A6" s="40" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>4 portions</t>
         </is>
       </c>
       <c r="B6" s="40" t="inlineStr">
         <is>
-          <t>20 min</t>
+          <t>1 portion</t>
         </is>
       </c>
       <c r="C6" s="40" t="inlineStr">
         <is>
-          <t>50 min</t>
+          <t>Hot</t>
         </is>
       </c>
       <c r="D6" s="40" t="inlineStr">
         <is>
-          <t>70 min</t>
+          <t>Prep 20 min · Cook 50 min</t>
         </is>
       </c>
     </row>
@@ -3511,35 +4488,188 @@
       <c r="C20" s="46" t="n"/>
       <c r="D20" s="46" t="n"/>
     </row>
-    <row r="21" ht="36" customHeight="1">
+    <row r="21" ht="66" customHeight="1">
       <c r="A21" s="47" t="n">
         <v>1</v>
       </c>
       <c r="B21" s="48" t="inlineStr">
         <is>
-          <t>Bake thin ghee-brushed layers in steel until 6–8 layers set.</t>
+          <t>Mise en place. Weigh every ingredient on this card for 4 portions. Set Steel or enamel baking dish — never aluminium. Wash produce. Confirm spice blends have no onion or garlic powder. No onion, no garlic, no aluminium.</t>
         </is>
       </c>
       <c r="C21" s="49" t="n"/>
       <c r="D21" s="49" t="n"/>
     </row>
+    <row r="22" ht="42" customHeight="1">
+      <c r="A22" s="32" t="n">
+        <v>2</v>
+      </c>
+      <c r="B22" s="30" t="inlineStr">
+        <is>
+          <t>Cut vegetables to even size so they cook together. Use a heavy stainless steel milk pot. Acidic or milk dishes must never touch aluminium.</t>
+        </is>
+      </c>
+      <c r="C22" s="31" t="n"/>
+      <c r="D22" s="31" t="n"/>
+    </row>
+    <row r="23" ht="66" customHeight="1">
+      <c r="A23" s="47" t="n">
+        <v>3</v>
+      </c>
+      <c r="B23" s="48" t="inlineStr">
+        <is>
+          <t>Bake thin ghee-brushed layers in steel until 6–8 layers set. Work in Steel or enamel baking dish — never aluminium. Cook to the doneness below, tasting salt at the end. Do not add onion, garlic or aluminium cookware.</t>
+        </is>
+      </c>
+      <c r="C23" s="49" t="n"/>
+      <c r="D23" s="49" t="n"/>
+    </row>
+    <row r="24" ht="42" customHeight="1">
+      <c r="A24" s="32" t="n">
+        <v>4</v>
+      </c>
+      <c r="B24" s="30" t="inlineStr">
+        <is>
+          <t>Doneness: mixture leaves the sides of the pan, or milk is thick enough to coat a spoon, or syrup has taken the stated string.</t>
+        </is>
+      </c>
+      <c r="C24" s="31" t="n"/>
+      <c r="D24" s="31" t="n"/>
+    </row>
+    <row r="25" ht="42" customHeight="1">
+      <c r="A25" s="47" t="n">
+        <v>5</v>
+      </c>
+      <c r="B25" s="48" t="inlineStr">
+        <is>
+          <t>Taste and adjust salt, lemon or chilli only — do not add onion or garlic at the finish. Garnish as listed. Yield is 4 portions.</t>
+        </is>
+      </c>
+      <c r="C25" s="49" t="n"/>
+      <c r="D25" s="49" t="n"/>
+    </row>
+    <row r="26" ht="42" customHeight="1">
+      <c r="A26" s="32" t="n">
+        <v>6</v>
+      </c>
+      <c r="B26" s="30" t="inlineStr">
+        <is>
+          <t>Hold as the dish is eaten — hot sweets in a bain of hot water, chilled sweets in the fridge. Label date and time. Service: Hot.</t>
+        </is>
+      </c>
+      <c r="C26" s="31" t="n"/>
+      <c r="D26" s="31" t="n"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="21" t="inlineStr">
+        <is>
+          <t>Nutrition per portion</t>
+        </is>
+      </c>
+      <c r="B28" s="22" t="n"/>
+      <c r="C28" s="22" t="n"/>
+      <c r="D28" s="22" t="n"/>
+    </row>
+    <row r="29" ht="36" customHeight="1">
+      <c r="A29" s="12" t="inlineStr">
+        <is>
+          <t>kcal 740  ·  Protein 9 g  ·  Carbs 87 g  ·  Fat 41 g  ·  Fibre 11 g. Nutrition is a kitchen estimate from typical produce values, not a laboratory analysis.</t>
+        </is>
+      </c>
+      <c r="B29" s="50" t="n"/>
+      <c r="C29" s="50" t="n"/>
+      <c r="D29" s="50" t="n"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="24" t="inlineStr">
+        <is>
+          <t>Allergens</t>
+        </is>
+      </c>
+      <c r="B30" s="6" t="n"/>
+      <c r="C30" s="6" t="n"/>
+      <c r="D30" s="6" t="n"/>
+    </row>
+    <row r="31" ht="48" customHeight="1">
+      <c r="A31" s="25" t="inlineStr">
+        <is>
+          <t>Gluten (wheat) · Milk · Always verify labels; this card is a kitchen estimate, not a lab certificate.</t>
+        </is>
+      </c>
+      <c r="B31" s="26" t="n"/>
+      <c r="C31" s="26" t="n"/>
+      <c r="D31" s="26" t="n"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="24" t="inlineStr">
+        <is>
+          <t>Chef notes</t>
+        </is>
+      </c>
+      <c r="B32" s="6" t="n"/>
+      <c r="C32" s="6" t="n"/>
+      <c r="D32" s="6" t="n"/>
+    </row>
+    <row r="33" ht="72" customHeight="1">
+      <c r="A33" s="25" t="inlineStr">
+        <is>
+          <t>For Bebinca Slab: keep the mix slightly drier than you think; wet mixes split or go greasy. Bloom hing in hot fat 20–30 seconds; raw hing tastes medicinal. Commercial hing is often cut with wheat flour — use a gluten-free hing if you must mark Gluten Free. Never cook tomato, tamarind, lemon, yogurt or milk in aluminium; use stainless steel, iron, clay or glass. Spice blends: read the packet. Many garam masalas hide onion or garlic powder.</t>
+        </is>
+      </c>
+      <c r="B33" s="26" t="n"/>
+      <c r="C33" s="26" t="n"/>
+      <c r="D33" s="26" t="n"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="51" t="inlineStr">
+        <is>
+          <t>Service notes</t>
+        </is>
+      </c>
+      <c r="B34" s="52" t="n"/>
+      <c r="C34" s="52" t="n"/>
+      <c r="D34" s="52" t="n"/>
+    </row>
+    <row r="35" ht="64" customHeight="1">
+      <c r="A35" s="12" t="inlineStr">
+        <is>
+          <t>Cut even portions. Garnish with nuts only if the allergen card allows. Service temperature: Hot. Allergen label for this dish: Gluten (wheat); Milk; Always verify labels; this card is a kitchen estimate, not a lab certificate. State clearly: vegetarian, no onion, no garlic, no eggs, no meat, no fish. Nutrition on this card is an estimate for 1 portion of 4.</t>
+        </is>
+      </c>
+      <c r="B35" s="50" t="n"/>
+      <c r="C35" s="50" t="n"/>
+      <c r="D35" s="50" t="n"/>
+    </row>
   </sheetData>
-  <mergeCells count="15">
+  <mergeCells count="28">
+    <mergeCell ref="A8:D8"/>
+    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="B23:D23"/>
+    <mergeCell ref="A35:D35"/>
+    <mergeCell ref="A29:D29"/>
+    <mergeCell ref="C14:D14"/>
+    <mergeCell ref="A19:D19"/>
+    <mergeCell ref="A28:D28"/>
+    <mergeCell ref="A9:D9"/>
+    <mergeCell ref="A31:D31"/>
+    <mergeCell ref="C16:D16"/>
+    <mergeCell ref="A34:D34"/>
+    <mergeCell ref="A30:D30"/>
+    <mergeCell ref="A11:D11"/>
+    <mergeCell ref="B24:D24"/>
+    <mergeCell ref="B20:D20"/>
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="C12:D12"/>
-    <mergeCell ref="A9:D9"/>
-    <mergeCell ref="A8:D8"/>
-    <mergeCell ref="C16:D16"/>
-    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="B26:D26"/>
+    <mergeCell ref="B25:D25"/>
+    <mergeCell ref="C17:D17"/>
+    <mergeCell ref="B22:D22"/>
     <mergeCell ref="A3:D3"/>
-    <mergeCell ref="C14:D14"/>
     <mergeCell ref="C13:D13"/>
     <mergeCell ref="A2:D2"/>
-    <mergeCell ref="A11:D11"/>
-    <mergeCell ref="A19:D19"/>
     <mergeCell ref="B21:D21"/>
-    <mergeCell ref="C17:D17"/>
-    <mergeCell ref="B20:D20"/>
+    <mergeCell ref="A33:D33"/>
+    <mergeCell ref="A32:D32"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" paperSize="9" fitToHeight="1" fitToWidth="1"/>
@@ -3553,7 +4683,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:D21"/>
+  <dimension ref="A1:D36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -3565,7 +4695,7 @@
     <row r="1" ht="32" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>RECIPE CARD  ·  Doce de Grao</t>
+          <t>Parslia Kitchen OS · RECIPE CARD · Doce de Grao</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3575,7 +4705,7 @@
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>Goa kitchen  ·  Sweet  ·  Goan Hindu vegetarian / sattvic</t>
+          <t>Pure Prasad · No onion · No garlic · No eggs · No meat · No fish  ·  Goa  ·  Sweet</t>
         </is>
       </c>
       <c r="B2" s="4" t="n"/>
@@ -3595,44 +4725,44 @@
     <row r="5" ht="18" customHeight="1">
       <c r="A5" s="39" t="inlineStr">
         <is>
-          <t>Serves</t>
+          <t>YIELD</t>
         </is>
       </c>
       <c r="B5" s="39" t="inlineStr">
         <is>
-          <t>Prep</t>
+          <t>PORTION</t>
         </is>
       </c>
       <c r="C5" s="39" t="inlineStr">
         <is>
-          <t>Cook</t>
+          <t>SERVICE</t>
         </is>
       </c>
       <c r="D5" s="39" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>TIME</t>
         </is>
       </c>
     </row>
     <row r="6" ht="28" customHeight="1">
       <c r="A6" s="40" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>4 portions</t>
         </is>
       </c>
       <c r="B6" s="40" t="inlineStr">
         <is>
-          <t>15 min</t>
+          <t>1 portion</t>
         </is>
       </c>
       <c r="C6" s="40" t="inlineStr">
         <is>
-          <t>25 min</t>
+          <t>Hot</t>
         </is>
       </c>
       <c r="D6" s="40" t="inlineStr">
         <is>
-          <t>40 min</t>
+          <t>Prep 15 min · Cook 25 min</t>
         </is>
       </c>
     </row>
@@ -3798,35 +4928,201 @@
       <c r="C20" s="46" t="n"/>
       <c r="D20" s="46" t="n"/>
     </row>
-    <row r="21" ht="36" customHeight="1">
+    <row r="21" ht="66" customHeight="1">
       <c r="A21" s="47" t="n">
         <v>1</v>
       </c>
       <c r="B21" s="48" t="inlineStr">
         <is>
-          <t>Cook in steel until it leaves the sides. Press, cut diamonds.</t>
+          <t>Mise en place. Weigh every ingredient on this card for 4 portions. Set Stainless steel kadhai or saucepan — never aluminium. Wash produce. Confirm spice blends have no onion or garlic powder. No onion, no garlic, no aluminium.</t>
         </is>
       </c>
       <c r="C21" s="49" t="n"/>
       <c r="D21" s="49" t="n"/>
     </row>
+    <row r="22" ht="36" customHeight="1">
+      <c r="A22" s="32" t="n">
+        <v>2</v>
+      </c>
+      <c r="B22" s="30" t="inlineStr">
+        <is>
+          <t>Cut vegetables to even size so they cook together.</t>
+        </is>
+      </c>
+      <c r="C22" s="31" t="n"/>
+      <c r="D22" s="31" t="n"/>
+    </row>
+    <row r="23" ht="54" customHeight="1">
+      <c r="A23" s="47" t="n">
+        <v>3</v>
+      </c>
+      <c r="B23" s="48" t="inlineStr">
+        <is>
+          <t>Cook in steel until it leaves the sides. Work in Stainless steel kadhai or saucepan — never aluminium. Cook to the doneness below, tasting salt at the end. Do not add onion, garlic or aluminium cookware.</t>
+        </is>
+      </c>
+      <c r="C23" s="49" t="n"/>
+      <c r="D23" s="49" t="n"/>
+    </row>
+    <row r="24" ht="54" customHeight="1">
+      <c r="A24" s="32" t="n">
+        <v>4</v>
+      </c>
+      <c r="B24" s="30" t="inlineStr">
+        <is>
+          <t>Press, cut diamonds. Work in Stainless steel kadhai or saucepan — never aluminium. Cook to the doneness below, tasting salt at the end. Do not add onion, garlic or aluminium cookware.</t>
+        </is>
+      </c>
+      <c r="C24" s="31" t="n"/>
+      <c r="D24" s="31" t="n"/>
+    </row>
+    <row r="25" ht="42" customHeight="1">
+      <c r="A25" s="47" t="n">
+        <v>5</v>
+      </c>
+      <c r="B25" s="48" t="inlineStr">
+        <is>
+          <t>Doneness: mixture leaves the sides of the pan, or milk is thick enough to coat a spoon, or syrup has taken the stated string.</t>
+        </is>
+      </c>
+      <c r="C25" s="49" t="n"/>
+      <c r="D25" s="49" t="n"/>
+    </row>
+    <row r="26" ht="42" customHeight="1">
+      <c r="A26" s="32" t="n">
+        <v>6</v>
+      </c>
+      <c r="B26" s="30" t="inlineStr">
+        <is>
+          <t>Taste and adjust salt, lemon or chilli only — do not add onion or garlic at the finish. Garnish as listed. Yield is 4 portions.</t>
+        </is>
+      </c>
+      <c r="C26" s="31" t="n"/>
+      <c r="D26" s="31" t="n"/>
+    </row>
+    <row r="27" ht="42" customHeight="1">
+      <c r="A27" s="47" t="n">
+        <v>7</v>
+      </c>
+      <c r="B27" s="48" t="inlineStr">
+        <is>
+          <t>Hold as the dish is eaten — hot sweets in a bain of hot water, chilled sweets in the fridge. Label date and time. Service: Hot.</t>
+        </is>
+      </c>
+      <c r="C27" s="49" t="n"/>
+      <c r="D27" s="49" t="n"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="21" t="inlineStr">
+        <is>
+          <t>Nutrition per portion</t>
+        </is>
+      </c>
+      <c r="B29" s="22" t="n"/>
+      <c r="C29" s="22" t="n"/>
+      <c r="D29" s="22" t="n"/>
+    </row>
+    <row r="30" ht="36" customHeight="1">
+      <c r="A30" s="12" t="inlineStr">
+        <is>
+          <t>kcal 440  ·  Protein 8 g  ·  Carbs 57 g  ·  Fat 22 g  ·  Fibre 10 g. Nutrition is a kitchen estimate from typical produce values, not a laboratory analysis.</t>
+        </is>
+      </c>
+      <c r="B30" s="50" t="n"/>
+      <c r="C30" s="50" t="n"/>
+      <c r="D30" s="50" t="n"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="24" t="inlineStr">
+        <is>
+          <t>Allergens</t>
+        </is>
+      </c>
+      <c r="B31" s="6" t="n"/>
+      <c r="C31" s="6" t="n"/>
+      <c r="D31" s="6" t="n"/>
+    </row>
+    <row r="32" ht="48" customHeight="1">
+      <c r="A32" s="25" t="inlineStr">
+        <is>
+          <t>Milk · Always verify labels; this card is a kitchen estimate, not a lab certificate.</t>
+        </is>
+      </c>
+      <c r="B32" s="26" t="n"/>
+      <c r="C32" s="26" t="n"/>
+      <c r="D32" s="26" t="n"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="24" t="inlineStr">
+        <is>
+          <t>Chef notes</t>
+        </is>
+      </c>
+      <c r="B33" s="6" t="n"/>
+      <c r="C33" s="6" t="n"/>
+      <c r="D33" s="6" t="n"/>
+    </row>
+    <row r="34" ht="72" customHeight="1">
+      <c r="A34" s="25" t="inlineStr">
+        <is>
+          <t>For Doce de Grao: keep the mix slightly drier than you think; wet mixes split or go greasy. Bloom hing in hot fat 20–30 seconds; raw hing tastes medicinal. Commercial hing is often cut with wheat flour — use a gluten-free hing if you must mark Gluten Free. Never cook tomato, tamarind, lemon, yogurt or milk in aluminium; use stainless steel, iron, clay or glass. Spice blends: read the packet. Many garam masalas hide onion or garlic powder.</t>
+        </is>
+      </c>
+      <c r="B34" s="26" t="n"/>
+      <c r="C34" s="26" t="n"/>
+      <c r="D34" s="26" t="n"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="51" t="inlineStr">
+        <is>
+          <t>Service notes</t>
+        </is>
+      </c>
+      <c r="B35" s="52" t="n"/>
+      <c r="C35" s="52" t="n"/>
+      <c r="D35" s="52" t="n"/>
+    </row>
+    <row r="36" ht="64" customHeight="1">
+      <c r="A36" s="12" t="inlineStr">
+        <is>
+          <t>Cut even portions. Garnish with nuts only if the allergen card allows. Service temperature: Hot. Allergen label for this dish: Milk; Always verify labels; this card is a kitchen estimate, not a lab certificate. State clearly: vegetarian, no onion, no garlic, no eggs, no meat, no fish. Nutrition on this card is an estimate for 1 portion of 4.</t>
+        </is>
+      </c>
+      <c r="B36" s="50" t="n"/>
+      <c r="C36" s="50" t="n"/>
+      <c r="D36" s="50" t="n"/>
+    </row>
   </sheetData>
-  <mergeCells count="15">
+  <mergeCells count="29">
+    <mergeCell ref="A8:D8"/>
+    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="B23:D23"/>
+    <mergeCell ref="A35:D35"/>
+    <mergeCell ref="A29:D29"/>
+    <mergeCell ref="C14:D14"/>
+    <mergeCell ref="A19:D19"/>
+    <mergeCell ref="A9:D9"/>
+    <mergeCell ref="A31:D31"/>
+    <mergeCell ref="C16:D16"/>
+    <mergeCell ref="A34:D34"/>
+    <mergeCell ref="A30:D30"/>
+    <mergeCell ref="A11:D11"/>
+    <mergeCell ref="B24:D24"/>
+    <mergeCell ref="A36:D36"/>
+    <mergeCell ref="B20:D20"/>
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="C12:D12"/>
-    <mergeCell ref="A9:D9"/>
-    <mergeCell ref="A8:D8"/>
-    <mergeCell ref="C16:D16"/>
-    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="B26:D26"/>
+    <mergeCell ref="B25:D25"/>
+    <mergeCell ref="C17:D17"/>
+    <mergeCell ref="B22:D22"/>
     <mergeCell ref="A3:D3"/>
-    <mergeCell ref="C14:D14"/>
+    <mergeCell ref="B27:D27"/>
     <mergeCell ref="C13:D13"/>
     <mergeCell ref="A2:D2"/>
-    <mergeCell ref="A11:D11"/>
-    <mergeCell ref="A19:D19"/>
     <mergeCell ref="B21:D21"/>
-    <mergeCell ref="C17:D17"/>
-    <mergeCell ref="B20:D20"/>
+    <mergeCell ref="A33:D33"/>
+    <mergeCell ref="A32:D32"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" paperSize="9" fitToHeight="1" fitToWidth="1"/>
@@ -3840,7 +5136,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:D20"/>
+  <dimension ref="A1:D35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -3852,7 +5148,7 @@
     <row r="1" ht="32" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>RECIPE CARD  ·  Coconut Toffee</t>
+          <t>Parslia Kitchen OS · RECIPE CARD · Coconut Toffee</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3862,7 +5158,7 @@
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>Goa kitchen  ·  Sweet  ·  Goan Hindu vegetarian / sattvic</t>
+          <t>Pure Prasad · No onion · No garlic · No eggs · No meat · No fish  ·  Goa  ·  Sweet</t>
         </is>
       </c>
       <c r="B2" s="4" t="n"/>
@@ -3882,44 +5178,44 @@
     <row r="5" ht="18" customHeight="1">
       <c r="A5" s="39" t="inlineStr">
         <is>
-          <t>Serves</t>
+          <t>YIELD</t>
         </is>
       </c>
       <c r="B5" s="39" t="inlineStr">
         <is>
-          <t>Prep</t>
+          <t>PORTION</t>
         </is>
       </c>
       <c r="C5" s="39" t="inlineStr">
         <is>
-          <t>Cook</t>
+          <t>SERVICE</t>
         </is>
       </c>
       <c r="D5" s="39" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>TIME</t>
         </is>
       </c>
     </row>
     <row r="6" ht="28" customHeight="1">
       <c r="A6" s="40" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>4 portions</t>
         </is>
       </c>
       <c r="B6" s="40" t="inlineStr">
         <is>
-          <t>10 min</t>
+          <t>1 portion</t>
         </is>
       </c>
       <c r="C6" s="40" t="inlineStr">
         <is>
-          <t>20 min</t>
+          <t>Hot</t>
         </is>
       </c>
       <c r="D6" s="40" t="inlineStr">
         <is>
-          <t>30 min</t>
+          <t>Prep 10 min · Cook 20 min</t>
         </is>
       </c>
     </row>
@@ -4067,34 +5363,200 @@
       <c r="C19" s="46" t="n"/>
       <c r="D19" s="46" t="n"/>
     </row>
-    <row r="20" ht="36" customHeight="1">
+    <row r="20" ht="66" customHeight="1">
       <c r="A20" s="47" t="n">
         <v>1</v>
       </c>
       <c r="B20" s="48" t="inlineStr">
         <is>
-          <t>Cook to toffee stage in steel. Set, cut.</t>
+          <t>Mise en place. Weigh every ingredient on this card for 4 portions. Set Stainless steel kadhai or saucepan — never aluminium. Wash produce. Confirm spice blends have no onion or garlic powder. No onion, no garlic, no aluminium.</t>
         </is>
       </c>
       <c r="C20" s="49" t="n"/>
       <c r="D20" s="49" t="n"/>
     </row>
+    <row r="21" ht="36" customHeight="1">
+      <c r="A21" s="32" t="n">
+        <v>2</v>
+      </c>
+      <c r="B21" s="30" t="inlineStr">
+        <is>
+          <t>Cut vegetables to even size so they cook together.</t>
+        </is>
+      </c>
+      <c r="C21" s="31" t="n"/>
+      <c r="D21" s="31" t="n"/>
+    </row>
+    <row r="22" ht="54" customHeight="1">
+      <c r="A22" s="47" t="n">
+        <v>3</v>
+      </c>
+      <c r="B22" s="48" t="inlineStr">
+        <is>
+          <t>Cook to toffee stage in steel. Work in Stainless steel kadhai or saucepan — never aluminium. Cook to the doneness below, tasting salt at the end. Do not add onion, garlic or aluminium cookware.</t>
+        </is>
+      </c>
+      <c r="C22" s="49" t="n"/>
+      <c r="D22" s="49" t="n"/>
+    </row>
+    <row r="23" ht="54" customHeight="1">
+      <c r="A23" s="32" t="n">
+        <v>4</v>
+      </c>
+      <c r="B23" s="30" t="inlineStr">
+        <is>
+          <t>Set, cut. Work in Stainless steel kadhai or saucepan — never aluminium. Cook to the doneness below, tasting salt at the end. Do not add onion, garlic or aluminium cookware.</t>
+        </is>
+      </c>
+      <c r="C23" s="31" t="n"/>
+      <c r="D23" s="31" t="n"/>
+    </row>
+    <row r="24" ht="42" customHeight="1">
+      <c r="A24" s="47" t="n">
+        <v>5</v>
+      </c>
+      <c r="B24" s="48" t="inlineStr">
+        <is>
+          <t>Doneness: mixture leaves the sides of the pan, or milk is thick enough to coat a spoon, or syrup has taken the stated string.</t>
+        </is>
+      </c>
+      <c r="C24" s="49" t="n"/>
+      <c r="D24" s="49" t="n"/>
+    </row>
+    <row r="25" ht="42" customHeight="1">
+      <c r="A25" s="32" t="n">
+        <v>6</v>
+      </c>
+      <c r="B25" s="30" t="inlineStr">
+        <is>
+          <t>Taste and adjust salt, lemon or chilli only — do not add onion or garlic at the finish. Garnish as listed. Yield is 4 portions.</t>
+        </is>
+      </c>
+      <c r="C25" s="31" t="n"/>
+      <c r="D25" s="31" t="n"/>
+    </row>
+    <row r="26" ht="42" customHeight="1">
+      <c r="A26" s="47" t="n">
+        <v>7</v>
+      </c>
+      <c r="B26" s="48" t="inlineStr">
+        <is>
+          <t>Hold as the dish is eaten — hot sweets in a bain of hot water, chilled sweets in the fridge. Label date and time. Service: Hot.</t>
+        </is>
+      </c>
+      <c r="C26" s="49" t="n"/>
+      <c r="D26" s="49" t="n"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="21" t="inlineStr">
+        <is>
+          <t>Nutrition per portion</t>
+        </is>
+      </c>
+      <c r="B28" s="22" t="n"/>
+      <c r="C28" s="22" t="n"/>
+      <c r="D28" s="22" t="n"/>
+    </row>
+    <row r="29" ht="36" customHeight="1">
+      <c r="A29" s="12" t="inlineStr">
+        <is>
+          <t>kcal 474  ·  Protein 2 g  ·  Carbs 49 g  ·  Fat 32 g  ·  Fibre 7 g. Nutrition is a kitchen estimate from typical produce values, not a laboratory analysis.</t>
+        </is>
+      </c>
+      <c r="B29" s="50" t="n"/>
+      <c r="C29" s="50" t="n"/>
+      <c r="D29" s="50" t="n"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="24" t="inlineStr">
+        <is>
+          <t>Allergens</t>
+        </is>
+      </c>
+      <c r="B30" s="6" t="n"/>
+      <c r="C30" s="6" t="n"/>
+      <c r="D30" s="6" t="n"/>
+    </row>
+    <row r="31" ht="48" customHeight="1">
+      <c r="A31" s="25" t="inlineStr">
+        <is>
+          <t>Milk · Always verify labels; this card is a kitchen estimate, not a lab certificate.</t>
+        </is>
+      </c>
+      <c r="B31" s="26" t="n"/>
+      <c r="C31" s="26" t="n"/>
+      <c r="D31" s="26" t="n"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="24" t="inlineStr">
+        <is>
+          <t>Chef notes</t>
+        </is>
+      </c>
+      <c r="B32" s="6" t="n"/>
+      <c r="C32" s="6" t="n"/>
+      <c r="D32" s="6" t="n"/>
+    </row>
+    <row r="33" ht="72" customHeight="1">
+      <c r="A33" s="25" t="inlineStr">
+        <is>
+          <t>For Coconut Toffee: keep the mix slightly drier than you think; wet mixes split or go greasy. Bloom hing in hot fat 20–30 seconds; raw hing tastes medicinal. Commercial hing is often cut with wheat flour — use a gluten-free hing if you must mark Gluten Free. Never cook tomato, tamarind, lemon, yogurt or milk in aluminium; use stainless steel, iron, clay or glass. Spice blends: read the packet. Many garam masalas hide onion or garlic powder.</t>
+        </is>
+      </c>
+      <c r="B33" s="26" t="n"/>
+      <c r="C33" s="26" t="n"/>
+      <c r="D33" s="26" t="n"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="51" t="inlineStr">
+        <is>
+          <t>Service notes</t>
+        </is>
+      </c>
+      <c r="B34" s="52" t="n"/>
+      <c r="C34" s="52" t="n"/>
+      <c r="D34" s="52" t="n"/>
+    </row>
+    <row r="35" ht="64" customHeight="1">
+      <c r="A35" s="12" t="inlineStr">
+        <is>
+          <t>Cut even portions. Garnish with nuts only if the allergen card allows. Service temperature: Hot. Allergen label for this dish: Milk; Always verify labels; this card is a kitchen estimate, not a lab certificate. State clearly: vegetarian, no onion, no garlic, no eggs, no meat, no fish. Nutrition on this card is an estimate for 1 portion of 4.</t>
+        </is>
+      </c>
+      <c r="B35" s="50" t="n"/>
+      <c r="C35" s="50" t="n"/>
+      <c r="D35" s="50" t="n"/>
+    </row>
   </sheetData>
-  <mergeCells count="14">
+  <mergeCells count="28">
+    <mergeCell ref="A8:D8"/>
+    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="B23:D23"/>
+    <mergeCell ref="A35:D35"/>
+    <mergeCell ref="A29:D29"/>
+    <mergeCell ref="C14:D14"/>
+    <mergeCell ref="A28:D28"/>
+    <mergeCell ref="A9:D9"/>
+    <mergeCell ref="B19:D19"/>
+    <mergeCell ref="A31:D31"/>
+    <mergeCell ref="C16:D16"/>
+    <mergeCell ref="A34:D34"/>
+    <mergeCell ref="A30:D30"/>
+    <mergeCell ref="A11:D11"/>
+    <mergeCell ref="B24:D24"/>
+    <mergeCell ref="B20:D20"/>
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="C12:D12"/>
-    <mergeCell ref="A9:D9"/>
+    <mergeCell ref="B26:D26"/>
+    <mergeCell ref="B25:D25"/>
     <mergeCell ref="A18:D18"/>
-    <mergeCell ref="A8:D8"/>
-    <mergeCell ref="B19:D19"/>
-    <mergeCell ref="C16:D16"/>
-    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="B22:D22"/>
     <mergeCell ref="A3:D3"/>
-    <mergeCell ref="C14:D14"/>
     <mergeCell ref="C13:D13"/>
     <mergeCell ref="A2:D2"/>
-    <mergeCell ref="A11:D11"/>
-    <mergeCell ref="B20:D20"/>
+    <mergeCell ref="B21:D21"/>
+    <mergeCell ref="A33:D33"/>
+    <mergeCell ref="A32:D32"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" paperSize="9" fitToHeight="1" fitToWidth="1"/>
@@ -4108,7 +5570,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:D21"/>
+  <dimension ref="A1:D36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -4120,7 +5582,7 @@
     <row r="1" ht="32" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>RECIPE CARD  ·  Coconut Payasam</t>
+          <t>Parslia Kitchen OS · RECIPE CARD · Coconut Payasam</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -4130,7 +5592,7 @@
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>Goa kitchen  ·  Dessert  ·  Goan Hindu vegetarian / sattvic</t>
+          <t>Pure Prasad · No onion · No garlic · No eggs · No meat · No fish  ·  Goa  ·  Dessert</t>
         </is>
       </c>
       <c r="B2" s="4" t="n"/>
@@ -4150,44 +5612,44 @@
     <row r="5" ht="18" customHeight="1">
       <c r="A5" s="39" t="inlineStr">
         <is>
-          <t>Serves</t>
+          <t>YIELD</t>
         </is>
       </c>
       <c r="B5" s="39" t="inlineStr">
         <is>
-          <t>Prep</t>
+          <t>PORTION</t>
         </is>
       </c>
       <c r="C5" s="39" t="inlineStr">
         <is>
-          <t>Cook</t>
+          <t>SERVICE</t>
         </is>
       </c>
       <c r="D5" s="39" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>TIME</t>
         </is>
       </c>
     </row>
     <row r="6" ht="28" customHeight="1">
       <c r="A6" s="40" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>4 portions</t>
         </is>
       </c>
       <c r="B6" s="40" t="inlineStr">
         <is>
-          <t>5 min</t>
+          <t>1 portion</t>
         </is>
       </c>
       <c r="C6" s="40" t="inlineStr">
         <is>
-          <t>20 min</t>
+          <t>Hot or chilled</t>
         </is>
       </c>
       <c r="D6" s="40" t="inlineStr">
         <is>
-          <t>25 min</t>
+          <t>Prep 5 min · Cook 20 min</t>
         </is>
       </c>
     </row>
@@ -4353,35 +5815,201 @@
       <c r="C20" s="46" t="n"/>
       <c r="D20" s="46" t="n"/>
     </row>
-    <row r="21" ht="36" customHeight="1">
+    <row r="21" ht="66" customHeight="1">
       <c r="A21" s="47" t="n">
         <v>1</v>
       </c>
       <c r="B21" s="48" t="inlineStr">
         <is>
-          <t>Cook in steel. Do not boil coconut milk hard.</t>
+          <t>Mise en place. Weigh every ingredient on this card for 4 portions. Set Stainless steel kadhai or saucepan — never aluminium. Wash produce. Confirm spice blends have no onion or garlic powder. No onion, no garlic, no aluminium.</t>
         </is>
       </c>
       <c r="C21" s="49" t="n"/>
       <c r="D21" s="49" t="n"/>
     </row>
+    <row r="22" ht="42" customHeight="1">
+      <c r="A22" s="32" t="n">
+        <v>2</v>
+      </c>
+      <c r="B22" s="30" t="inlineStr">
+        <is>
+          <t>Cut vegetables to even size so they cook together. Use a heavy stainless steel milk pot. Acidic or milk dishes must never touch aluminium.</t>
+        </is>
+      </c>
+      <c r="C22" s="31" t="n"/>
+      <c r="D22" s="31" t="n"/>
+    </row>
+    <row r="23" ht="54" customHeight="1">
+      <c r="A23" s="47" t="n">
+        <v>3</v>
+      </c>
+      <c r="B23" s="48" t="inlineStr">
+        <is>
+          <t>Cook in steel. Work in Stainless steel kadhai or saucepan — never aluminium. Cook to the doneness below, tasting salt at the end. Do not add onion, garlic or aluminium cookware.</t>
+        </is>
+      </c>
+      <c r="C23" s="49" t="n"/>
+      <c r="D23" s="49" t="n"/>
+    </row>
+    <row r="24" ht="54" customHeight="1">
+      <c r="A24" s="32" t="n">
+        <v>4</v>
+      </c>
+      <c r="B24" s="30" t="inlineStr">
+        <is>
+          <t>Do not boil coconut milk hard. Work in Stainless steel kadhai or saucepan — never aluminium. Cook to the doneness below, tasting salt at the end. Do not add onion, garlic or aluminium cookware.</t>
+        </is>
+      </c>
+      <c r="C24" s="31" t="n"/>
+      <c r="D24" s="31" t="n"/>
+    </row>
+    <row r="25" ht="42" customHeight="1">
+      <c r="A25" s="47" t="n">
+        <v>5</v>
+      </c>
+      <c r="B25" s="48" t="inlineStr">
+        <is>
+          <t>Doneness: mixture leaves the sides of the pan, or milk is thick enough to coat a spoon, or syrup has taken the stated string.</t>
+        </is>
+      </c>
+      <c r="C25" s="49" t="n"/>
+      <c r="D25" s="49" t="n"/>
+    </row>
+    <row r="26" ht="42" customHeight="1">
+      <c r="A26" s="32" t="n">
+        <v>6</v>
+      </c>
+      <c r="B26" s="30" t="inlineStr">
+        <is>
+          <t>Taste and adjust salt, lemon or chilli only — do not add onion or garlic at the finish. Garnish as listed. Yield is 4 portions.</t>
+        </is>
+      </c>
+      <c r="C26" s="31" t="n"/>
+      <c r="D26" s="31" t="n"/>
+    </row>
+    <row r="27" ht="42" customHeight="1">
+      <c r="A27" s="47" t="n">
+        <v>7</v>
+      </c>
+      <c r="B27" s="48" t="inlineStr">
+        <is>
+          <t>Hold as the dish is eaten — hot sweets in a bain of hot water, chilled sweets in the fridge. Label date and time. Service: Hot or chilled.</t>
+        </is>
+      </c>
+      <c r="C27" s="49" t="n"/>
+      <c r="D27" s="49" t="n"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="21" t="inlineStr">
+        <is>
+          <t>Nutrition per portion</t>
+        </is>
+      </c>
+      <c r="B29" s="22" t="n"/>
+      <c r="C29" s="22" t="n"/>
+      <c r="D29" s="22" t="n"/>
+    </row>
+    <row r="30" ht="36" customHeight="1">
+      <c r="A30" s="12" t="inlineStr">
+        <is>
+          <t>kcal 502  ·  Protein 5 g  ·  Carbs 45 g  ·  Fat 36 g  ·  Fibre 10 g. Nutrition is a kitchen estimate from typical produce values, not a laboratory analysis.</t>
+        </is>
+      </c>
+      <c r="B30" s="50" t="n"/>
+      <c r="C30" s="50" t="n"/>
+      <c r="D30" s="50" t="n"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="24" t="inlineStr">
+        <is>
+          <t>Allergens</t>
+        </is>
+      </c>
+      <c r="B31" s="6" t="n"/>
+      <c r="C31" s="6" t="n"/>
+      <c r="D31" s="6" t="n"/>
+    </row>
+    <row r="32" ht="48" customHeight="1">
+      <c r="A32" s="25" t="inlineStr">
+        <is>
+          <t>Milk · Always verify labels; this card is a kitchen estimate, not a lab certificate.</t>
+        </is>
+      </c>
+      <c r="B32" s="26" t="n"/>
+      <c r="C32" s="26" t="n"/>
+      <c r="D32" s="26" t="n"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="24" t="inlineStr">
+        <is>
+          <t>Chef notes</t>
+        </is>
+      </c>
+      <c r="B33" s="6" t="n"/>
+      <c r="C33" s="6" t="n"/>
+      <c r="D33" s="6" t="n"/>
+    </row>
+    <row r="34" ht="72" customHeight="1">
+      <c r="A34" s="25" t="inlineStr">
+        <is>
+          <t>For Coconut Payasam: keep the mix slightly drier than you think; wet mixes split or go greasy. Bloom hing in hot fat 20–30 seconds; raw hing tastes medicinal. Commercial hing is often cut with wheat flour — use a gluten-free hing if you must mark Gluten Free. Never cook tomato, tamarind, lemon, yogurt or milk in aluminium; use stainless steel, iron, clay or glass. Spice blends: read the packet. Many garam masalas hide onion or garlic powder.</t>
+        </is>
+      </c>
+      <c r="B34" s="26" t="n"/>
+      <c r="C34" s="26" t="n"/>
+      <c r="D34" s="26" t="n"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="51" t="inlineStr">
+        <is>
+          <t>Service notes</t>
+        </is>
+      </c>
+      <c r="B35" s="52" t="n"/>
+      <c r="C35" s="52" t="n"/>
+      <c r="D35" s="52" t="n"/>
+    </row>
+    <row r="36" ht="64" customHeight="1">
+      <c r="A36" s="12" t="inlineStr">
+        <is>
+          <t>Serve in steel or glass bowls. If chilled, take out 5 minutes before the pass. Service temperature: Hot or chilled. Allergen label for this dish: Milk; Always verify labels; this card is a kitchen estimate, not a lab certificate. State clearly: vegetarian, no onion, no garlic, no eggs, no meat, no fish. Nutrition on this card is an estimate for 1 portion of 4.</t>
+        </is>
+      </c>
+      <c r="B36" s="50" t="n"/>
+      <c r="C36" s="50" t="n"/>
+      <c r="D36" s="50" t="n"/>
+    </row>
   </sheetData>
-  <mergeCells count="15">
+  <mergeCells count="29">
+    <mergeCell ref="A8:D8"/>
+    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="B23:D23"/>
+    <mergeCell ref="A35:D35"/>
+    <mergeCell ref="A29:D29"/>
+    <mergeCell ref="C14:D14"/>
+    <mergeCell ref="A19:D19"/>
+    <mergeCell ref="A9:D9"/>
+    <mergeCell ref="A31:D31"/>
+    <mergeCell ref="C16:D16"/>
+    <mergeCell ref="A34:D34"/>
+    <mergeCell ref="A30:D30"/>
+    <mergeCell ref="A11:D11"/>
+    <mergeCell ref="B24:D24"/>
+    <mergeCell ref="A36:D36"/>
+    <mergeCell ref="B20:D20"/>
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="C12:D12"/>
-    <mergeCell ref="A9:D9"/>
-    <mergeCell ref="A8:D8"/>
-    <mergeCell ref="C16:D16"/>
-    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="B26:D26"/>
+    <mergeCell ref="B25:D25"/>
+    <mergeCell ref="C17:D17"/>
+    <mergeCell ref="B22:D22"/>
     <mergeCell ref="A3:D3"/>
-    <mergeCell ref="C14:D14"/>
+    <mergeCell ref="B27:D27"/>
     <mergeCell ref="C13:D13"/>
     <mergeCell ref="A2:D2"/>
-    <mergeCell ref="A11:D11"/>
-    <mergeCell ref="A19:D19"/>
     <mergeCell ref="B21:D21"/>
-    <mergeCell ref="C17:D17"/>
-    <mergeCell ref="B20:D20"/>
+    <mergeCell ref="A33:D33"/>
+    <mergeCell ref="A32:D32"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" paperSize="9" fitToHeight="1" fitToWidth="1"/>
@@ -4659,7 +6287,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:D21"/>
+  <dimension ref="A1:D37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -4671,7 +6299,7 @@
     <row r="1" ht="32" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>RECIPE CARD  ·  Moong Mangane</t>
+          <t>Parslia Kitchen OS · RECIPE CARD · Moong Mangane</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -4681,7 +6309,7 @@
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>Goa kitchen  ·  Dessert  ·  Goan Hindu vegetarian / sattvic</t>
+          <t>Pure Prasad · No onion · No garlic · No eggs · No meat · No fish  ·  Goa  ·  Dessert</t>
         </is>
       </c>
       <c r="B2" s="4" t="n"/>
@@ -4701,44 +6329,44 @@
     <row r="5" ht="18" customHeight="1">
       <c r="A5" s="39" t="inlineStr">
         <is>
-          <t>Serves</t>
+          <t>YIELD</t>
         </is>
       </c>
       <c r="B5" s="39" t="inlineStr">
         <is>
-          <t>Prep</t>
+          <t>PORTION</t>
         </is>
       </c>
       <c r="C5" s="39" t="inlineStr">
         <is>
-          <t>Cook</t>
+          <t>SERVICE</t>
         </is>
       </c>
       <c r="D5" s="39" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>TIME</t>
         </is>
       </c>
     </row>
     <row r="6" ht="28" customHeight="1">
       <c r="A6" s="40" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>4 portions</t>
         </is>
       </c>
       <c r="B6" s="40" t="inlineStr">
         <is>
-          <t>10 min</t>
+          <t>1 portion</t>
         </is>
       </c>
       <c r="C6" s="40" t="inlineStr">
         <is>
-          <t>25 min</t>
+          <t>Hot</t>
         </is>
       </c>
       <c r="D6" s="40" t="inlineStr">
         <is>
-          <t>35 min</t>
+          <t>Prep 10 min · Cook 25 min</t>
         </is>
       </c>
     </row>
@@ -4904,35 +6532,214 @@
       <c r="C20" s="46" t="n"/>
       <c r="D20" s="46" t="n"/>
     </row>
-    <row r="21" ht="36" customHeight="1">
+    <row r="21" ht="66" customHeight="1">
       <c r="A21" s="47" t="n">
         <v>1</v>
       </c>
       <c r="B21" s="48" t="inlineStr">
         <is>
-          <t>Cook moong soft. Add jaggery and coconut milk. Cardamom.</t>
+          <t>Mise en place. Weigh every ingredient on this card for 4 portions. Set Stainless steel kadhai or saucepan — never aluminium. Wash produce. Confirm spice blends have no onion or garlic powder. No onion, no garlic, no aluminium.</t>
         </is>
       </c>
       <c r="C21" s="49" t="n"/>
       <c r="D21" s="49" t="n"/>
     </row>
+    <row r="22" ht="42" customHeight="1">
+      <c r="A22" s="32" t="n">
+        <v>2</v>
+      </c>
+      <c r="B22" s="30" t="inlineStr">
+        <is>
+          <t>Cut vegetables to even size so they cook together. Use a heavy stainless steel milk pot. Acidic or milk dishes must never touch aluminium.</t>
+        </is>
+      </c>
+      <c r="C22" s="31" t="n"/>
+      <c r="D22" s="31" t="n"/>
+    </row>
+    <row r="23" ht="54" customHeight="1">
+      <c r="A23" s="47" t="n">
+        <v>3</v>
+      </c>
+      <c r="B23" s="48" t="inlineStr">
+        <is>
+          <t>Cook moong soft. Work in Stainless steel kadhai or saucepan — never aluminium. Cook to the doneness below, tasting salt at the end. Do not add onion, garlic or aluminium cookware.</t>
+        </is>
+      </c>
+      <c r="C23" s="49" t="n"/>
+      <c r="D23" s="49" t="n"/>
+    </row>
+    <row r="24" ht="54" customHeight="1">
+      <c r="A24" s="32" t="n">
+        <v>4</v>
+      </c>
+      <c r="B24" s="30" t="inlineStr">
+        <is>
+          <t>Add jaggery and coconut milk. Work in Stainless steel kadhai or saucepan — never aluminium. Cook to the doneness below, tasting salt at the end. Do not add onion, garlic or aluminium cookware.</t>
+        </is>
+      </c>
+      <c r="C24" s="31" t="n"/>
+      <c r="D24" s="31" t="n"/>
+    </row>
+    <row r="25" ht="54" customHeight="1">
+      <c r="A25" s="47" t="n">
+        <v>5</v>
+      </c>
+      <c r="B25" s="48" t="inlineStr">
+        <is>
+          <t>Cardamom. Work in Stainless steel kadhai or saucepan — never aluminium. Cook to the doneness below, tasting salt at the end. Do not add onion, garlic or aluminium cookware.</t>
+        </is>
+      </c>
+      <c r="C25" s="49" t="n"/>
+      <c r="D25" s="49" t="n"/>
+    </row>
+    <row r="26" ht="42" customHeight="1">
+      <c r="A26" s="32" t="n">
+        <v>6</v>
+      </c>
+      <c r="B26" s="30" t="inlineStr">
+        <is>
+          <t>Doneness: mixture leaves the sides of the pan, or milk is thick enough to coat a spoon, or syrup has taken the stated string.</t>
+        </is>
+      </c>
+      <c r="C26" s="31" t="n"/>
+      <c r="D26" s="31" t="n"/>
+    </row>
+    <row r="27" ht="42" customHeight="1">
+      <c r="A27" s="47" t="n">
+        <v>7</v>
+      </c>
+      <c r="B27" s="48" t="inlineStr">
+        <is>
+          <t>Taste and adjust salt, lemon or chilli only — do not add onion or garlic at the finish. Garnish as listed. Yield is 4 portions.</t>
+        </is>
+      </c>
+      <c r="C27" s="49" t="n"/>
+      <c r="D27" s="49" t="n"/>
+    </row>
+    <row r="28" ht="42" customHeight="1">
+      <c r="A28" s="32" t="n">
+        <v>8</v>
+      </c>
+      <c r="B28" s="30" t="inlineStr">
+        <is>
+          <t>Hold as the dish is eaten — hot sweets in a bain of hot water, chilled sweets in the fridge. Label date and time. Service: Hot.</t>
+        </is>
+      </c>
+      <c r="C28" s="31" t="n"/>
+      <c r="D28" s="31" t="n"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="21" t="inlineStr">
+        <is>
+          <t>Nutrition per portion</t>
+        </is>
+      </c>
+      <c r="B30" s="22" t="n"/>
+      <c r="C30" s="22" t="n"/>
+      <c r="D30" s="22" t="n"/>
+    </row>
+    <row r="31" ht="36" customHeight="1">
+      <c r="A31" s="12" t="inlineStr">
+        <is>
+          <t>kcal 543  ·  Protein 8 g  ·  Carbs 53 g  ·  Fat 35 g  ·  Fibre 12 g. Nutrition is a kitchen estimate from typical produce values, not a laboratory analysis.</t>
+        </is>
+      </c>
+      <c r="B31" s="50" t="n"/>
+      <c r="C31" s="50" t="n"/>
+      <c r="D31" s="50" t="n"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="24" t="inlineStr">
+        <is>
+          <t>Allergens</t>
+        </is>
+      </c>
+      <c r="B32" s="6" t="n"/>
+      <c r="C32" s="6" t="n"/>
+      <c r="D32" s="6" t="n"/>
+    </row>
+    <row r="33" ht="48" customHeight="1">
+      <c r="A33" s="25" t="inlineStr">
+        <is>
+          <t>Milk · Always verify labels; this card is a kitchen estimate, not a lab certificate.</t>
+        </is>
+      </c>
+      <c r="B33" s="26" t="n"/>
+      <c r="C33" s="26" t="n"/>
+      <c r="D33" s="26" t="n"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="24" t="inlineStr">
+        <is>
+          <t>Chef notes</t>
+        </is>
+      </c>
+      <c r="B34" s="6" t="n"/>
+      <c r="C34" s="6" t="n"/>
+      <c r="D34" s="6" t="n"/>
+    </row>
+    <row r="35" ht="72" customHeight="1">
+      <c r="A35" s="25" t="inlineStr">
+        <is>
+          <t>For Moong Mangane: keep the mix slightly drier than you think; wet mixes split or go greasy. Bloom hing in hot fat 20–30 seconds; raw hing tastes medicinal. Commercial hing is often cut with wheat flour — use a gluten-free hing if you must mark Gluten Free. Never cook tomato, tamarind, lemon, yogurt or milk in aluminium; use stainless steel, iron, clay or glass. Spice blends: read the packet. Many garam masalas hide onion or garlic powder.</t>
+        </is>
+      </c>
+      <c r="B35" s="26" t="n"/>
+      <c r="C35" s="26" t="n"/>
+      <c r="D35" s="26" t="n"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="51" t="inlineStr">
+        <is>
+          <t>Service notes</t>
+        </is>
+      </c>
+      <c r="B36" s="52" t="n"/>
+      <c r="C36" s="52" t="n"/>
+      <c r="D36" s="52" t="n"/>
+    </row>
+    <row r="37" ht="64" customHeight="1">
+      <c r="A37" s="12" t="inlineStr">
+        <is>
+          <t>Serve in steel or glass bowls. If chilled, take out 5 minutes before the pass. Service temperature: Hot. Allergen label for this dish: Milk; Always verify labels; this card is a kitchen estimate, not a lab certificate. State clearly: vegetarian, no onion, no garlic, no eggs, no meat, no fish. Nutrition on this card is an estimate for 1 portion of 4.</t>
+        </is>
+      </c>
+      <c r="B37" s="50" t="n"/>
+      <c r="C37" s="50" t="n"/>
+      <c r="D37" s="50" t="n"/>
+    </row>
   </sheetData>
-  <mergeCells count="15">
+  <mergeCells count="30">
+    <mergeCell ref="A8:D8"/>
+    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="B23:D23"/>
+    <mergeCell ref="A35:D35"/>
+    <mergeCell ref="C14:D14"/>
+    <mergeCell ref="A19:D19"/>
+    <mergeCell ref="B28:D28"/>
+    <mergeCell ref="A9:D9"/>
+    <mergeCell ref="A31:D31"/>
+    <mergeCell ref="C16:D16"/>
+    <mergeCell ref="A34:D34"/>
+    <mergeCell ref="A30:D30"/>
+    <mergeCell ref="A11:D11"/>
+    <mergeCell ref="B24:D24"/>
+    <mergeCell ref="A36:D36"/>
+    <mergeCell ref="B20:D20"/>
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="C12:D12"/>
-    <mergeCell ref="A9:D9"/>
-    <mergeCell ref="A8:D8"/>
-    <mergeCell ref="C16:D16"/>
-    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="B26:D26"/>
+    <mergeCell ref="B25:D25"/>
+    <mergeCell ref="C17:D17"/>
+    <mergeCell ref="A37:D37"/>
+    <mergeCell ref="B22:D22"/>
     <mergeCell ref="A3:D3"/>
-    <mergeCell ref="C14:D14"/>
+    <mergeCell ref="B27:D27"/>
     <mergeCell ref="C13:D13"/>
     <mergeCell ref="A2:D2"/>
-    <mergeCell ref="A11:D11"/>
-    <mergeCell ref="A19:D19"/>
     <mergeCell ref="B21:D21"/>
-    <mergeCell ref="C17:D17"/>
-    <mergeCell ref="B20:D20"/>
+    <mergeCell ref="A33:D33"/>
+    <mergeCell ref="A32:D32"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" paperSize="9" fitToHeight="1" fitToWidth="1"/>
@@ -4946,7 +6753,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:D20"/>
+  <dimension ref="A1:D34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -4958,7 +6765,7 @@
     <row r="1" ht="32" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>RECIPE CARD  ·  Rice Kheer</t>
+          <t>Parslia Kitchen OS · RECIPE CARD · Rice Kheer</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -4968,7 +6775,7 @@
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>Goa kitchen  ·  Dessert  ·  Goan Hindu vegetarian / sattvic</t>
+          <t>Pure Prasad · No onion · No garlic · No eggs · No meat · No fish  ·  Goa  ·  Dessert</t>
         </is>
       </c>
       <c r="B2" s="4" t="n"/>
@@ -4988,44 +6795,44 @@
     <row r="5" ht="18" customHeight="1">
       <c r="A5" s="39" t="inlineStr">
         <is>
-          <t>Serves</t>
+          <t>YIELD</t>
         </is>
       </c>
       <c r="B5" s="39" t="inlineStr">
         <is>
-          <t>Prep</t>
+          <t>PORTION</t>
         </is>
       </c>
       <c r="C5" s="39" t="inlineStr">
         <is>
-          <t>Cook</t>
+          <t>SERVICE</t>
         </is>
       </c>
       <c r="D5" s="39" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>TIME</t>
         </is>
       </c>
     </row>
     <row r="6" ht="28" customHeight="1">
       <c r="A6" s="40" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>4 portions</t>
         </is>
       </c>
       <c r="B6" s="40" t="inlineStr">
         <is>
-          <t>10 min</t>
+          <t>1 portion</t>
         </is>
       </c>
       <c r="C6" s="40" t="inlineStr">
         <is>
-          <t>35 min</t>
+          <t>Hot or chilled</t>
         </is>
       </c>
       <c r="D6" s="40" t="inlineStr">
         <is>
-          <t>45 min</t>
+          <t>Prep 10 min · Cook 35 min</t>
         </is>
       </c>
     </row>
@@ -5173,34 +6980,187 @@
       <c r="C19" s="46" t="n"/>
       <c r="D19" s="46" t="n"/>
     </row>
-    <row r="20" ht="36" customHeight="1">
+    <row r="20" ht="66" customHeight="1">
       <c r="A20" s="47" t="n">
         <v>1</v>
       </c>
       <c r="B20" s="48" t="inlineStr">
         <is>
-          <t>Simmer in a steel pot.</t>
+          <t>Mise en place. Weigh every ingredient on this card for 4 portions. Set Heavy stainless steel milk pot — never aluminium. Wash produce. Confirm spice blends have no onion or garlic powder. No onion, no garlic, no aluminium.</t>
         </is>
       </c>
       <c r="C20" s="49" t="n"/>
       <c r="D20" s="49" t="n"/>
     </row>
+    <row r="21" ht="42" customHeight="1">
+      <c r="A21" s="32" t="n">
+        <v>2</v>
+      </c>
+      <c r="B21" s="30" t="inlineStr">
+        <is>
+          <t>Cut vegetables to even size so they cook together. Use a heavy stainless steel milk pot. Acidic or milk dishes must never touch aluminium.</t>
+        </is>
+      </c>
+      <c r="C21" s="31" t="n"/>
+      <c r="D21" s="31" t="n"/>
+    </row>
+    <row r="22" ht="54" customHeight="1">
+      <c r="A22" s="47" t="n">
+        <v>3</v>
+      </c>
+      <c r="B22" s="48" t="inlineStr">
+        <is>
+          <t>Simmer in a steel pot. Work in Heavy stainless steel milk pot — never aluminium. Cook to the doneness below, tasting salt at the end. Do not add onion, garlic or aluminium cookware.</t>
+        </is>
+      </c>
+      <c r="C22" s="49" t="n"/>
+      <c r="D22" s="49" t="n"/>
+    </row>
+    <row r="23" ht="42" customHeight="1">
+      <c r="A23" s="32" t="n">
+        <v>4</v>
+      </c>
+      <c r="B23" s="30" t="inlineStr">
+        <is>
+          <t>Doneness: mixture leaves the sides of the pan, or milk is thick enough to coat a spoon, or syrup has taken the stated string.</t>
+        </is>
+      </c>
+      <c r="C23" s="31" t="n"/>
+      <c r="D23" s="31" t="n"/>
+    </row>
+    <row r="24" ht="42" customHeight="1">
+      <c r="A24" s="47" t="n">
+        <v>5</v>
+      </c>
+      <c r="B24" s="48" t="inlineStr">
+        <is>
+          <t>Taste and adjust salt, lemon or chilli only — do not add onion or garlic at the finish. Garnish as listed. Yield is 4 portions.</t>
+        </is>
+      </c>
+      <c r="C24" s="49" t="n"/>
+      <c r="D24" s="49" t="n"/>
+    </row>
+    <row r="25" ht="42" customHeight="1">
+      <c r="A25" s="32" t="n">
+        <v>6</v>
+      </c>
+      <c r="B25" s="30" t="inlineStr">
+        <is>
+          <t>Hold as the dish is eaten — hot sweets in a bain of hot water, chilled sweets in the fridge. Label date and time. Service: Hot or chilled.</t>
+        </is>
+      </c>
+      <c r="C25" s="31" t="n"/>
+      <c r="D25" s="31" t="n"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="21" t="inlineStr">
+        <is>
+          <t>Nutrition per portion</t>
+        </is>
+      </c>
+      <c r="B27" s="22" t="n"/>
+      <c r="C27" s="22" t="n"/>
+      <c r="D27" s="22" t="n"/>
+    </row>
+    <row r="28" ht="36" customHeight="1">
+      <c r="A28" s="12" t="inlineStr">
+        <is>
+          <t>kcal 437  ·  Protein 12 g  ·  Carbs 77 g  ·  Fat 9 g  ·  Fibre 1 g. Nutrition is a kitchen estimate from typical produce values, not a laboratory analysis.</t>
+        </is>
+      </c>
+      <c r="B28" s="50" t="n"/>
+      <c r="C28" s="50" t="n"/>
+      <c r="D28" s="50" t="n"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="24" t="inlineStr">
+        <is>
+          <t>Allergens</t>
+        </is>
+      </c>
+      <c r="B29" s="6" t="n"/>
+      <c r="C29" s="6" t="n"/>
+      <c r="D29" s="6" t="n"/>
+    </row>
+    <row r="30" ht="48" customHeight="1">
+      <c r="A30" s="25" t="inlineStr">
+        <is>
+          <t>Milk · Always verify labels; this card is a kitchen estimate, not a lab certificate.</t>
+        </is>
+      </c>
+      <c r="B30" s="26" t="n"/>
+      <c r="C30" s="26" t="n"/>
+      <c r="D30" s="26" t="n"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="24" t="inlineStr">
+        <is>
+          <t>Chef notes</t>
+        </is>
+      </c>
+      <c r="B31" s="6" t="n"/>
+      <c r="C31" s="6" t="n"/>
+      <c r="D31" s="6" t="n"/>
+    </row>
+    <row r="32" ht="72" customHeight="1">
+      <c r="A32" s="25" t="inlineStr">
+        <is>
+          <t>For Rice Kheer: keep the mix slightly drier than you think; wet mixes split or go greasy. Bloom hing in hot fat 20–30 seconds; raw hing tastes medicinal. Commercial hing is often cut with wheat flour — use a gluten-free hing if you must mark Gluten Free. Never cook tomato, tamarind, lemon, yogurt or milk in aluminium; use stainless steel, iron, clay or glass. Spice blends: read the packet. Many garam masalas hide onion or garlic powder.</t>
+        </is>
+      </c>
+      <c r="B32" s="26" t="n"/>
+      <c r="C32" s="26" t="n"/>
+      <c r="D32" s="26" t="n"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="51" t="inlineStr">
+        <is>
+          <t>Service notes</t>
+        </is>
+      </c>
+      <c r="B33" s="52" t="n"/>
+      <c r="C33" s="52" t="n"/>
+      <c r="D33" s="52" t="n"/>
+    </row>
+    <row r="34" ht="64" customHeight="1">
+      <c r="A34" s="12" t="inlineStr">
+        <is>
+          <t>Serve in steel or glass bowls. If chilled, take out 5 minutes before the pass. Service temperature: Hot or chilled. Allergen label for this dish: Milk; Always verify labels; this card is a kitchen estimate, not a lab certificate. State clearly: vegetarian, no onion, no garlic, no eggs, no meat, no fish. Nutrition on this card is an estimate for 1 portion of 4.</t>
+        </is>
+      </c>
+      <c r="B34" s="50" t="n"/>
+      <c r="C34" s="50" t="n"/>
+      <c r="D34" s="50" t="n"/>
+    </row>
   </sheetData>
-  <mergeCells count="14">
+  <mergeCells count="27">
+    <mergeCell ref="A8:D8"/>
+    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="B23:D23"/>
+    <mergeCell ref="A29:D29"/>
+    <mergeCell ref="C14:D14"/>
+    <mergeCell ref="A28:D28"/>
+    <mergeCell ref="A9:D9"/>
+    <mergeCell ref="B19:D19"/>
+    <mergeCell ref="A31:D31"/>
+    <mergeCell ref="C16:D16"/>
+    <mergeCell ref="A34:D34"/>
+    <mergeCell ref="A30:D30"/>
+    <mergeCell ref="A11:D11"/>
+    <mergeCell ref="B24:D24"/>
+    <mergeCell ref="B20:D20"/>
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="C12:D12"/>
-    <mergeCell ref="A9:D9"/>
+    <mergeCell ref="B25:D25"/>
     <mergeCell ref="A18:D18"/>
-    <mergeCell ref="A8:D8"/>
-    <mergeCell ref="B19:D19"/>
-    <mergeCell ref="C16:D16"/>
-    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="A27:D27"/>
+    <mergeCell ref="B22:D22"/>
     <mergeCell ref="A3:D3"/>
-    <mergeCell ref="C14:D14"/>
     <mergeCell ref="C13:D13"/>
     <mergeCell ref="A2:D2"/>
-    <mergeCell ref="A11:D11"/>
-    <mergeCell ref="B20:D20"/>
+    <mergeCell ref="B21:D21"/>
+    <mergeCell ref="A33:D33"/>
+    <mergeCell ref="A32:D32"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" paperSize="9" fitToHeight="1" fitToWidth="1"/>
@@ -5214,7 +7174,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:D21"/>
+  <dimension ref="A1:D36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -5226,7 +7186,7 @@
     <row r="1" ht="32" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>RECIPE CARD  ·  Kokum Cucumber Salad</t>
+          <t>Parslia Kitchen OS · RECIPE CARD · Kokum Cucumber Salad</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -5236,7 +7196,7 @@
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>Goa kitchen  ·  Salad  ·  Goan Hindu vegetarian / sattvic</t>
+          <t>Pure Prasad · No onion · No garlic · No eggs · No meat · No fish  ·  Goa  ·  Salad</t>
         </is>
       </c>
       <c r="B2" s="4" t="n"/>
@@ -5256,44 +7216,44 @@
     <row r="5" ht="18" customHeight="1">
       <c r="A5" s="39" t="inlineStr">
         <is>
-          <t>Serves</t>
+          <t>YIELD</t>
         </is>
       </c>
       <c r="B5" s="39" t="inlineStr">
         <is>
-          <t>Prep</t>
+          <t>PORTION</t>
         </is>
       </c>
       <c r="C5" s="39" t="inlineStr">
         <is>
-          <t>Cook</t>
+          <t>SERVICE</t>
         </is>
       </c>
       <c r="D5" s="39" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>TIME</t>
         </is>
       </c>
     </row>
     <row r="6" ht="28" customHeight="1">
       <c r="A6" s="40" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>4 portions</t>
         </is>
       </c>
       <c r="B6" s="40" t="inlineStr">
         <is>
-          <t>8 min</t>
+          <t>1 portion</t>
         </is>
       </c>
       <c r="C6" s="40" t="inlineStr">
         <is>
-          <t>0 min</t>
+          <t>Cold</t>
         </is>
       </c>
       <c r="D6" s="40" t="inlineStr">
         <is>
-          <t>8 min</t>
+          <t>Prep 8 min · Cook 0 min</t>
         </is>
       </c>
     </row>
@@ -5459,35 +7419,201 @@
       <c r="C20" s="46" t="n"/>
       <c r="D20" s="46" t="n"/>
     </row>
-    <row r="21" ht="36" customHeight="1">
+    <row r="21" ht="54" customHeight="1">
       <c r="A21" s="47" t="n">
         <v>1</v>
       </c>
       <c r="B21" s="48" t="inlineStr">
         <is>
-          <t>Toss. Kokum replaces onion bite.</t>
+          <t>Mise en place. Weigh every ingredient on this card for 4 portions. Set Steel or glass bowl. Wash produce. Confirm spice blends have no onion or garlic powder. No onion, no garlic, no aluminium.</t>
         </is>
       </c>
       <c r="C21" s="49" t="n"/>
       <c r="D21" s="49" t="n"/>
     </row>
+    <row r="22" ht="36" customHeight="1">
+      <c r="A22" s="32" t="n">
+        <v>2</v>
+      </c>
+      <c r="B22" s="30" t="inlineStr">
+        <is>
+          <t>Cut vegetables to even size so they cook together.</t>
+        </is>
+      </c>
+      <c r="C22" s="31" t="n"/>
+      <c r="D22" s="31" t="n"/>
+    </row>
+    <row r="23" ht="42" customHeight="1">
+      <c r="A23" s="47" t="n">
+        <v>3</v>
+      </c>
+      <c r="B23" s="48" t="inlineStr">
+        <is>
+          <t>Toss. Work in Steel or glass bowl. Cook to the doneness below, tasting salt at the end. Do not add onion, garlic or aluminium cookware.</t>
+        </is>
+      </c>
+      <c r="C23" s="49" t="n"/>
+      <c r="D23" s="49" t="n"/>
+    </row>
+    <row r="24" ht="54" customHeight="1">
+      <c r="A24" s="32" t="n">
+        <v>4</v>
+      </c>
+      <c r="B24" s="30" t="inlineStr">
+        <is>
+          <t>Kokum replaces onion bite. Work in Steel or glass bowl. Cook to the doneness below, tasting salt at the end. Do not add onion, garlic or aluminium cookware.</t>
+        </is>
+      </c>
+      <c r="C24" s="31" t="n"/>
+      <c r="D24" s="31" t="n"/>
+    </row>
+    <row r="25" ht="42" customHeight="1">
+      <c r="A25" s="47" t="n">
+        <v>5</v>
+      </c>
+      <c r="B25" s="48" t="inlineStr">
+        <is>
+          <t>Doneness: vegetables stay crisp; dressing coats evenly; seasoning is bright, not flat.</t>
+        </is>
+      </c>
+      <c r="C25" s="49" t="n"/>
+      <c r="D25" s="49" t="n"/>
+    </row>
+    <row r="26" ht="42" customHeight="1">
+      <c r="A26" s="32" t="n">
+        <v>6</v>
+      </c>
+      <c r="B26" s="30" t="inlineStr">
+        <is>
+          <t>Taste and adjust salt, lemon or chilli only — do not add onion or garlic at the finish. Garnish as listed. Yield is 4 portions.</t>
+        </is>
+      </c>
+      <c r="C26" s="31" t="n"/>
+      <c r="D26" s="31" t="n"/>
+    </row>
+    <row r="27" ht="54" customHeight="1">
+      <c r="A27" s="47" t="n">
+        <v>7</v>
+      </c>
+      <c r="B27" s="48" t="inlineStr">
+        <is>
+          <t>Hold chilled, covered, up to 2 hours. Stir before service. Discard if it weeps heavily or smells sour beyond yogurt character. Service: Cold.</t>
+        </is>
+      </c>
+      <c r="C27" s="49" t="n"/>
+      <c r="D27" s="49" t="n"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="21" t="inlineStr">
+        <is>
+          <t>Nutrition per portion</t>
+        </is>
+      </c>
+      <c r="B29" s="22" t="n"/>
+      <c r="C29" s="22" t="n"/>
+      <c r="D29" s="22" t="n"/>
+    </row>
+    <row r="30" ht="36" customHeight="1">
+      <c r="A30" s="12" t="inlineStr">
+        <is>
+          <t>kcal 164  ·  Protein 6 g  ·  Carbs 26 g  ·  Fat 5 g  ·  Fibre 4 g. Nutrition is a kitchen estimate from typical produce values, not a laboratory analysis.</t>
+        </is>
+      </c>
+      <c r="B30" s="50" t="n"/>
+      <c r="C30" s="50" t="n"/>
+      <c r="D30" s="50" t="n"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="24" t="inlineStr">
+        <is>
+          <t>Allergens</t>
+        </is>
+      </c>
+      <c r="B31" s="6" t="n"/>
+      <c r="C31" s="6" t="n"/>
+      <c r="D31" s="6" t="n"/>
+    </row>
+    <row r="32" ht="48" customHeight="1">
+      <c r="A32" s="25" t="inlineStr">
+        <is>
+          <t>Milk · Always verify labels; this card is a kitchen estimate, not a lab certificate.</t>
+        </is>
+      </c>
+      <c r="B32" s="26" t="n"/>
+      <c r="C32" s="26" t="n"/>
+      <c r="D32" s="26" t="n"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="24" t="inlineStr">
+        <is>
+          <t>Chef notes</t>
+        </is>
+      </c>
+      <c r="B33" s="6" t="n"/>
+      <c r="C33" s="6" t="n"/>
+      <c r="D33" s="6" t="n"/>
+    </row>
+    <row r="34" ht="72" customHeight="1">
+      <c r="A34" s="25" t="inlineStr">
+        <is>
+          <t>For Kokum Cucumber Salad: squeeze wet vegetables dry or the bowl weeps on the pass. Season slightly higher than you think — cold dulls salt. No onion, no garlic, no allium garnish. Use steel or glass, never aluminium. Dress at the last minute. Verify dahi and spice labels.</t>
+        </is>
+      </c>
+      <c r="B34" s="26" t="n"/>
+      <c r="C34" s="26" t="n"/>
+      <c r="D34" s="26" t="n"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="51" t="inlineStr">
+        <is>
+          <t>Service notes</t>
+        </is>
+      </c>
+      <c r="B35" s="52" t="n"/>
+      <c r="C35" s="52" t="n"/>
+      <c r="D35" s="52" t="n"/>
+    </row>
+    <row r="36" ht="64" customHeight="1">
+      <c r="A36" s="12" t="inlineStr">
+        <is>
+          <t>Dress at the last minute. Toss at the pass, do not send a wet bowl. Service temperature: Cold. Allergen label for this dish: Milk; Always verify labels; this card is a kitchen estimate, not a lab certificate. State clearly: vegetarian, no onion, no garlic, no eggs, no meat, no fish. Nutrition on this card is an estimate for 1 portion of 4.</t>
+        </is>
+      </c>
+      <c r="B36" s="50" t="n"/>
+      <c r="C36" s="50" t="n"/>
+      <c r="D36" s="50" t="n"/>
+    </row>
   </sheetData>
-  <mergeCells count="15">
+  <mergeCells count="29">
+    <mergeCell ref="A8:D8"/>
+    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="B23:D23"/>
+    <mergeCell ref="A35:D35"/>
+    <mergeCell ref="A29:D29"/>
+    <mergeCell ref="C14:D14"/>
+    <mergeCell ref="A19:D19"/>
+    <mergeCell ref="A9:D9"/>
+    <mergeCell ref="A31:D31"/>
+    <mergeCell ref="C16:D16"/>
+    <mergeCell ref="A34:D34"/>
+    <mergeCell ref="A30:D30"/>
+    <mergeCell ref="A11:D11"/>
+    <mergeCell ref="B24:D24"/>
+    <mergeCell ref="A36:D36"/>
+    <mergeCell ref="B20:D20"/>
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="C12:D12"/>
-    <mergeCell ref="A9:D9"/>
-    <mergeCell ref="A8:D8"/>
-    <mergeCell ref="C16:D16"/>
-    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="B26:D26"/>
+    <mergeCell ref="B25:D25"/>
+    <mergeCell ref="C17:D17"/>
+    <mergeCell ref="B22:D22"/>
     <mergeCell ref="A3:D3"/>
-    <mergeCell ref="C14:D14"/>
+    <mergeCell ref="B27:D27"/>
     <mergeCell ref="C13:D13"/>
     <mergeCell ref="A2:D2"/>
-    <mergeCell ref="A11:D11"/>
-    <mergeCell ref="A19:D19"/>
     <mergeCell ref="B21:D21"/>
-    <mergeCell ref="C17:D17"/>
-    <mergeCell ref="B20:D20"/>
+    <mergeCell ref="A33:D33"/>
+    <mergeCell ref="A32:D32"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" paperSize="9" fitToHeight="1" fitToWidth="1"/>
@@ -5501,7 +7627,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:D21"/>
+  <dimension ref="A1:D35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -5513,7 +7639,7 @@
     <row r="1" ht="32" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>RECIPE CARD  ·  Kachumber without Onion</t>
+          <t>Parslia Kitchen OS · RECIPE CARD · Kachumber without Onion</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -5523,7 +7649,7 @@
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>Goa kitchen  ·  Salad  ·  Goan Hindu vegetarian / sattvic</t>
+          <t>Pure Prasad · No onion · No garlic · No eggs · No meat · No fish  ·  Goa  ·  Salad</t>
         </is>
       </c>
       <c r="B2" s="4" t="n"/>
@@ -5543,44 +7669,44 @@
     <row r="5" ht="18" customHeight="1">
       <c r="A5" s="39" t="inlineStr">
         <is>
-          <t>Serves</t>
+          <t>YIELD</t>
         </is>
       </c>
       <c r="B5" s="39" t="inlineStr">
         <is>
-          <t>Prep</t>
+          <t>PORTION</t>
         </is>
       </c>
       <c r="C5" s="39" t="inlineStr">
         <is>
-          <t>Cook</t>
+          <t>SERVICE</t>
         </is>
       </c>
       <c r="D5" s="39" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>TIME</t>
         </is>
       </c>
     </row>
     <row r="6" ht="28" customHeight="1">
       <c r="A6" s="40" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>4 portions</t>
         </is>
       </c>
       <c r="B6" s="40" t="inlineStr">
         <is>
-          <t>8 min</t>
+          <t>1 portion</t>
         </is>
       </c>
       <c r="C6" s="40" t="inlineStr">
         <is>
-          <t>0 min</t>
+          <t>Cold</t>
         </is>
       </c>
       <c r="D6" s="40" t="inlineStr">
         <is>
-          <t>8 min</t>
+          <t>Prep 8 min · Cook 0 min</t>
         </is>
       </c>
     </row>
@@ -5746,35 +7872,188 @@
       <c r="C20" s="46" t="n"/>
       <c r="D20" s="46" t="n"/>
     </row>
-    <row r="21" ht="36" customHeight="1">
+    <row r="21" ht="54" customHeight="1">
       <c r="A21" s="47" t="n">
         <v>1</v>
       </c>
       <c r="B21" s="48" t="inlineStr">
         <is>
-          <t>Toss.</t>
+          <t>Mise en place. Weigh every ingredient on this card for 4 portions. Set Steel or glass bowl. Wash produce. Confirm spice blends have no onion or garlic powder. No onion, no garlic, no aluminium.</t>
         </is>
       </c>
       <c r="C21" s="49" t="n"/>
       <c r="D21" s="49" t="n"/>
     </row>
+    <row r="22" ht="36" customHeight="1">
+      <c r="A22" s="32" t="n">
+        <v>2</v>
+      </c>
+      <c r="B22" s="30" t="inlineStr">
+        <is>
+          <t>Cut vegetables to even size so they cook together.</t>
+        </is>
+      </c>
+      <c r="C22" s="31" t="n"/>
+      <c r="D22" s="31" t="n"/>
+    </row>
+    <row r="23" ht="42" customHeight="1">
+      <c r="A23" s="47" t="n">
+        <v>3</v>
+      </c>
+      <c r="B23" s="48" t="inlineStr">
+        <is>
+          <t>Toss. Work in Steel or glass bowl. Cook to the doneness below, tasting salt at the end. Do not add onion, garlic or aluminium cookware.</t>
+        </is>
+      </c>
+      <c r="C23" s="49" t="n"/>
+      <c r="D23" s="49" t="n"/>
+    </row>
+    <row r="24" ht="42" customHeight="1">
+      <c r="A24" s="32" t="n">
+        <v>4</v>
+      </c>
+      <c r="B24" s="30" t="inlineStr">
+        <is>
+          <t>Doneness: vegetables stay crisp; dressing coats evenly; seasoning is bright, not flat.</t>
+        </is>
+      </c>
+      <c r="C24" s="31" t="n"/>
+      <c r="D24" s="31" t="n"/>
+    </row>
+    <row r="25" ht="42" customHeight="1">
+      <c r="A25" s="47" t="n">
+        <v>5</v>
+      </c>
+      <c r="B25" s="48" t="inlineStr">
+        <is>
+          <t>Taste and adjust salt, lemon or chilli only — do not add onion or garlic at the finish. Garnish as listed. Yield is 4 portions.</t>
+        </is>
+      </c>
+      <c r="C25" s="49" t="n"/>
+      <c r="D25" s="49" t="n"/>
+    </row>
+    <row r="26" ht="54" customHeight="1">
+      <c r="A26" s="32" t="n">
+        <v>6</v>
+      </c>
+      <c r="B26" s="30" t="inlineStr">
+        <is>
+          <t>Hold chilled, covered, up to 2 hours. Stir before service. Discard if it weeps heavily or smells sour beyond yogurt character. Service: Cold.</t>
+        </is>
+      </c>
+      <c r="C26" s="31" t="n"/>
+      <c r="D26" s="31" t="n"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="21" t="inlineStr">
+        <is>
+          <t>Nutrition per portion</t>
+        </is>
+      </c>
+      <c r="B28" s="22" t="n"/>
+      <c r="C28" s="22" t="n"/>
+      <c r="D28" s="22" t="n"/>
+    </row>
+    <row r="29" ht="36" customHeight="1">
+      <c r="A29" s="12" t="inlineStr">
+        <is>
+          <t>kcal 24  ·  Protein 1 g  ·  Carbs 6 g  ·  Fat 0 g  ·  Fibre 1 g. Nutrition is a kitchen estimate from typical produce values, not a laboratory analysis.</t>
+        </is>
+      </c>
+      <c r="B29" s="50" t="n"/>
+      <c r="C29" s="50" t="n"/>
+      <c r="D29" s="50" t="n"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="24" t="inlineStr">
+        <is>
+          <t>Allergens</t>
+        </is>
+      </c>
+      <c r="B30" s="6" t="n"/>
+      <c r="C30" s="6" t="n"/>
+      <c r="D30" s="6" t="n"/>
+    </row>
+    <row r="31" ht="48" customHeight="1">
+      <c r="A31" s="25" t="inlineStr">
+        <is>
+          <t>Milk · Always verify labels; this card is a kitchen estimate, not a lab certificate.</t>
+        </is>
+      </c>
+      <c r="B31" s="26" t="n"/>
+      <c r="C31" s="26" t="n"/>
+      <c r="D31" s="26" t="n"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="24" t="inlineStr">
+        <is>
+          <t>Chef notes</t>
+        </is>
+      </c>
+      <c r="B32" s="6" t="n"/>
+      <c r="C32" s="6" t="n"/>
+      <c r="D32" s="6" t="n"/>
+    </row>
+    <row r="33" ht="72" customHeight="1">
+      <c r="A33" s="25" t="inlineStr">
+        <is>
+          <t>For Kachumber without Onion: squeeze wet vegetables dry or the bowl weeps on the pass. Season slightly higher than you think — cold dulls salt. No onion, no garlic, no allium garnish. Use steel or glass, never aluminium. Dress at the last minute. Verify dahi and spice labels.</t>
+        </is>
+      </c>
+      <c r="B33" s="26" t="n"/>
+      <c r="C33" s="26" t="n"/>
+      <c r="D33" s="26" t="n"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="51" t="inlineStr">
+        <is>
+          <t>Service notes</t>
+        </is>
+      </c>
+      <c r="B34" s="52" t="n"/>
+      <c r="C34" s="52" t="n"/>
+      <c r="D34" s="52" t="n"/>
+    </row>
+    <row r="35" ht="64" customHeight="1">
+      <c r="A35" s="12" t="inlineStr">
+        <is>
+          <t>Dress at the last minute. Toss at the pass, do not send a wet bowl. Service temperature: Cold. Allergen label for this dish: Milk; Always verify labels; this card is a kitchen estimate, not a lab certificate. State clearly: vegetarian, no onion, no garlic, no eggs, no meat, no fish. Nutrition on this card is an estimate for 1 portion of 4.</t>
+        </is>
+      </c>
+      <c r="B35" s="50" t="n"/>
+      <c r="C35" s="50" t="n"/>
+      <c r="D35" s="50" t="n"/>
+    </row>
   </sheetData>
-  <mergeCells count="15">
+  <mergeCells count="28">
+    <mergeCell ref="A8:D8"/>
+    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="B23:D23"/>
+    <mergeCell ref="A35:D35"/>
+    <mergeCell ref="A29:D29"/>
+    <mergeCell ref="C14:D14"/>
+    <mergeCell ref="A19:D19"/>
+    <mergeCell ref="A28:D28"/>
+    <mergeCell ref="A9:D9"/>
+    <mergeCell ref="A31:D31"/>
+    <mergeCell ref="C16:D16"/>
+    <mergeCell ref="A34:D34"/>
+    <mergeCell ref="A30:D30"/>
+    <mergeCell ref="A11:D11"/>
+    <mergeCell ref="B24:D24"/>
+    <mergeCell ref="B20:D20"/>
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="C12:D12"/>
-    <mergeCell ref="A9:D9"/>
-    <mergeCell ref="A8:D8"/>
-    <mergeCell ref="C16:D16"/>
-    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="B26:D26"/>
+    <mergeCell ref="B25:D25"/>
+    <mergeCell ref="C17:D17"/>
+    <mergeCell ref="B22:D22"/>
     <mergeCell ref="A3:D3"/>
-    <mergeCell ref="C14:D14"/>
     <mergeCell ref="C13:D13"/>
     <mergeCell ref="A2:D2"/>
-    <mergeCell ref="A11:D11"/>
-    <mergeCell ref="A19:D19"/>
     <mergeCell ref="B21:D21"/>
-    <mergeCell ref="C17:D17"/>
-    <mergeCell ref="B20:D20"/>
+    <mergeCell ref="A33:D33"/>
+    <mergeCell ref="A32:D32"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" paperSize="9" fitToHeight="1" fitToWidth="1"/>
@@ -5788,7 +8067,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:D21"/>
+  <dimension ref="A1:D36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -5800,7 +8079,7 @@
     <row r="1" ht="32" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>RECIPE CARD  ·  Raw Mango Coconut Salad</t>
+          <t>Parslia Kitchen OS · RECIPE CARD · Raw Mango Coconut Salad</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -5810,7 +8089,7 @@
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>Goa kitchen  ·  Salad  ·  Goan Hindu vegetarian / sattvic</t>
+          <t>Pure Prasad · No onion · No garlic · No eggs · No meat · No fish  ·  Goa  ·  Salad</t>
         </is>
       </c>
       <c r="B2" s="4" t="n"/>
@@ -5830,44 +8109,44 @@
     <row r="5" ht="18" customHeight="1">
       <c r="A5" s="39" t="inlineStr">
         <is>
-          <t>Serves</t>
+          <t>YIELD</t>
         </is>
       </c>
       <c r="B5" s="39" t="inlineStr">
         <is>
-          <t>Prep</t>
+          <t>PORTION</t>
         </is>
       </c>
       <c r="C5" s="39" t="inlineStr">
         <is>
-          <t>Cook</t>
+          <t>SERVICE</t>
         </is>
       </c>
       <c r="D5" s="39" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>TIME</t>
         </is>
       </c>
     </row>
     <row r="6" ht="28" customHeight="1">
       <c r="A6" s="40" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>4 portions</t>
         </is>
       </c>
       <c r="B6" s="40" t="inlineStr">
         <is>
-          <t>10 min</t>
+          <t>1 portion</t>
         </is>
       </c>
       <c r="C6" s="40" t="inlineStr">
         <is>
-          <t>0 min</t>
+          <t>Cold</t>
         </is>
       </c>
       <c r="D6" s="40" t="inlineStr">
         <is>
-          <t>10 min</t>
+          <t>Prep 10 min · Cook 0 min</t>
         </is>
       </c>
     </row>
@@ -6033,35 +8312,201 @@
       <c r="C20" s="46" t="n"/>
       <c r="D20" s="46" t="n"/>
     </row>
-    <row r="21" ht="36" customHeight="1">
+    <row r="21" ht="54" customHeight="1">
       <c r="A21" s="47" t="n">
         <v>1</v>
       </c>
       <c r="B21" s="48" t="inlineStr">
         <is>
-          <t>Toss. Rest 5 minutes.</t>
+          <t>Mise en place. Weigh every ingredient on this card for 4 portions. Set Steel or glass bowl. Wash produce. Confirm spice blends have no onion or garlic powder. No onion, no garlic, no aluminium.</t>
         </is>
       </c>
       <c r="C21" s="49" t="n"/>
       <c r="D21" s="49" t="n"/>
     </row>
+    <row r="22" ht="36" customHeight="1">
+      <c r="A22" s="32" t="n">
+        <v>2</v>
+      </c>
+      <c r="B22" s="30" t="inlineStr">
+        <is>
+          <t>Cut vegetables to even size so they cook together.</t>
+        </is>
+      </c>
+      <c r="C22" s="31" t="n"/>
+      <c r="D22" s="31" t="n"/>
+    </row>
+    <row r="23" ht="42" customHeight="1">
+      <c r="A23" s="47" t="n">
+        <v>3</v>
+      </c>
+      <c r="B23" s="48" t="inlineStr">
+        <is>
+          <t>Toss. Work in Steel or glass bowl. Cook to the doneness below, tasting salt at the end. Do not add onion, garlic or aluminium cookware.</t>
+        </is>
+      </c>
+      <c r="C23" s="49" t="n"/>
+      <c r="D23" s="49" t="n"/>
+    </row>
+    <row r="24" ht="54" customHeight="1">
+      <c r="A24" s="32" t="n">
+        <v>4</v>
+      </c>
+      <c r="B24" s="30" t="inlineStr">
+        <is>
+          <t>Rest 5 minutes. Work in Steel or glass bowl. Cook to the doneness below, tasting salt at the end. Do not add onion, garlic or aluminium cookware.</t>
+        </is>
+      </c>
+      <c r="C24" s="31" t="n"/>
+      <c r="D24" s="31" t="n"/>
+    </row>
+    <row r="25" ht="42" customHeight="1">
+      <c r="A25" s="47" t="n">
+        <v>5</v>
+      </c>
+      <c r="B25" s="48" t="inlineStr">
+        <is>
+          <t>Doneness: vegetables stay crisp; dressing coats evenly; seasoning is bright, not flat.</t>
+        </is>
+      </c>
+      <c r="C25" s="49" t="n"/>
+      <c r="D25" s="49" t="n"/>
+    </row>
+    <row r="26" ht="42" customHeight="1">
+      <c r="A26" s="32" t="n">
+        <v>6</v>
+      </c>
+      <c r="B26" s="30" t="inlineStr">
+        <is>
+          <t>Taste and adjust salt, lemon or chilli only — do not add onion or garlic at the finish. Garnish as listed. Yield is 4 portions.</t>
+        </is>
+      </c>
+      <c r="C26" s="31" t="n"/>
+      <c r="D26" s="31" t="n"/>
+    </row>
+    <row r="27" ht="54" customHeight="1">
+      <c r="A27" s="47" t="n">
+        <v>7</v>
+      </c>
+      <c r="B27" s="48" t="inlineStr">
+        <is>
+          <t>Hold chilled, covered, up to 2 hours. Stir before service. Discard if it weeps heavily or smells sour beyond yogurt character. Service: Cold.</t>
+        </is>
+      </c>
+      <c r="C27" s="49" t="n"/>
+      <c r="D27" s="49" t="n"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="21" t="inlineStr">
+        <is>
+          <t>Nutrition per portion</t>
+        </is>
+      </c>
+      <c r="B29" s="22" t="n"/>
+      <c r="C29" s="22" t="n"/>
+      <c r="D29" s="22" t="n"/>
+    </row>
+    <row r="30" ht="36" customHeight="1">
+      <c r="A30" s="12" t="inlineStr">
+        <is>
+          <t>kcal 120  ·  Protein 1 g  ·  Carbs 12 g  ·  Fat 8 g  ·  Fibre 3 g. Nutrition is a kitchen estimate from typical produce values, not a laboratory analysis.</t>
+        </is>
+      </c>
+      <c r="B30" s="50" t="n"/>
+      <c r="C30" s="50" t="n"/>
+      <c r="D30" s="50" t="n"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="24" t="inlineStr">
+        <is>
+          <t>Allergens</t>
+        </is>
+      </c>
+      <c r="B31" s="6" t="n"/>
+      <c r="C31" s="6" t="n"/>
+      <c r="D31" s="6" t="n"/>
+    </row>
+    <row r="32" ht="48" customHeight="1">
+      <c r="A32" s="25" t="inlineStr">
+        <is>
+          <t>Milk · Always verify labels; this card is a kitchen estimate, not a lab certificate.</t>
+        </is>
+      </c>
+      <c r="B32" s="26" t="n"/>
+      <c r="C32" s="26" t="n"/>
+      <c r="D32" s="26" t="n"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="24" t="inlineStr">
+        <is>
+          <t>Chef notes</t>
+        </is>
+      </c>
+      <c r="B33" s="6" t="n"/>
+      <c r="C33" s="6" t="n"/>
+      <c r="D33" s="6" t="n"/>
+    </row>
+    <row r="34" ht="72" customHeight="1">
+      <c r="A34" s="25" t="inlineStr">
+        <is>
+          <t>For Raw Mango Coconut Salad: squeeze wet vegetables dry or the bowl weeps on the pass. Season slightly higher than you think — cold dulls salt. No onion, no garlic, no allium garnish. Use steel or glass, never aluminium. Dress at the last minute. Verify dahi and spice labels.</t>
+        </is>
+      </c>
+      <c r="B34" s="26" t="n"/>
+      <c r="C34" s="26" t="n"/>
+      <c r="D34" s="26" t="n"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="51" t="inlineStr">
+        <is>
+          <t>Service notes</t>
+        </is>
+      </c>
+      <c r="B35" s="52" t="n"/>
+      <c r="C35" s="52" t="n"/>
+      <c r="D35" s="52" t="n"/>
+    </row>
+    <row r="36" ht="64" customHeight="1">
+      <c r="A36" s="12" t="inlineStr">
+        <is>
+          <t>Dress at the last minute. Toss at the pass, do not send a wet bowl. Service temperature: Cold. Allergen label for this dish: Milk; Always verify labels; this card is a kitchen estimate, not a lab certificate. State clearly: vegetarian, no onion, no garlic, no eggs, no meat, no fish. Nutrition on this card is an estimate for 1 portion of 4.</t>
+        </is>
+      </c>
+      <c r="B36" s="50" t="n"/>
+      <c r="C36" s="50" t="n"/>
+      <c r="D36" s="50" t="n"/>
+    </row>
   </sheetData>
-  <mergeCells count="15">
+  <mergeCells count="29">
+    <mergeCell ref="A8:D8"/>
+    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="B23:D23"/>
+    <mergeCell ref="A35:D35"/>
+    <mergeCell ref="A29:D29"/>
+    <mergeCell ref="C14:D14"/>
+    <mergeCell ref="A19:D19"/>
+    <mergeCell ref="A9:D9"/>
+    <mergeCell ref="A31:D31"/>
+    <mergeCell ref="C16:D16"/>
+    <mergeCell ref="A34:D34"/>
+    <mergeCell ref="A30:D30"/>
+    <mergeCell ref="A11:D11"/>
+    <mergeCell ref="B24:D24"/>
+    <mergeCell ref="A36:D36"/>
+    <mergeCell ref="B20:D20"/>
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="C12:D12"/>
-    <mergeCell ref="A9:D9"/>
-    <mergeCell ref="A8:D8"/>
-    <mergeCell ref="C16:D16"/>
-    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="B26:D26"/>
+    <mergeCell ref="B25:D25"/>
+    <mergeCell ref="C17:D17"/>
+    <mergeCell ref="B22:D22"/>
     <mergeCell ref="A3:D3"/>
-    <mergeCell ref="C14:D14"/>
+    <mergeCell ref="B27:D27"/>
     <mergeCell ref="C13:D13"/>
     <mergeCell ref="A2:D2"/>
-    <mergeCell ref="A11:D11"/>
-    <mergeCell ref="A19:D19"/>
     <mergeCell ref="B21:D21"/>
-    <mergeCell ref="C17:D17"/>
-    <mergeCell ref="B20:D20"/>
+    <mergeCell ref="A33:D33"/>
+    <mergeCell ref="A32:D32"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" paperSize="9" fitToHeight="1" fitToWidth="1"/>
@@ -9381,7 +11826,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:D23"/>
+  <dimension ref="A1:D38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -9393,7 +11838,7 @@
     <row r="1" ht="32" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>RECIPE CARD  ·  Coconut Cucumber Cutlets</t>
+          <t>Parslia Kitchen OS · RECIPE CARD · Coconut Cucumber Cutlets</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -9403,7 +11848,7 @@
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>Goa kitchen  ·  Starter  ·  Goan Hindu vegetarian / sattvic</t>
+          <t>Pure Prasad · No onion · No garlic · No eggs · No meat · No fish  ·  Goa  ·  Starter</t>
         </is>
       </c>
       <c r="B2" s="4" t="n"/>
@@ -9423,44 +11868,44 @@
     <row r="5" ht="18" customHeight="1">
       <c r="A5" s="39" t="inlineStr">
         <is>
-          <t>Serves</t>
+          <t>YIELD</t>
         </is>
       </c>
       <c r="B5" s="39" t="inlineStr">
         <is>
-          <t>Prep</t>
+          <t>PORTION</t>
         </is>
       </c>
       <c r="C5" s="39" t="inlineStr">
         <is>
-          <t>Cook</t>
+          <t>SERVICE</t>
         </is>
       </c>
       <c r="D5" s="39" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>TIME</t>
         </is>
       </c>
     </row>
     <row r="6" ht="28" customHeight="1">
       <c r="A6" s="40" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>4 portions</t>
         </is>
       </c>
       <c r="B6" s="40" t="inlineStr">
         <is>
-          <t>15 min</t>
+          <t>1 portion</t>
         </is>
       </c>
       <c r="C6" s="40" t="inlineStr">
         <is>
-          <t>15 min</t>
+          <t>Hot</t>
         </is>
       </c>
       <c r="D6" s="40" t="inlineStr">
         <is>
-          <t>30 min</t>
+          <t>Prep 15 min · Cook 15 min</t>
         </is>
       </c>
     </row>
@@ -9662,37 +12107,203 @@
       <c r="C22" s="46" t="n"/>
       <c r="D22" s="46" t="n"/>
     </row>
-    <row r="23" ht="36" customHeight="1">
+    <row r="23" ht="66" customHeight="1">
       <c r="A23" s="47" t="n">
         <v>1</v>
       </c>
       <c r="B23" s="48" t="inlineStr">
         <is>
-          <t>Mix, shape, pan-fry in a steel kadhai until brown.</t>
+          <t>Mise en place. Weigh every ingredient on this card for 4 portions. Set Steel kadhai for frying — never aluminium. Wash produce. Confirm spice blends have no onion or garlic powder. No onion, no garlic, no aluminium.</t>
         </is>
       </c>
       <c r="C23" s="49" t="n"/>
       <c r="D23" s="49" t="n"/>
     </row>
+    <row r="24" ht="36" customHeight="1">
+      <c r="A24" s="32" t="n">
+        <v>2</v>
+      </c>
+      <c r="B24" s="30" t="inlineStr">
+        <is>
+          <t>Cut vegetables to even size so they cook together.</t>
+        </is>
+      </c>
+      <c r="C24" s="31" t="n"/>
+      <c r="D24" s="31" t="n"/>
+    </row>
+    <row r="25" ht="54" customHeight="1">
+      <c r="A25" s="47" t="n">
+        <v>3</v>
+      </c>
+      <c r="B25" s="48" t="inlineStr">
+        <is>
+          <t>Heat fat in Steel kadhai for frying — never aluminium on medium. Bloom hing 20–30 seconds until fragrant — this is the onion-garlic stand-in. Do not burn it.</t>
+        </is>
+      </c>
+      <c r="C25" s="49" t="n"/>
+      <c r="D25" s="49" t="n"/>
+    </row>
+    <row r="26" ht="54" customHeight="1">
+      <c r="A26" s="32" t="n">
+        <v>4</v>
+      </c>
+      <c r="B26" s="30" t="inlineStr">
+        <is>
+          <t>Mix, shape, pan-fry in a steel kadhai until brown. Work in Steel kadhai for frying — never aluminium. Cook to the doneness below, tasting salt at the end. Do not add onion, garlic or aluminium cookware.</t>
+        </is>
+      </c>
+      <c r="C26" s="31" t="n"/>
+      <c r="D26" s="31" t="n"/>
+    </row>
+    <row r="27" ht="42" customHeight="1">
+      <c r="A27" s="47" t="n">
+        <v>5</v>
+      </c>
+      <c r="B27" s="48" t="inlineStr">
+        <is>
+          <t>Doneness: crust or crumb is set, centre is hot, no raw flour or potato taste. Drain on a steel rack, not paper in the fryer basket.</t>
+        </is>
+      </c>
+      <c r="C27" s="49" t="n"/>
+      <c r="D27" s="49" t="n"/>
+    </row>
+    <row r="28" ht="42" customHeight="1">
+      <c r="A28" s="32" t="n">
+        <v>6</v>
+      </c>
+      <c r="B28" s="30" t="inlineStr">
+        <is>
+          <t>Taste and adjust salt, lemon or chilli only — do not add onion or garlic at the finish. Garnish as listed. Yield is 4 portions.</t>
+        </is>
+      </c>
+      <c r="C28" s="31" t="n"/>
+      <c r="D28" s="31" t="n"/>
+    </row>
+    <row r="29" ht="42" customHeight="1">
+      <c r="A29" s="47" t="n">
+        <v>7</v>
+      </c>
+      <c r="B29" s="48" t="inlineStr">
+        <is>
+          <t>Hold hot above 63 C if the pass is delayed, or cool quickly and reheat once only to piping hot. Do not hold in aluminium. Service: Hot.</t>
+        </is>
+      </c>
+      <c r="C29" s="49" t="n"/>
+      <c r="D29" s="49" t="n"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="21" t="inlineStr">
+        <is>
+          <t>Nutrition per portion</t>
+        </is>
+      </c>
+      <c r="B31" s="22" t="n"/>
+      <c r="C31" s="22" t="n"/>
+      <c r="D31" s="22" t="n"/>
+    </row>
+    <row r="32" ht="36" customHeight="1">
+      <c r="A32" s="12" t="inlineStr">
+        <is>
+          <t>kcal 213  ·  Protein 2 g  ·  Carbs 9 g  ·  Fat 20 g  ·  Fibre 4 g. Nutrition is a kitchen estimate from typical produce values, not a laboratory analysis.</t>
+        </is>
+      </c>
+      <c r="B32" s="50" t="n"/>
+      <c r="C32" s="50" t="n"/>
+      <c r="D32" s="50" t="n"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="24" t="inlineStr">
+        <is>
+          <t>Allergens</t>
+        </is>
+      </c>
+      <c r="B33" s="6" t="n"/>
+      <c r="C33" s="6" t="n"/>
+      <c r="D33" s="6" t="n"/>
+    </row>
+    <row r="34" ht="48" customHeight="1">
+      <c r="A34" s="25" t="inlineStr">
+        <is>
+          <t>Gluten (wheat) · Always verify labels; this card is a kitchen estimate, not a lab certificate.</t>
+        </is>
+      </c>
+      <c r="B34" s="26" t="n"/>
+      <c r="C34" s="26" t="n"/>
+      <c r="D34" s="26" t="n"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="24" t="inlineStr">
+        <is>
+          <t>Chef notes</t>
+        </is>
+      </c>
+      <c r="B35" s="6" t="n"/>
+      <c r="C35" s="6" t="n"/>
+      <c r="D35" s="6" t="n"/>
+    </row>
+    <row r="36" ht="72" customHeight="1">
+      <c r="A36" s="25" t="inlineStr">
+        <is>
+          <t>For Coconut Cucumber Cutlets: keep the mix slightly drier than you think; wet mixes split or go greasy. Bloom hing in hot fat 20–30 seconds; raw hing tastes medicinal. Commercial hing is often cut with wheat flour — use a gluten-free hing if you must mark Gluten Free. Never cook tomato, tamarind, lemon, yogurt or milk in aluminium; use stainless steel, iron, clay or glass. Spice blends: read the packet. Many garam masalas hide onion or garlic powder. Cook or roast besan until the raw smell is gone.</t>
+        </is>
+      </c>
+      <c r="B36" s="26" t="n"/>
+      <c r="C36" s="26" t="n"/>
+      <c r="D36" s="26" t="n"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="51" t="inlineStr">
+        <is>
+          <t>Service notes</t>
+        </is>
+      </c>
+      <c r="B37" s="52" t="n"/>
+      <c r="C37" s="52" t="n"/>
+      <c r="D37" s="52" t="n"/>
+    </row>
+    <row r="38" ht="64" customHeight="1">
+      <c r="A38" s="12" t="inlineStr">
+        <is>
+          <t>Serve immediately while crisp or hot. Offer a chutney or raita that is also onion-garlic free. Service temperature: Hot. Allergen label for this dish: Gluten (wheat); Always verify labels; this card is a kitchen estimate, not a lab certificate. State clearly: vegetarian, no onion, no garlic, no eggs, no meat, no fish. Nutrition on this card is an estimate for 1 portion of 4.</t>
+        </is>
+      </c>
+      <c r="B38" s="50" t="n"/>
+      <c r="C38" s="50" t="n"/>
+      <c r="D38" s="50" t="n"/>
+    </row>
   </sheetData>
-  <mergeCells count="17">
+  <mergeCells count="31">
+    <mergeCell ref="A8:D8"/>
+    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="B23:D23"/>
+    <mergeCell ref="A35:D35"/>
+    <mergeCell ref="A38:D38"/>
+    <mergeCell ref="C14:D14"/>
+    <mergeCell ref="B29:D29"/>
+    <mergeCell ref="B28:D28"/>
+    <mergeCell ref="A9:D9"/>
+    <mergeCell ref="A31:D31"/>
+    <mergeCell ref="C16:D16"/>
+    <mergeCell ref="A34:D34"/>
+    <mergeCell ref="A11:D11"/>
+    <mergeCell ref="B24:D24"/>
+    <mergeCell ref="A36:D36"/>
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="C12:D12"/>
-    <mergeCell ref="A9:D9"/>
-    <mergeCell ref="A8:D8"/>
-    <mergeCell ref="C16:D16"/>
-    <mergeCell ref="C15:D15"/>
-    <mergeCell ref="B23:D23"/>
+    <mergeCell ref="B26:D26"/>
+    <mergeCell ref="B25:D25"/>
+    <mergeCell ref="C17:D17"/>
+    <mergeCell ref="A37:D37"/>
     <mergeCell ref="B22:D22"/>
     <mergeCell ref="A3:D3"/>
     <mergeCell ref="C19:D19"/>
     <mergeCell ref="A21:D21"/>
-    <mergeCell ref="C14:D14"/>
+    <mergeCell ref="B27:D27"/>
     <mergeCell ref="C13:D13"/>
     <mergeCell ref="A2:D2"/>
-    <mergeCell ref="A11:D11"/>
-    <mergeCell ref="C17:D17"/>
     <mergeCell ref="C18:D18"/>
+    <mergeCell ref="A33:D33"/>
+    <mergeCell ref="A32:D32"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" paperSize="9" fitToHeight="1" fitToWidth="1"/>
@@ -9706,7 +12317,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:D21"/>
+  <dimension ref="A1:D37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -9718,7 +12329,7 @@
     <row r="1" ht="32" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>RECIPE CARD  ·  Moong Ghavan</t>
+          <t>Parslia Kitchen OS · RECIPE CARD · Moong Ghavan</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -9728,7 +12339,7 @@
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>Goa kitchen  ·  Starter  ·  Goan Hindu vegetarian / sattvic</t>
+          <t>Pure Prasad · No onion · No garlic · No eggs · No meat · No fish  ·  Goa  ·  Starter</t>
         </is>
       </c>
       <c r="B2" s="4" t="n"/>
@@ -9748,44 +12359,44 @@
     <row r="5" ht="18" customHeight="1">
       <c r="A5" s="39" t="inlineStr">
         <is>
-          <t>Serves</t>
+          <t>YIELD</t>
         </is>
       </c>
       <c r="B5" s="39" t="inlineStr">
         <is>
-          <t>Prep</t>
+          <t>PORTION</t>
         </is>
       </c>
       <c r="C5" s="39" t="inlineStr">
         <is>
-          <t>Cook</t>
+          <t>SERVICE</t>
         </is>
       </c>
       <c r="D5" s="39" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>TIME</t>
         </is>
       </c>
     </row>
     <row r="6" ht="28" customHeight="1">
       <c r="A6" s="40" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>4 portions</t>
         </is>
       </c>
       <c r="B6" s="40" t="inlineStr">
         <is>
-          <t>20 min</t>
+          <t>1 portion</t>
         </is>
       </c>
       <c r="C6" s="40" t="inlineStr">
         <is>
-          <t>15 min</t>
+          <t>Hot</t>
         </is>
       </c>
       <c r="D6" s="40" t="inlineStr">
         <is>
-          <t>35 min</t>
+          <t>Prep 20 min · Cook 15 min</t>
         </is>
       </c>
     </row>
@@ -9951,35 +12562,214 @@
       <c r="C20" s="46" t="n"/>
       <c r="D20" s="46" t="n"/>
     </row>
-    <row r="21" ht="36" customHeight="1">
+    <row r="21" ht="54" customHeight="1">
       <c r="A21" s="47" t="n">
         <v>1</v>
       </c>
       <c r="B21" s="48" t="inlineStr">
         <is>
-          <t>Grind a thick batter. Spread on an iron tawa. Cook both sides.</t>
+          <t>Mise en place. Weigh every ingredient on this card for 4 portions. Set Cast-iron tawa (not aluminium). Wash produce. Confirm spice blends have no onion or garlic powder. No onion, no garlic, no aluminium.</t>
         </is>
       </c>
       <c r="C21" s="49" t="n"/>
       <c r="D21" s="49" t="n"/>
     </row>
+    <row r="22" ht="36" customHeight="1">
+      <c r="A22" s="32" t="n">
+        <v>2</v>
+      </c>
+      <c r="B22" s="30" t="inlineStr">
+        <is>
+          <t>Cut vegetables to even size so they cook together.</t>
+        </is>
+      </c>
+      <c r="C22" s="31" t="n"/>
+      <c r="D22" s="31" t="n"/>
+    </row>
+    <row r="23" ht="54" customHeight="1">
+      <c r="A23" s="47" t="n">
+        <v>3</v>
+      </c>
+      <c r="B23" s="48" t="inlineStr">
+        <is>
+          <t>Grind a thick batter. Work in Cast-iron tawa (not aluminium). Cook to the doneness below, tasting salt at the end. Do not add onion, garlic or aluminium cookware.</t>
+        </is>
+      </c>
+      <c r="C23" s="49" t="n"/>
+      <c r="D23" s="49" t="n"/>
+    </row>
+    <row r="24" ht="54" customHeight="1">
+      <c r="A24" s="32" t="n">
+        <v>4</v>
+      </c>
+      <c r="B24" s="30" t="inlineStr">
+        <is>
+          <t>Spread on an iron tawa. Work in Cast-iron tawa (not aluminium). Cook to the doneness below, tasting salt at the end. Do not add onion, garlic or aluminium cookware.</t>
+        </is>
+      </c>
+      <c r="C24" s="31" t="n"/>
+      <c r="D24" s="31" t="n"/>
+    </row>
+    <row r="25" ht="54" customHeight="1">
+      <c r="A25" s="47" t="n">
+        <v>5</v>
+      </c>
+      <c r="B25" s="48" t="inlineStr">
+        <is>
+          <t>Cook both sides. Work in Cast-iron tawa (not aluminium). Cook to the doneness below, tasting salt at the end. Do not add onion, garlic or aluminium cookware.</t>
+        </is>
+      </c>
+      <c r="C25" s="49" t="n"/>
+      <c r="D25" s="49" t="n"/>
+    </row>
+    <row r="26" ht="42" customHeight="1">
+      <c r="A26" s="32" t="n">
+        <v>6</v>
+      </c>
+      <c r="B26" s="30" t="inlineStr">
+        <is>
+          <t>Doneness: crust or crumb is set, centre is hot, no raw flour or potato taste. Drain on a steel rack, not paper in the fryer basket.</t>
+        </is>
+      </c>
+      <c r="C26" s="31" t="n"/>
+      <c r="D26" s="31" t="n"/>
+    </row>
+    <row r="27" ht="42" customHeight="1">
+      <c r="A27" s="47" t="n">
+        <v>7</v>
+      </c>
+      <c r="B27" s="48" t="inlineStr">
+        <is>
+          <t>Taste and adjust salt, lemon or chilli only — do not add onion or garlic at the finish. Garnish as listed. Yield is 4 portions.</t>
+        </is>
+      </c>
+      <c r="C27" s="49" t="n"/>
+      <c r="D27" s="49" t="n"/>
+    </row>
+    <row r="28" ht="42" customHeight="1">
+      <c r="A28" s="32" t="n">
+        <v>8</v>
+      </c>
+      <c r="B28" s="30" t="inlineStr">
+        <is>
+          <t>Hold hot above 63 C if the pass is delayed, or cool quickly and reheat once only to piping hot. Do not hold in aluminium. Service: Hot.</t>
+        </is>
+      </c>
+      <c r="C28" s="31" t="n"/>
+      <c r="D28" s="31" t="n"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="21" t="inlineStr">
+        <is>
+          <t>Nutrition per portion</t>
+        </is>
+      </c>
+      <c r="B30" s="22" t="n"/>
+      <c r="C30" s="22" t="n"/>
+      <c r="D30" s="22" t="n"/>
+    </row>
+    <row r="31" ht="36" customHeight="1">
+      <c r="A31" s="12" t="inlineStr">
+        <is>
+          <t>kcal 194  ·  Protein 9 g  ·  Carbs 24 g  ·  Fat 7 g  ·  Fibre 6 g. Nutrition is a kitchen estimate from typical produce values, not a laboratory analysis.</t>
+        </is>
+      </c>
+      <c r="B31" s="50" t="n"/>
+      <c r="C31" s="50" t="n"/>
+      <c r="D31" s="50" t="n"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="24" t="inlineStr">
+        <is>
+          <t>Allergens</t>
+        </is>
+      </c>
+      <c r="B32" s="6" t="n"/>
+      <c r="C32" s="6" t="n"/>
+      <c r="D32" s="6" t="n"/>
+    </row>
+    <row r="33" ht="48" customHeight="1">
+      <c r="A33" s="25" t="inlineStr">
+        <is>
+          <t>None identified in this spec — still verify hing brand (many contain wheat) and spice blends.</t>
+        </is>
+      </c>
+      <c r="B33" s="26" t="n"/>
+      <c r="C33" s="26" t="n"/>
+      <c r="D33" s="26" t="n"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="24" t="inlineStr">
+        <is>
+          <t>Chef notes</t>
+        </is>
+      </c>
+      <c r="B34" s="6" t="n"/>
+      <c r="C34" s="6" t="n"/>
+      <c r="D34" s="6" t="n"/>
+    </row>
+    <row r="35" ht="72" customHeight="1">
+      <c r="A35" s="25" t="inlineStr">
+        <is>
+          <t>For Moong Ghavan: keep the mix slightly drier than you think; wet mixes split or go greasy. Bloom hing in hot fat 20–30 seconds; raw hing tastes medicinal. Commercial hing is often cut with wheat flour — use a gluten-free hing if you must mark Gluten Free. Never cook tomato, tamarind, lemon, yogurt or milk in aluminium; use stainless steel, iron, clay or glass. Spice blends: read the packet. Many garam masalas hide onion or garlic powder.</t>
+        </is>
+      </c>
+      <c r="B35" s="26" t="n"/>
+      <c r="C35" s="26" t="n"/>
+      <c r="D35" s="26" t="n"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="51" t="inlineStr">
+        <is>
+          <t>Service notes</t>
+        </is>
+      </c>
+      <c r="B36" s="52" t="n"/>
+      <c r="C36" s="52" t="n"/>
+      <c r="D36" s="52" t="n"/>
+    </row>
+    <row r="37" ht="64" customHeight="1">
+      <c r="A37" s="12" t="inlineStr">
+        <is>
+          <t>Serve immediately while crisp or hot. Offer a chutney or raita that is also onion-garlic free. Service temperature: Hot. Allergen label for this dish: None identified in this spec — still verify hing brand (many contain wheat) and spice blends. State clearly: vegetarian, no onion, no garlic, no eggs, no meat, no fish. Nutrition on this card is an estimate for 1 portion of 4.</t>
+        </is>
+      </c>
+      <c r="B37" s="50" t="n"/>
+      <c r="C37" s="50" t="n"/>
+      <c r="D37" s="50" t="n"/>
+    </row>
   </sheetData>
-  <mergeCells count="15">
+  <mergeCells count="30">
+    <mergeCell ref="A8:D8"/>
+    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="B23:D23"/>
+    <mergeCell ref="A35:D35"/>
+    <mergeCell ref="C14:D14"/>
+    <mergeCell ref="A19:D19"/>
+    <mergeCell ref="B28:D28"/>
+    <mergeCell ref="A9:D9"/>
+    <mergeCell ref="A31:D31"/>
+    <mergeCell ref="C16:D16"/>
+    <mergeCell ref="A34:D34"/>
+    <mergeCell ref="A30:D30"/>
+    <mergeCell ref="A11:D11"/>
+    <mergeCell ref="B24:D24"/>
+    <mergeCell ref="A36:D36"/>
+    <mergeCell ref="B20:D20"/>
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="C12:D12"/>
-    <mergeCell ref="A9:D9"/>
-    <mergeCell ref="A8:D8"/>
-    <mergeCell ref="C16:D16"/>
-    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="B26:D26"/>
+    <mergeCell ref="B25:D25"/>
+    <mergeCell ref="C17:D17"/>
+    <mergeCell ref="A37:D37"/>
+    <mergeCell ref="B22:D22"/>
     <mergeCell ref="A3:D3"/>
-    <mergeCell ref="C14:D14"/>
+    <mergeCell ref="B27:D27"/>
     <mergeCell ref="C13:D13"/>
     <mergeCell ref="A2:D2"/>
-    <mergeCell ref="A11:D11"/>
-    <mergeCell ref="A19:D19"/>
     <mergeCell ref="B21:D21"/>
-    <mergeCell ref="C17:D17"/>
-    <mergeCell ref="B20:D20"/>
+    <mergeCell ref="A33:D33"/>
+    <mergeCell ref="A32:D32"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" paperSize="9" fitToHeight="1" fitToWidth="1"/>
@@ -9993,7 +12783,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:D22"/>
+  <dimension ref="A1:D37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -10005,7 +12795,7 @@
     <row r="1" ht="32" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>RECIPE CARD  ·  Jeev Kadgi Fritters</t>
+          <t>Parslia Kitchen OS · RECIPE CARD · Jeev Kadgi Fritters</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -10015,7 +12805,7 @@
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>Goa kitchen  ·  Starter  ·  Goan Hindu vegetarian / sattvic</t>
+          <t>Pure Prasad · No onion · No garlic · No eggs · No meat · No fish  ·  Goa  ·  Starter</t>
         </is>
       </c>
       <c r="B2" s="4" t="n"/>
@@ -10035,44 +12825,44 @@
     <row r="5" ht="18" customHeight="1">
       <c r="A5" s="39" t="inlineStr">
         <is>
-          <t>Serves</t>
+          <t>YIELD</t>
         </is>
       </c>
       <c r="B5" s="39" t="inlineStr">
         <is>
-          <t>Prep</t>
+          <t>PORTION</t>
         </is>
       </c>
       <c r="C5" s="39" t="inlineStr">
         <is>
-          <t>Cook</t>
+          <t>SERVICE</t>
         </is>
       </c>
       <c r="D5" s="39" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>TIME</t>
         </is>
       </c>
     </row>
     <row r="6" ht="28" customHeight="1">
       <c r="A6" s="40" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>4 portions</t>
         </is>
       </c>
       <c r="B6" s="40" t="inlineStr">
         <is>
-          <t>15 min</t>
+          <t>1 portion</t>
         </is>
       </c>
       <c r="C6" s="40" t="inlineStr">
         <is>
-          <t>15 min</t>
+          <t>Hot</t>
         </is>
       </c>
       <c r="D6" s="40" t="inlineStr">
         <is>
-          <t>30 min</t>
+          <t>Prep 15 min · Cook 15 min</t>
         </is>
       </c>
     </row>
@@ -10256,36 +13046,202 @@
       <c r="C21" s="46" t="n"/>
       <c r="D21" s="46" t="n"/>
     </row>
-    <row r="22" ht="36" customHeight="1">
+    <row r="22" ht="66" customHeight="1">
       <c r="A22" s="47" t="n">
         <v>1</v>
       </c>
       <c r="B22" s="48" t="inlineStr">
         <is>
-          <t>Dip and fry in steel until crisp. Serve with kokum dip.</t>
+          <t>Mise en place. Weigh every ingredient on this card for 4 portions. Set Steel kadhai for frying — never aluminium. Wash produce. Confirm spice blends have no onion or garlic powder. No onion, no garlic, no aluminium.</t>
         </is>
       </c>
       <c r="C22" s="49" t="n"/>
       <c r="D22" s="49" t="n"/>
     </row>
+    <row r="23" ht="36" customHeight="1">
+      <c r="A23" s="32" t="n">
+        <v>2</v>
+      </c>
+      <c r="B23" s="30" t="inlineStr">
+        <is>
+          <t>Cut vegetables to even size so they cook together.</t>
+        </is>
+      </c>
+      <c r="C23" s="31" t="n"/>
+      <c r="D23" s="31" t="n"/>
+    </row>
+    <row r="24" ht="54" customHeight="1">
+      <c r="A24" s="47" t="n">
+        <v>3</v>
+      </c>
+      <c r="B24" s="48" t="inlineStr">
+        <is>
+          <t>Dip and fry in steel until crisp. Work in Steel kadhai for frying — never aluminium. Cook to the doneness below, tasting salt at the end. Do not add onion, garlic or aluminium cookware.</t>
+        </is>
+      </c>
+      <c r="C24" s="49" t="n"/>
+      <c r="D24" s="49" t="n"/>
+    </row>
+    <row r="25" ht="54" customHeight="1">
+      <c r="A25" s="32" t="n">
+        <v>4</v>
+      </c>
+      <c r="B25" s="30" t="inlineStr">
+        <is>
+          <t>Serve with kokum dip. Work in Steel kadhai for frying — never aluminium. Cook to the doneness below, tasting salt at the end. Do not add onion, garlic or aluminium cookware.</t>
+        </is>
+      </c>
+      <c r="C25" s="31" t="n"/>
+      <c r="D25" s="31" t="n"/>
+    </row>
+    <row r="26" ht="42" customHeight="1">
+      <c r="A26" s="47" t="n">
+        <v>5</v>
+      </c>
+      <c r="B26" s="48" t="inlineStr">
+        <is>
+          <t>Doneness: crust or crumb is set, centre is hot, no raw flour or potato taste. Drain on a steel rack, not paper in the fryer basket.</t>
+        </is>
+      </c>
+      <c r="C26" s="49" t="n"/>
+      <c r="D26" s="49" t="n"/>
+    </row>
+    <row r="27" ht="42" customHeight="1">
+      <c r="A27" s="32" t="n">
+        <v>6</v>
+      </c>
+      <c r="B27" s="30" t="inlineStr">
+        <is>
+          <t>Taste and adjust salt, lemon or chilli only — do not add onion or garlic at the finish. Garnish as listed. Yield is 4 portions.</t>
+        </is>
+      </c>
+      <c r="C27" s="31" t="n"/>
+      <c r="D27" s="31" t="n"/>
+    </row>
+    <row r="28" ht="42" customHeight="1">
+      <c r="A28" s="47" t="n">
+        <v>7</v>
+      </c>
+      <c r="B28" s="48" t="inlineStr">
+        <is>
+          <t>Hold hot above 63 C if the pass is delayed, or cool quickly and reheat once only to piping hot. Do not hold in aluminium. Service: Hot.</t>
+        </is>
+      </c>
+      <c r="C28" s="49" t="n"/>
+      <c r="D28" s="49" t="n"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="21" t="inlineStr">
+        <is>
+          <t>Nutrition per portion</t>
+        </is>
+      </c>
+      <c r="B30" s="22" t="n"/>
+      <c r="C30" s="22" t="n"/>
+      <c r="D30" s="22" t="n"/>
+    </row>
+    <row r="31" ht="36" customHeight="1">
+      <c r="A31" s="12" t="inlineStr">
+        <is>
+          <t>kcal 171  ·  Protein 2 g  ·  Carbs 26 g  ·  Fat 7 g  ·  Fibre 2 g. Nutrition is a kitchen estimate from typical produce values, not a laboratory analysis.</t>
+        </is>
+      </c>
+      <c r="B31" s="50" t="n"/>
+      <c r="C31" s="50" t="n"/>
+      <c r="D31" s="50" t="n"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="24" t="inlineStr">
+        <is>
+          <t>Allergens</t>
+        </is>
+      </c>
+      <c r="B32" s="6" t="n"/>
+      <c r="C32" s="6" t="n"/>
+      <c r="D32" s="6" t="n"/>
+    </row>
+    <row r="33" ht="48" customHeight="1">
+      <c r="A33" s="25" t="inlineStr">
+        <is>
+          <t>None identified in this spec — still verify hing brand (many contain wheat) and spice blends.</t>
+        </is>
+      </c>
+      <c r="B33" s="26" t="n"/>
+      <c r="C33" s="26" t="n"/>
+      <c r="D33" s="26" t="n"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="24" t="inlineStr">
+        <is>
+          <t>Chef notes</t>
+        </is>
+      </c>
+      <c r="B34" s="6" t="n"/>
+      <c r="C34" s="6" t="n"/>
+      <c r="D34" s="6" t="n"/>
+    </row>
+    <row r="35" ht="72" customHeight="1">
+      <c r="A35" s="25" t="inlineStr">
+        <is>
+          <t>For Jeev Kadgi Fritters: keep the mix slightly drier than you think; wet mixes split or go greasy. Bloom hing in hot fat 20–30 seconds; raw hing tastes medicinal. Commercial hing is often cut with wheat flour — use a gluten-free hing if you must mark Gluten Free. Never cook tomato, tamarind, lemon, yogurt or milk in aluminium; use stainless steel, iron, clay or glass. Spice blends: read the packet. Many garam masalas hide onion or garlic powder.</t>
+        </is>
+      </c>
+      <c r="B35" s="26" t="n"/>
+      <c r="C35" s="26" t="n"/>
+      <c r="D35" s="26" t="n"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="51" t="inlineStr">
+        <is>
+          <t>Service notes</t>
+        </is>
+      </c>
+      <c r="B36" s="52" t="n"/>
+      <c r="C36" s="52" t="n"/>
+      <c r="D36" s="52" t="n"/>
+    </row>
+    <row r="37" ht="64" customHeight="1">
+      <c r="A37" s="12" t="inlineStr">
+        <is>
+          <t>Serve immediately while crisp or hot. Offer a chutney or raita that is also onion-garlic free. Service temperature: Hot. Allergen label for this dish: None identified in this spec — still verify hing brand (many contain wheat) and spice blends. State clearly: vegetarian, no onion, no garlic, no eggs, no meat, no fish. Nutrition on this card is an estimate for 1 portion of 4.</t>
+        </is>
+      </c>
+      <c r="B37" s="50" t="n"/>
+      <c r="C37" s="50" t="n"/>
+      <c r="D37" s="50" t="n"/>
+    </row>
   </sheetData>
-  <mergeCells count="16">
+  <mergeCells count="30">
+    <mergeCell ref="A8:D8"/>
+    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="B23:D23"/>
+    <mergeCell ref="A35:D35"/>
+    <mergeCell ref="A20:D20"/>
+    <mergeCell ref="C14:D14"/>
+    <mergeCell ref="C18:D18"/>
+    <mergeCell ref="B28:D28"/>
+    <mergeCell ref="A9:D9"/>
+    <mergeCell ref="A31:D31"/>
+    <mergeCell ref="C16:D16"/>
+    <mergeCell ref="A34:D34"/>
+    <mergeCell ref="A30:D30"/>
+    <mergeCell ref="A11:D11"/>
+    <mergeCell ref="B24:D24"/>
+    <mergeCell ref="A36:D36"/>
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="C12:D12"/>
-    <mergeCell ref="A9:D9"/>
-    <mergeCell ref="A8:D8"/>
-    <mergeCell ref="C16:D16"/>
-    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="B26:D26"/>
+    <mergeCell ref="B25:D25"/>
+    <mergeCell ref="C17:D17"/>
+    <mergeCell ref="A37:D37"/>
     <mergeCell ref="B22:D22"/>
     <mergeCell ref="A3:D3"/>
-    <mergeCell ref="A20:D20"/>
-    <mergeCell ref="C14:D14"/>
+    <mergeCell ref="B27:D27"/>
     <mergeCell ref="C13:D13"/>
     <mergeCell ref="A2:D2"/>
-    <mergeCell ref="A11:D11"/>
     <mergeCell ref="B21:D21"/>
-    <mergeCell ref="C17:D17"/>
-    <mergeCell ref="C18:D18"/>
+    <mergeCell ref="A33:D33"/>
+    <mergeCell ref="A32:D32"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" paperSize="9" fitToHeight="1" fitToWidth="1"/>
@@ -10299,7 +13255,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:D24"/>
+  <dimension ref="A1:D41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -10311,7 +13267,7 @@
     <row r="1" ht="32" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>RECIPE CARD  ·  Khatkhate</t>
+          <t>Parslia Kitchen OS · RECIPE CARD · Khatkhate</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -10321,7 +13277,7 @@
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>Goa kitchen  ·  Main  ·  Goan Hindu vegetarian / sattvic</t>
+          <t>Pure Prasad · No onion · No garlic · No eggs · No meat · No fish  ·  Goa  ·  Main</t>
         </is>
       </c>
       <c r="B2" s="4" t="n"/>
@@ -10341,44 +13297,44 @@
     <row r="5" ht="18" customHeight="1">
       <c r="A5" s="39" t="inlineStr">
         <is>
-          <t>Serves</t>
+          <t>YIELD</t>
         </is>
       </c>
       <c r="B5" s="39" t="inlineStr">
         <is>
-          <t>Prep</t>
+          <t>PORTION</t>
         </is>
       </c>
       <c r="C5" s="39" t="inlineStr">
         <is>
-          <t>Cook</t>
+          <t>SERVICE</t>
         </is>
       </c>
       <c r="D5" s="39" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>TIME</t>
         </is>
       </c>
     </row>
     <row r="6" ht="28" customHeight="1">
       <c r="A6" s="40" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>4 portions</t>
         </is>
       </c>
       <c r="B6" s="40" t="inlineStr">
         <is>
-          <t>15 min</t>
+          <t>1 portion</t>
         </is>
       </c>
       <c r="C6" s="40" t="inlineStr">
         <is>
-          <t>30 min</t>
+          <t>Hot</t>
         </is>
       </c>
       <c r="D6" s="40" t="inlineStr">
         <is>
-          <t>45 min</t>
+          <t>Prep 15 min · Cook 30 min</t>
         </is>
       </c>
     </row>
@@ -10598,38 +13554,230 @@
       <c r="C23" s="46" t="n"/>
       <c r="D23" s="46" t="n"/>
     </row>
-    <row r="24" ht="42" customHeight="1">
+    <row r="24" ht="66" customHeight="1">
       <c r="A24" s="47" t="n">
         <v>1</v>
       </c>
       <c r="B24" s="48" t="inlineStr">
         <is>
-          <t>Cook veg with tamarind. Add coconut paste. Temper mustard, hing, curry leaves.</t>
+          <t>Mise en place. Weigh every ingredient on this card for 4 portions. Set Stainless steel kadhai or saucepan — never aluminium. Wash produce. Confirm spice blends have no onion or garlic powder. No onion, no garlic, no aluminium.</t>
         </is>
       </c>
       <c r="C24" s="49" t="n"/>
       <c r="D24" s="49" t="n"/>
     </row>
+    <row r="25" ht="36" customHeight="1">
+      <c r="A25" s="32" t="n">
+        <v>2</v>
+      </c>
+      <c r="B25" s="30" t="inlineStr">
+        <is>
+          <t>Cut vegetables to even size so they cook together.</t>
+        </is>
+      </c>
+      <c r="C25" s="31" t="n"/>
+      <c r="D25" s="31" t="n"/>
+    </row>
+    <row r="26" ht="54" customHeight="1">
+      <c r="A26" s="47" t="n">
+        <v>3</v>
+      </c>
+      <c r="B26" s="48" t="inlineStr">
+        <is>
+          <t>Heat fat in Stainless steel kadhai or saucepan — never aluminium on medium. Bloom hing 20–30 seconds until fragrant — this is the onion-garlic stand-in. Do not burn it.</t>
+        </is>
+      </c>
+      <c r="C26" s="49" t="n"/>
+      <c r="D26" s="49" t="n"/>
+    </row>
+    <row r="27" ht="54" customHeight="1">
+      <c r="A27" s="32" t="n">
+        <v>4</v>
+      </c>
+      <c r="B27" s="30" t="inlineStr">
+        <is>
+          <t>Cook veg with tamarind. Work in Stainless steel kadhai or saucepan — never aluminium. Cook to the doneness below, tasting salt at the end. Do not add onion, garlic or aluminium cookware.</t>
+        </is>
+      </c>
+      <c r="C27" s="31" t="n"/>
+      <c r="D27" s="31" t="n"/>
+    </row>
+    <row r="28" ht="54" customHeight="1">
+      <c r="A28" s="47" t="n">
+        <v>5</v>
+      </c>
+      <c r="B28" s="48" t="inlineStr">
+        <is>
+          <t>Add coconut paste. Work in Stainless steel kadhai or saucepan — never aluminium. Cook to the doneness below, tasting salt at the end. Do not add onion, garlic or aluminium cookware.</t>
+        </is>
+      </c>
+      <c r="C28" s="49" t="n"/>
+      <c r="D28" s="49" t="n"/>
+    </row>
+    <row r="29" ht="54" customHeight="1">
+      <c r="A29" s="32" t="n">
+        <v>6</v>
+      </c>
+      <c r="B29" s="30" t="inlineStr">
+        <is>
+          <t>Temper mustard, hing, curry leaves. Work in Stainless steel kadhai or saucepan — never aluminium. Cook to the doneness below, tasting salt at the end. Do not add onion, garlic or aluminium cookware.</t>
+        </is>
+      </c>
+      <c r="C29" s="31" t="n"/>
+      <c r="D29" s="31" t="n"/>
+    </row>
+    <row r="30" ht="42" customHeight="1">
+      <c r="A30" s="47" t="n">
+        <v>7</v>
+      </c>
+      <c r="B30" s="48" t="inlineStr">
+        <is>
+          <t>Doneness: vegetables yield to a knife, gravy coats a spoon, salt is balanced. Rest 2 minutes off the heat so seasoning settles.</t>
+        </is>
+      </c>
+      <c r="C30" s="49" t="n"/>
+      <c r="D30" s="49" t="n"/>
+    </row>
+    <row r="31" ht="42" customHeight="1">
+      <c r="A31" s="32" t="n">
+        <v>8</v>
+      </c>
+      <c r="B31" s="30" t="inlineStr">
+        <is>
+          <t>Taste and adjust salt, lemon or chilli only — do not add onion or garlic at the finish. Garnish as listed. Yield is 4 portions.</t>
+        </is>
+      </c>
+      <c r="C31" s="31" t="n"/>
+      <c r="D31" s="31" t="n"/>
+    </row>
+    <row r="32" ht="42" customHeight="1">
+      <c r="A32" s="47" t="n">
+        <v>9</v>
+      </c>
+      <c r="B32" s="48" t="inlineStr">
+        <is>
+          <t>Hold hot above 63 C if the pass is delayed, or cool quickly and reheat once only to piping hot. Do not hold in aluminium. Service: Hot.</t>
+        </is>
+      </c>
+      <c r="C32" s="49" t="n"/>
+      <c r="D32" s="49" t="n"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="21" t="inlineStr">
+        <is>
+          <t>Nutrition per portion</t>
+        </is>
+      </c>
+      <c r="B34" s="22" t="n"/>
+      <c r="C34" s="22" t="n"/>
+      <c r="D34" s="22" t="n"/>
+    </row>
+    <row r="35" ht="36" customHeight="1">
+      <c r="A35" s="12" t="inlineStr">
+        <is>
+          <t>kcal 206  ·  Protein 3 g  ·  Carbs 19 g  ·  Fat 15 g  ·  Fibre 5 g. Nutrition is a kitchen estimate from typical produce values, not a laboratory analysis.</t>
+        </is>
+      </c>
+      <c r="B35" s="50" t="n"/>
+      <c r="C35" s="50" t="n"/>
+      <c r="D35" s="50" t="n"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="24" t="inlineStr">
+        <is>
+          <t>Allergens</t>
+        </is>
+      </c>
+      <c r="B36" s="6" t="n"/>
+      <c r="C36" s="6" t="n"/>
+      <c r="D36" s="6" t="n"/>
+    </row>
+    <row r="37" ht="48" customHeight="1">
+      <c r="A37" s="25" t="inlineStr">
+        <is>
+          <t>Gluten (wheat) · Mustard · Always verify labels; this card is a kitchen estimate, not a lab certificate.</t>
+        </is>
+      </c>
+      <c r="B37" s="26" t="n"/>
+      <c r="C37" s="26" t="n"/>
+      <c r="D37" s="26" t="n"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="24" t="inlineStr">
+        <is>
+          <t>Chef notes</t>
+        </is>
+      </c>
+      <c r="B38" s="6" t="n"/>
+      <c r="C38" s="6" t="n"/>
+      <c r="D38" s="6" t="n"/>
+    </row>
+    <row r="39" ht="72" customHeight="1">
+      <c r="A39" s="25" t="inlineStr">
+        <is>
+          <t>For Khatkhate: keep the mix slightly drier than you think; wet mixes split or go greasy. Bloom hing in hot fat 20–30 seconds; raw hing tastes medicinal. Commercial hing is often cut with wheat flour — use a gluten-free hing if you must mark Gluten Free. Never cook tomato, tamarind, lemon, yogurt or milk in aluminium; use stainless steel, iron, clay or glass. Spice blends: read the packet. Many garam masalas hide onion or garlic powder.</t>
+        </is>
+      </c>
+      <c r="B39" s="26" t="n"/>
+      <c r="C39" s="26" t="n"/>
+      <c r="D39" s="26" t="n"/>
+    </row>
+    <row r="40">
+      <c r="A40" s="51" t="inlineStr">
+        <is>
+          <t>Service notes</t>
+        </is>
+      </c>
+      <c r="B40" s="52" t="n"/>
+      <c r="C40" s="52" t="n"/>
+      <c r="D40" s="52" t="n"/>
+    </row>
+    <row r="41" ht="64" customHeight="1">
+      <c r="A41" s="12" t="inlineStr">
+        <is>
+          <t>Plate with bread or rice from the same kitchen card. Sauce should nap, not flood. Service temperature: Hot. Allergen label for this dish: Gluten (wheat); Mustard; Always verify labels; this card is a kitchen estimate, not a lab certificate. State clearly: vegetarian, no onion, no garlic, no eggs, no meat, no fish. Nutrition on this card is an estimate for 1 portion of 4.</t>
+        </is>
+      </c>
+      <c r="B41" s="50" t="n"/>
+      <c r="C41" s="50" t="n"/>
+      <c r="D41" s="50" t="n"/>
+    </row>
   </sheetData>
-  <mergeCells count="18">
-    <mergeCell ref="A1:D1"/>
-    <mergeCell ref="C12:D12"/>
-    <mergeCell ref="A9:D9"/>
-    <mergeCell ref="C20:D20"/>
+  <mergeCells count="34">
     <mergeCell ref="A8:D8"/>
-    <mergeCell ref="C16:D16"/>
     <mergeCell ref="A22:D22"/>
     <mergeCell ref="C15:D15"/>
     <mergeCell ref="B23:D23"/>
+    <mergeCell ref="A35:D35"/>
+    <mergeCell ref="A38:D38"/>
+    <mergeCell ref="C14:D14"/>
+    <mergeCell ref="B29:D29"/>
+    <mergeCell ref="C20:D20"/>
+    <mergeCell ref="B28:D28"/>
+    <mergeCell ref="A9:D9"/>
+    <mergeCell ref="A40:D40"/>
+    <mergeCell ref="C16:D16"/>
+    <mergeCell ref="A34:D34"/>
+    <mergeCell ref="A39:D39"/>
+    <mergeCell ref="B30:D30"/>
+    <mergeCell ref="A11:D11"/>
+    <mergeCell ref="B24:D24"/>
+    <mergeCell ref="A36:D36"/>
+    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="C12:D12"/>
+    <mergeCell ref="B32:D32"/>
+    <mergeCell ref="B26:D26"/>
+    <mergeCell ref="A41:D41"/>
+    <mergeCell ref="B25:D25"/>
+    <mergeCell ref="C17:D17"/>
+    <mergeCell ref="A37:D37"/>
+    <mergeCell ref="B31:D31"/>
     <mergeCell ref="A3:D3"/>
     <mergeCell ref="C19:D19"/>
-    <mergeCell ref="C14:D14"/>
+    <mergeCell ref="B27:D27"/>
     <mergeCell ref="C13:D13"/>
     <mergeCell ref="A2:D2"/>
-    <mergeCell ref="A11:D11"/>
-    <mergeCell ref="C17:D17"/>
     <mergeCell ref="C18:D18"/>
-    <mergeCell ref="B24:D24"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" paperSize="9" fitToHeight="1" fitToWidth="1"/>
@@ -10643,7 +13791,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:D25"/>
+  <dimension ref="A1:D41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -10655,7 +13803,7 @@
     <row r="1" ht="32" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>RECIPE CARD  ·  Vegetable Caldin</t>
+          <t>Parslia Kitchen OS · RECIPE CARD · Vegetable Caldin</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -10665,7 +13813,7 @@
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>Goa kitchen  ·  Main  ·  Goan Hindu vegetarian / sattvic</t>
+          <t>Pure Prasad · No onion · No garlic · No eggs · No meat · No fish  ·  Goa  ·  Main</t>
         </is>
       </c>
       <c r="B2" s="4" t="n"/>
@@ -10685,44 +13833,44 @@
     <row r="5" ht="18" customHeight="1">
       <c r="A5" s="39" t="inlineStr">
         <is>
-          <t>Serves</t>
+          <t>YIELD</t>
         </is>
       </c>
       <c r="B5" s="39" t="inlineStr">
         <is>
-          <t>Prep</t>
+          <t>PORTION</t>
         </is>
       </c>
       <c r="C5" s="39" t="inlineStr">
         <is>
-          <t>Cook</t>
+          <t>SERVICE</t>
         </is>
       </c>
       <c r="D5" s="39" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>TIME</t>
         </is>
       </c>
     </row>
     <row r="6" ht="28" customHeight="1">
       <c r="A6" s="40" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>4 portions</t>
         </is>
       </c>
       <c r="B6" s="40" t="inlineStr">
         <is>
-          <t>15 min</t>
+          <t>1 portion</t>
         </is>
       </c>
       <c r="C6" s="40" t="inlineStr">
         <is>
-          <t>25 min</t>
+          <t>Hot</t>
         </is>
       </c>
       <c r="D6" s="40" t="inlineStr">
         <is>
-          <t>40 min</t>
+          <t>Prep 15 min · Cook 25 min</t>
         </is>
       </c>
     </row>
@@ -10960,36 +14108,215 @@
       <c r="C24" s="46" t="n"/>
       <c r="D24" s="46" t="n"/>
     </row>
-    <row r="25" ht="36" customHeight="1">
+    <row r="25" ht="66" customHeight="1">
       <c r="A25" s="47" t="n">
         <v>1</v>
       </c>
       <c r="B25" s="48" t="inlineStr">
         <is>
-          <t>Temper spices. Simmer veg in coconut milk with kokum until coated.</t>
+          <t>Mise en place. Weigh every ingredient on this card for 4 portions. Set Stainless steel kadhai or saucepan — never aluminium. Wash produce. Confirm spice blends have no onion or garlic powder. No onion, no garlic, no aluminium.</t>
         </is>
       </c>
       <c r="C25" s="49" t="n"/>
       <c r="D25" s="49" t="n"/>
     </row>
+    <row r="26" ht="42" customHeight="1">
+      <c r="A26" s="32" t="n">
+        <v>2</v>
+      </c>
+      <c r="B26" s="30" t="inlineStr">
+        <is>
+          <t>Cut vegetables to even size so they cook together. Use a heavy stainless steel milk pot. Acidic or milk dishes must never touch aluminium.</t>
+        </is>
+      </c>
+      <c r="C26" s="31" t="n"/>
+      <c r="D26" s="31" t="n"/>
+    </row>
+    <row r="27" ht="54" customHeight="1">
+      <c r="A27" s="47" t="n">
+        <v>3</v>
+      </c>
+      <c r="B27" s="48" t="inlineStr">
+        <is>
+          <t>Heat fat in Stainless steel kadhai or saucepan — never aluminium on medium. Bloom hing 20–30 seconds until fragrant — this is the onion-garlic stand-in. Do not burn it.</t>
+        </is>
+      </c>
+      <c r="C27" s="49" t="n"/>
+      <c r="D27" s="49" t="n"/>
+    </row>
+    <row r="28" ht="54" customHeight="1">
+      <c r="A28" s="32" t="n">
+        <v>4</v>
+      </c>
+      <c r="B28" s="30" t="inlineStr">
+        <is>
+          <t>Temper spices. Work in Stainless steel kadhai or saucepan — never aluminium. Cook to the doneness below, tasting salt at the end. Do not add onion, garlic or aluminium cookware.</t>
+        </is>
+      </c>
+      <c r="C28" s="31" t="n"/>
+      <c r="D28" s="31" t="n"/>
+    </row>
+    <row r="29" ht="66" customHeight="1">
+      <c r="A29" s="47" t="n">
+        <v>5</v>
+      </c>
+      <c r="B29" s="48" t="inlineStr">
+        <is>
+          <t>Simmer veg in coconut milk with kokum until coated. Work in Stainless steel kadhai or saucepan — never aluminium. Cook to the doneness below, tasting salt at the end. Do not add onion, garlic or aluminium cookware.</t>
+        </is>
+      </c>
+      <c r="C29" s="49" t="n"/>
+      <c r="D29" s="49" t="n"/>
+    </row>
+    <row r="30" ht="42" customHeight="1">
+      <c r="A30" s="32" t="n">
+        <v>6</v>
+      </c>
+      <c r="B30" s="30" t="inlineStr">
+        <is>
+          <t>Doneness: vegetables yield to a knife, gravy coats a spoon, salt is balanced. Rest 2 minutes off the heat so seasoning settles.</t>
+        </is>
+      </c>
+      <c r="C30" s="31" t="n"/>
+      <c r="D30" s="31" t="n"/>
+    </row>
+    <row r="31" ht="42" customHeight="1">
+      <c r="A31" s="47" t="n">
+        <v>7</v>
+      </c>
+      <c r="B31" s="48" t="inlineStr">
+        <is>
+          <t>Taste and adjust salt, lemon or chilli only — do not add onion or garlic at the finish. Garnish as listed. Yield is 4 portions.</t>
+        </is>
+      </c>
+      <c r="C31" s="49" t="n"/>
+      <c r="D31" s="49" t="n"/>
+    </row>
+    <row r="32" ht="42" customHeight="1">
+      <c r="A32" s="32" t="n">
+        <v>8</v>
+      </c>
+      <c r="B32" s="30" t="inlineStr">
+        <is>
+          <t>Hold hot above 63 C if the pass is delayed, or cool quickly and reheat once only to piping hot. Do not hold in aluminium. Service: Hot.</t>
+        </is>
+      </c>
+      <c r="C32" s="31" t="n"/>
+      <c r="D32" s="31" t="n"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="21" t="inlineStr">
+        <is>
+          <t>Nutrition per portion</t>
+        </is>
+      </c>
+      <c r="B34" s="22" t="n"/>
+      <c r="C34" s="22" t="n"/>
+      <c r="D34" s="22" t="n"/>
+    </row>
+    <row r="35" ht="36" customHeight="1">
+      <c r="A35" s="12" t="inlineStr">
+        <is>
+          <t>kcal 492  ·  Protein 10 g  ·  Carbs 41 g  ·  Fat 35 g  ·  Fibre 14 g. Nutrition is a kitchen estimate from typical produce values, not a laboratory analysis.</t>
+        </is>
+      </c>
+      <c r="B35" s="50" t="n"/>
+      <c r="C35" s="50" t="n"/>
+      <c r="D35" s="50" t="n"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="24" t="inlineStr">
+        <is>
+          <t>Allergens</t>
+        </is>
+      </c>
+      <c r="B36" s="6" t="n"/>
+      <c r="C36" s="6" t="n"/>
+      <c r="D36" s="6" t="n"/>
+    </row>
+    <row r="37" ht="48" customHeight="1">
+      <c r="A37" s="25" t="inlineStr">
+        <is>
+          <t>Gluten (wheat) · Milk · Always verify labels; this card is a kitchen estimate, not a lab certificate.</t>
+        </is>
+      </c>
+      <c r="B37" s="26" t="n"/>
+      <c r="C37" s="26" t="n"/>
+      <c r="D37" s="26" t="n"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="24" t="inlineStr">
+        <is>
+          <t>Chef notes</t>
+        </is>
+      </c>
+      <c r="B38" s="6" t="n"/>
+      <c r="C38" s="6" t="n"/>
+      <c r="D38" s="6" t="n"/>
+    </row>
+    <row r="39" ht="72" customHeight="1">
+      <c r="A39" s="25" t="inlineStr">
+        <is>
+          <t>For Vegetable Caldin: keep the mix slightly drier than you think; wet mixes split or go greasy. Bloom hing in hot fat 20–30 seconds; raw hing tastes medicinal. Commercial hing is often cut with wheat flour — use a gluten-free hing if you must mark Gluten Free. Never cook tomato, tamarind, lemon, yogurt or milk in aluminium; use stainless steel, iron, clay or glass. Spice blends: read the packet. Many garam masalas hide onion or garlic powder.</t>
+        </is>
+      </c>
+      <c r="B39" s="26" t="n"/>
+      <c r="C39" s="26" t="n"/>
+      <c r="D39" s="26" t="n"/>
+    </row>
+    <row r="40">
+      <c r="A40" s="51" t="inlineStr">
+        <is>
+          <t>Service notes</t>
+        </is>
+      </c>
+      <c r="B40" s="52" t="n"/>
+      <c r="C40" s="52" t="n"/>
+      <c r="D40" s="52" t="n"/>
+    </row>
+    <row r="41" ht="64" customHeight="1">
+      <c r="A41" s="12" t="inlineStr">
+        <is>
+          <t>Plate with bread or rice from the same kitchen card. Sauce should nap, not flood. Service temperature: Hot. Allergen label for this dish: Gluten (wheat); Milk; Always verify labels; this card is a kitchen estimate, not a lab certificate. State clearly: vegetarian, no onion, no garlic, no eggs, no meat, no fish. Nutrition on this card is an estimate for 1 portion of 4.</t>
+        </is>
+      </c>
+      <c r="B41" s="50" t="n"/>
+      <c r="C41" s="50" t="n"/>
+      <c r="D41" s="50" t="n"/>
+    </row>
   </sheetData>
-  <mergeCells count="19">
+  <mergeCells count="34">
     <mergeCell ref="A23:D23"/>
     <mergeCell ref="A8:D8"/>
     <mergeCell ref="C15:D15"/>
+    <mergeCell ref="A35:D35"/>
+    <mergeCell ref="A38:D38"/>
     <mergeCell ref="C14:D14"/>
+    <mergeCell ref="B29:D29"/>
     <mergeCell ref="C20:D20"/>
+    <mergeCell ref="B28:D28"/>
     <mergeCell ref="A9:D9"/>
+    <mergeCell ref="A40:D40"/>
     <mergeCell ref="C16:D16"/>
+    <mergeCell ref="A34:D34"/>
+    <mergeCell ref="A39:D39"/>
+    <mergeCell ref="B30:D30"/>
     <mergeCell ref="A11:D11"/>
     <mergeCell ref="B24:D24"/>
+    <mergeCell ref="A36:D36"/>
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="C12:D12"/>
     <mergeCell ref="C21:D21"/>
+    <mergeCell ref="B32:D32"/>
+    <mergeCell ref="B26:D26"/>
+    <mergeCell ref="A41:D41"/>
     <mergeCell ref="B25:D25"/>
     <mergeCell ref="C17:D17"/>
+    <mergeCell ref="A37:D37"/>
+    <mergeCell ref="B31:D31"/>
     <mergeCell ref="A3:D3"/>
     <mergeCell ref="C19:D19"/>
+    <mergeCell ref="B27:D27"/>
     <mergeCell ref="C13:D13"/>
     <mergeCell ref="A2:D2"/>
     <mergeCell ref="C18:D18"/>
@@ -11006,7 +14333,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:D24"/>
+  <dimension ref="A1:D41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -11018,7 +14345,7 @@
     <row r="1" ht="32" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>RECIPE CARD  ·  Moong Coconut Usal</t>
+          <t>Parslia Kitchen OS · RECIPE CARD · Moong Coconut Usal</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -11028,7 +14355,7 @@
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>Goa kitchen  ·  Main  ·  Goan Hindu vegetarian / sattvic</t>
+          <t>Pure Prasad · No onion · No garlic · No eggs · No meat · No fish  ·  Goa  ·  Main</t>
         </is>
       </c>
       <c r="B2" s="4" t="n"/>
@@ -11048,44 +14375,44 @@
     <row r="5" ht="18" customHeight="1">
       <c r="A5" s="39" t="inlineStr">
         <is>
-          <t>Serves</t>
+          <t>YIELD</t>
         </is>
       </c>
       <c r="B5" s="39" t="inlineStr">
         <is>
-          <t>Prep</t>
+          <t>PORTION</t>
         </is>
       </c>
       <c r="C5" s="39" t="inlineStr">
         <is>
-          <t>Cook</t>
+          <t>SERVICE</t>
         </is>
       </c>
       <c r="D5" s="39" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>TIME</t>
         </is>
       </c>
     </row>
     <row r="6" ht="28" customHeight="1">
       <c r="A6" s="40" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>4 portions</t>
         </is>
       </c>
       <c r="B6" s="40" t="inlineStr">
         <is>
-          <t>10 min</t>
+          <t>1 portion</t>
         </is>
       </c>
       <c r="C6" s="40" t="inlineStr">
         <is>
-          <t>20 min</t>
+          <t>Hot</t>
         </is>
       </c>
       <c r="D6" s="40" t="inlineStr">
         <is>
-          <t>30 min</t>
+          <t>Prep 10 min · Cook 20 min</t>
         </is>
       </c>
     </row>
@@ -11305,38 +14632,230 @@
       <c r="C23" s="46" t="n"/>
       <c r="D23" s="46" t="n"/>
     </row>
-    <row r="24" ht="42" customHeight="1">
+    <row r="24" ht="66" customHeight="1">
       <c r="A24" s="47" t="n">
         <v>1</v>
       </c>
       <c r="B24" s="48" t="inlineStr">
         <is>
-          <t>Temper, add sprouts, coconut, splash of water. Cover 8 minutes. Lemon.</t>
+          <t>Mise en place. Weigh every ingredient on this card for 4 portions. Set Stainless steel kadhai or saucepan — never aluminium. Wash produce. Confirm spice blends have no onion or garlic powder. No onion, no garlic, no aluminium.</t>
         </is>
       </c>
       <c r="C24" s="49" t="n"/>
       <c r="D24" s="49" t="n"/>
     </row>
+    <row r="25" ht="36" customHeight="1">
+      <c r="A25" s="32" t="n">
+        <v>2</v>
+      </c>
+      <c r="B25" s="30" t="inlineStr">
+        <is>
+          <t>Cut vegetables to even size so they cook together.</t>
+        </is>
+      </c>
+      <c r="C25" s="31" t="n"/>
+      <c r="D25" s="31" t="n"/>
+    </row>
+    <row r="26" ht="54" customHeight="1">
+      <c r="A26" s="47" t="n">
+        <v>3</v>
+      </c>
+      <c r="B26" s="48" t="inlineStr">
+        <is>
+          <t>Heat fat in Stainless steel kadhai or saucepan — never aluminium on medium. Bloom hing 20–30 seconds until fragrant — this is the onion-garlic stand-in. Do not burn it.</t>
+        </is>
+      </c>
+      <c r="C26" s="49" t="n"/>
+      <c r="D26" s="49" t="n"/>
+    </row>
+    <row r="27" ht="54" customHeight="1">
+      <c r="A27" s="32" t="n">
+        <v>4</v>
+      </c>
+      <c r="B27" s="30" t="inlineStr">
+        <is>
+          <t>Temper, add sprouts, coconut, splash of water. Work in Stainless steel kadhai or saucepan — never aluminium. Cook to the doneness below, tasting salt at the end. Do not add onion, garlic or aluminium cookware.</t>
+        </is>
+      </c>
+      <c r="C27" s="31" t="n"/>
+      <c r="D27" s="31" t="n"/>
+    </row>
+    <row r="28" ht="54" customHeight="1">
+      <c r="A28" s="47" t="n">
+        <v>5</v>
+      </c>
+      <c r="B28" s="48" t="inlineStr">
+        <is>
+          <t>Cover 8 minutes. Work in Stainless steel kadhai or saucepan — never aluminium. Cook to the doneness below, tasting salt at the end. Do not add onion, garlic or aluminium cookware.</t>
+        </is>
+      </c>
+      <c r="C28" s="49" t="n"/>
+      <c r="D28" s="49" t="n"/>
+    </row>
+    <row r="29" ht="54" customHeight="1">
+      <c r="A29" s="32" t="n">
+        <v>6</v>
+      </c>
+      <c r="B29" s="30" t="inlineStr">
+        <is>
+          <t>Lemon. Work in Stainless steel kadhai or saucepan — never aluminium. Cook to the doneness below, tasting salt at the end. Do not add onion, garlic or aluminium cookware.</t>
+        </is>
+      </c>
+      <c r="C29" s="31" t="n"/>
+      <c r="D29" s="31" t="n"/>
+    </row>
+    <row r="30" ht="42" customHeight="1">
+      <c r="A30" s="47" t="n">
+        <v>7</v>
+      </c>
+      <c r="B30" s="48" t="inlineStr">
+        <is>
+          <t>Doneness: vegetables yield to a knife, gravy coats a spoon, salt is balanced. Rest 2 minutes off the heat so seasoning settles.</t>
+        </is>
+      </c>
+      <c r="C30" s="49" t="n"/>
+      <c r="D30" s="49" t="n"/>
+    </row>
+    <row r="31" ht="42" customHeight="1">
+      <c r="A31" s="32" t="n">
+        <v>8</v>
+      </c>
+      <c r="B31" s="30" t="inlineStr">
+        <is>
+          <t>Taste and adjust salt, lemon or chilli only — do not add onion or garlic at the finish. Garnish as listed. Yield is 4 portions.</t>
+        </is>
+      </c>
+      <c r="C31" s="31" t="n"/>
+      <c r="D31" s="31" t="n"/>
+    </row>
+    <row r="32" ht="42" customHeight="1">
+      <c r="A32" s="47" t="n">
+        <v>9</v>
+      </c>
+      <c r="B32" s="48" t="inlineStr">
+        <is>
+          <t>Hold hot above 63 C if the pass is delayed, or cool quickly and reheat once only to piping hot. Do not hold in aluminium. Service: Hot.</t>
+        </is>
+      </c>
+      <c r="C32" s="49" t="n"/>
+      <c r="D32" s="49" t="n"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="21" t="inlineStr">
+        <is>
+          <t>Nutrition per portion</t>
+        </is>
+      </c>
+      <c r="B34" s="22" t="n"/>
+      <c r="C34" s="22" t="n"/>
+      <c r="D34" s="22" t="n"/>
+    </row>
+    <row r="35" ht="36" customHeight="1">
+      <c r="A35" s="12" t="inlineStr">
+        <is>
+          <t>kcal 332  ·  Protein 19 g  ·  Carbs 51 g  ·  Fat 7 g  ·  Fibre 14 g. Nutrition is a kitchen estimate from typical produce values, not a laboratory analysis.</t>
+        </is>
+      </c>
+      <c r="B35" s="50" t="n"/>
+      <c r="C35" s="50" t="n"/>
+      <c r="D35" s="50" t="n"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="24" t="inlineStr">
+        <is>
+          <t>Allergens</t>
+        </is>
+      </c>
+      <c r="B36" s="6" t="n"/>
+      <c r="C36" s="6" t="n"/>
+      <c r="D36" s="6" t="n"/>
+    </row>
+    <row r="37" ht="48" customHeight="1">
+      <c r="A37" s="25" t="inlineStr">
+        <is>
+          <t>Gluten (wheat) · Mustard · Always verify labels; this card is a kitchen estimate, not a lab certificate.</t>
+        </is>
+      </c>
+      <c r="B37" s="26" t="n"/>
+      <c r="C37" s="26" t="n"/>
+      <c r="D37" s="26" t="n"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="24" t="inlineStr">
+        <is>
+          <t>Chef notes</t>
+        </is>
+      </c>
+      <c r="B38" s="6" t="n"/>
+      <c r="C38" s="6" t="n"/>
+      <c r="D38" s="6" t="n"/>
+    </row>
+    <row r="39" ht="72" customHeight="1">
+      <c r="A39" s="25" t="inlineStr">
+        <is>
+          <t>For Moong Coconut Usal: keep the mix slightly drier than you think; wet mixes split or go greasy. Bloom hing in hot fat 20–30 seconds; raw hing tastes medicinal. Commercial hing is often cut with wheat flour — use a gluten-free hing if you must mark Gluten Free. Never cook tomato, tamarind, lemon, yogurt or milk in aluminium; use stainless steel, iron, clay or glass. Spice blends: read the packet. Many garam masalas hide onion or garlic powder.</t>
+        </is>
+      </c>
+      <c r="B39" s="26" t="n"/>
+      <c r="C39" s="26" t="n"/>
+      <c r="D39" s="26" t="n"/>
+    </row>
+    <row r="40">
+      <c r="A40" s="51" t="inlineStr">
+        <is>
+          <t>Service notes</t>
+        </is>
+      </c>
+      <c r="B40" s="52" t="n"/>
+      <c r="C40" s="52" t="n"/>
+      <c r="D40" s="52" t="n"/>
+    </row>
+    <row r="41" ht="64" customHeight="1">
+      <c r="A41" s="12" t="inlineStr">
+        <is>
+          <t>Plate with bread or rice from the same kitchen card. Sauce should nap, not flood. Service temperature: Hot. Allergen label for this dish: Gluten (wheat); Mustard; Always verify labels; this card is a kitchen estimate, not a lab certificate. State clearly: vegetarian, no onion, no garlic, no eggs, no meat, no fish. Nutrition on this card is an estimate for 1 portion of 4.</t>
+        </is>
+      </c>
+      <c r="B41" s="50" t="n"/>
+      <c r="C41" s="50" t="n"/>
+      <c r="D41" s="50" t="n"/>
+    </row>
   </sheetData>
-  <mergeCells count="18">
-    <mergeCell ref="A1:D1"/>
-    <mergeCell ref="C12:D12"/>
-    <mergeCell ref="A9:D9"/>
-    <mergeCell ref="C20:D20"/>
+  <mergeCells count="34">
     <mergeCell ref="A8:D8"/>
-    <mergeCell ref="C16:D16"/>
     <mergeCell ref="A22:D22"/>
     <mergeCell ref="C15:D15"/>
     <mergeCell ref="B23:D23"/>
+    <mergeCell ref="A35:D35"/>
+    <mergeCell ref="A38:D38"/>
+    <mergeCell ref="C14:D14"/>
+    <mergeCell ref="B29:D29"/>
+    <mergeCell ref="C20:D20"/>
+    <mergeCell ref="B28:D28"/>
+    <mergeCell ref="A9:D9"/>
+    <mergeCell ref="A40:D40"/>
+    <mergeCell ref="C16:D16"/>
+    <mergeCell ref="A34:D34"/>
+    <mergeCell ref="A39:D39"/>
+    <mergeCell ref="B30:D30"/>
+    <mergeCell ref="A11:D11"/>
+    <mergeCell ref="B24:D24"/>
+    <mergeCell ref="A36:D36"/>
+    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="C12:D12"/>
+    <mergeCell ref="B32:D32"/>
+    <mergeCell ref="B26:D26"/>
+    <mergeCell ref="A41:D41"/>
+    <mergeCell ref="B25:D25"/>
+    <mergeCell ref="C17:D17"/>
+    <mergeCell ref="A37:D37"/>
+    <mergeCell ref="B31:D31"/>
     <mergeCell ref="A3:D3"/>
     <mergeCell ref="C19:D19"/>
-    <mergeCell ref="C14:D14"/>
+    <mergeCell ref="B27:D27"/>
     <mergeCell ref="C13:D13"/>
     <mergeCell ref="A2:D2"/>
-    <mergeCell ref="A11:D11"/>
-    <mergeCell ref="C17:D17"/>
     <mergeCell ref="C18:D18"/>
-    <mergeCell ref="B24:D24"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" paperSize="9" fitToHeight="1" fitToWidth="1"/>
